--- a/doc/SourceData2.xlsx
+++ b/doc/SourceData2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YH.CHIU\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0639CED5-EAA4-482D-90A0-7BAB0E6D6648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725A7D44-79A0-4843-A795-E76F5B203E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
   <sheets>
     <sheet name="黃光CT總表" sheetId="2" r:id="rId1"/>
@@ -3764,7 +3764,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3888,6 +3888,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4520,7 +4526,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5084,9 +5090,6 @@
     <xf numFmtId="178" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5108,30 +5111,6 @@
     <xf numFmtId="0" fontId="17" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="17" fillId="21" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5139,6 +5118,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="18" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="18" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6440,21 +6437,21 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G8" s="266" t="s">
+      <c r="G8" s="263" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="267"/>
-      <c r="I8" s="268"/>
-      <c r="J8" s="269" t="s">
+      <c r="H8" s="264"/>
+      <c r="I8" s="265"/>
+      <c r="J8" s="266" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="269"/>
-      <c r="L8" s="269"/>
-      <c r="M8" s="270" t="s">
+      <c r="K8" s="266"/>
+      <c r="L8" s="266"/>
+      <c r="M8" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="270"/>
-      <c r="O8" s="270"/>
+      <c r="N8" s="267"/>
+      <c r="O8" s="267"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6508,7 +6505,7 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="106.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="253" t="s">
+      <c r="B10" s="250" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6561,14 +6558,14 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="254"/>
-      <c r="C11" s="256" t="s">
+      <c r="B11" s="251"/>
+      <c r="C11" s="253" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="258">
+      <c r="E11" s="255">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6614,12 +6611,12 @@
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="2:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="254"/>
-      <c r="C12" s="257"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="254"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="259"/>
+      <c r="E12" s="256"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6663,14 +6660,14 @@
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="254"/>
-      <c r="C13" s="260" t="s">
+      <c r="B13" s="251"/>
+      <c r="C13" s="257" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="263">
+      <c r="E13" s="260">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6701,16 +6698,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="239"/>
-      <c r="Q13" s="245"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="242"/>
     </row>
     <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="254"/>
-      <c r="C14" s="261"/>
+      <c r="B14" s="251"/>
+      <c r="C14" s="258"/>
       <c r="D14" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="E14" s="264"/>
+      <c r="E14" s="261"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6730,16 +6727,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="239"/>
-      <c r="Q14" s="245"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="242"/>
     </row>
     <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="254"/>
-      <c r="C15" s="262"/>
+      <c r="B15" s="251"/>
+      <c r="C15" s="259"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="265"/>
+      <c r="E15" s="262"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6777,11 +6774,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="239"/>
-      <c r="Q15" s="245"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="242"/>
     </row>
     <row r="16" spans="2:17" ht="100.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="254"/>
+      <c r="B16" s="251"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6831,7 +6828,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="98.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="255"/>
+      <c r="B17" s="252"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -6886,7 +6883,7 @@
       <c r="Q17" s="31"/>
     </row>
     <row r="18" spans="2:18" ht="122.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="205" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6941,7 +6938,7 @@
       <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="209"/>
+      <c r="B19" s="206"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -6995,14 +6992,14 @@
       <c r="R19" s="37"/>
     </row>
     <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="209"/>
+      <c r="B20" s="206"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="246">
+      <c r="E20" s="243">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -7044,19 +7041,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="248"/>
-      <c r="Q20" s="250"/>
+      <c r="P20" s="245"/>
+      <c r="Q20" s="247"/>
       <c r="R20" s="41"/>
     </row>
     <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="209"/>
+      <c r="B21" s="206"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="247"/>
+      <c r="E21" s="244"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -7087,19 +7084,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="239"/>
-      <c r="Q21" s="251"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="248"/>
       <c r="R21" s="41"/>
     </row>
     <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="209"/>
+      <c r="B22" s="206"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="225" t="s">
+      <c r="D22" s="222" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="247"/>
+      <c r="E22" s="244"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7139,17 +7136,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="239"/>
-      <c r="Q22" s="251"/>
+      <c r="P22" s="236"/>
+      <c r="Q22" s="248"/>
       <c r="R22" s="41"/>
     </row>
     <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="209"/>
+      <c r="B23" s="206"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="226"/>
-      <c r="E23" s="232"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="229"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7189,12 +7186,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="249"/>
-      <c r="Q23" s="252"/>
+      <c r="P23" s="246"/>
+      <c r="Q23" s="249"/>
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="2:18" ht="133.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="210"/>
+      <c r="B24" s="207"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7248,29 +7245,29 @@
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="229" t="s">
+      <c r="B25" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="215" t="s">
+      <c r="C25" s="212" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="215" t="s">
+      <c r="D25" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="237">
+      <c r="E25" s="234">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="274">
+      <c r="G25" s="271">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="273">
+      <c r="H25" s="270">
         <v>8</v>
       </c>
-      <c r="I25" s="271">
+      <c r="I25" s="268">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7286,14 +7283,14 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="271">
+      <c r="M25" s="268">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="273">
+      <c r="N25" s="270">
         <v>10</v>
       </c>
-      <c r="O25" s="271">
+      <c r="O25" s="268">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7301,16 +7298,16 @@
       <c r="Q25" s="51"/>
     </row>
     <row r="26" spans="2:18" ht="136.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="229"/>
-      <c r="C26" s="215"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="238"/>
+      <c r="B26" s="226"/>
+      <c r="C26" s="212"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="235"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="275"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="272"/>
+      <c r="G26" s="272"/>
+      <c r="H26" s="259"/>
+      <c r="I26" s="269"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7323,21 +7320,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="272"/>
-      <c r="N26" s="262"/>
-      <c r="O26" s="272"/>
+      <c r="M26" s="269"/>
+      <c r="N26" s="259"/>
+      <c r="O26" s="269"/>
       <c r="P26" s="141"/>
       <c r="Q26" s="23"/>
     </row>
     <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="229"/>
+      <c r="B27" s="226"/>
       <c r="C27" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="230" t="s">
+      <c r="D27" s="227" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="231">
+      <c r="E27" s="228">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7379,16 +7376,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="233"/>
-      <c r="Q27" s="227"/>
+      <c r="P27" s="230"/>
+      <c r="Q27" s="224"/>
     </row>
     <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="229"/>
+      <c r="B28" s="226"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="226"/>
-      <c r="E28" s="232"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="229"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7425,11 +7422,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="234"/>
-      <c r="Q28" s="228"/>
+      <c r="P28" s="231"/>
+      <c r="Q28" s="225"/>
     </row>
     <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="229"/>
+      <c r="B29" s="226"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7482,7 +7479,7 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="229"/>
+      <c r="B30" s="226"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7535,14 +7532,14 @@
       <c r="Q30" s="58"/>
     </row>
     <row r="31" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="229"/>
-      <c r="C31" s="214" t="s">
+      <c r="B31" s="226"/>
+      <c r="C31" s="211" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="215" t="s">
+      <c r="D31" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="211">
+      <c r="E31" s="208">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7582,10 +7579,10 @@
       <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="229"/>
-      <c r="C32" s="214"/>
-      <c r="D32" s="215"/>
-      <c r="E32" s="212"/>
+      <c r="B32" s="226"/>
+      <c r="C32" s="211"/>
+      <c r="D32" s="212"/>
+      <c r="E32" s="209"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7623,10 +7620,10 @@
       <c r="Q32" s="60"/>
     </row>
     <row r="33" spans="2:17" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="229"/>
-      <c r="C33" s="214"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="213"/>
+      <c r="B33" s="226"/>
+      <c r="C33" s="211"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="210"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7664,14 +7661,14 @@
       <c r="Q33" s="60"/>
     </row>
     <row r="34" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="229"/>
-      <c r="C34" s="214" t="s">
+      <c r="B34" s="226"/>
+      <c r="C34" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="215" t="s">
+      <c r="D34" s="212" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="216">
+      <c r="E34" s="213">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7710,10 +7707,10 @@
       <c r="Q34" s="31"/>
     </row>
     <row r="35" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="229"/>
-      <c r="C35" s="214"/>
-      <c r="D35" s="215"/>
-      <c r="E35" s="216"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="211"/>
+      <c r="D35" s="212"/>
+      <c r="E35" s="213"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7754,7 +7751,7 @@
       <c r="Q35" s="31"/>
     </row>
     <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="229"/>
+      <c r="B36" s="226"/>
       <c r="C36" s="139" t="s">
         <v>97</v>
       </c>
@@ -7804,14 +7801,14 @@
       <c r="Q36" s="126"/>
     </row>
     <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="229"/>
-      <c r="C37" s="223" t="s">
+      <c r="B37" s="226"/>
+      <c r="C37" s="220" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="235">
+      <c r="E37" s="232">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7853,18 +7850,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="239"/>
-      <c r="Q37" s="241" t="s">
+      <c r="P37" s="236"/>
+      <c r="Q37" s="238" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="229"/>
-      <c r="C38" s="224"/>
+      <c r="B38" s="226"/>
+      <c r="C38" s="221"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="236"/>
+      <c r="E38" s="233"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -7904,18 +7901,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="239"/>
-      <c r="Q38" s="242"/>
+      <c r="P38" s="236"/>
+      <c r="Q38" s="239"/>
     </row>
     <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="229"/>
+      <c r="B39" s="226"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="236"/>
+      <c r="E39" s="233"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -7955,20 +7952,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="239"/>
-      <c r="Q39" s="243" t="s">
+      <c r="P39" s="236"/>
+      <c r="Q39" s="240" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="229"/>
+      <c r="B40" s="226"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="236"/>
+      <c r="E40" s="233"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -8008,11 +8005,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="240"/>
-      <c r="Q40" s="244"/>
+      <c r="P40" s="237"/>
+      <c r="Q40" s="241"/>
     </row>
     <row r="41" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="208" t="s">
+      <c r="B41" s="205" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -8021,7 +8018,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="216">
+      <c r="E41" s="213">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -8069,14 +8066,14 @@
       <c r="Q41" s="59"/>
     </row>
     <row r="42" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="209"/>
+      <c r="B42" s="206"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="216"/>
+      <c r="E42" s="213"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8122,7 +8119,7 @@
       <c r="Q42" s="66"/>
     </row>
     <row r="43" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="209"/>
+      <c r="B43" s="206"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8174,7 +8171,7 @@
       <c r="Q43" s="121"/>
     </row>
     <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="209"/>
+      <c r="B44" s="206"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8227,7 +8224,7 @@
       <c r="Q44" s="68"/>
     </row>
     <row r="45" spans="2:17" ht="97.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="209"/>
+      <c r="B45" s="206"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8280,14 +8277,14 @@
       <c r="Q45" s="51"/>
     </row>
     <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="209"/>
-      <c r="C46" s="217" t="s">
+      <c r="B46" s="206"/>
+      <c r="C46" s="214" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="220" t="s">
+      <c r="D46" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="211">
+      <c r="E46" s="208">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8333,10 +8330,10 @@
       <c r="Q46" s="69"/>
     </row>
     <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="209"/>
-      <c r="C47" s="218"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="212"/>
+      <c r="B47" s="206"/>
+      <c r="C47" s="215"/>
+      <c r="D47" s="218"/>
+      <c r="E47" s="209"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8380,10 +8377,10 @@
       <c r="Q47" s="69"/>
     </row>
     <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="209"/>
-      <c r="C48" s="219"/>
-      <c r="D48" s="222"/>
-      <c r="E48" s="213"/>
+      <c r="B48" s="206"/>
+      <c r="C48" s="216"/>
+      <c r="D48" s="219"/>
+      <c r="E48" s="210"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8424,7 +8421,7 @@
       <c r="Q48" s="69"/>
     </row>
     <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="209"/>
+      <c r="B49" s="206"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8477,7 +8474,7 @@
       <c r="Q49" s="71"/>
     </row>
     <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="210"/>
+      <c r="B50" s="207"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8527,7 +8524,7 @@
       <c r="Q50" s="72"/>
     </row>
     <row r="51" spans="2:17" ht="88.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="208" t="s">
+      <c r="B51" s="205" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8582,7 +8579,7 @@
       </c>
     </row>
     <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="209"/>
+      <c r="B52" s="206"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8632,7 +8629,7 @@
       <c r="Q52" s="30"/>
     </row>
     <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="209"/>
+      <c r="B53" s="206"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8682,7 +8679,7 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="71.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="209"/>
+      <c r="B54" s="206"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8730,7 +8727,7 @@
       <c r="Q54" s="76"/>
     </row>
     <row r="55" spans="2:17" s="113" customFormat="1" ht="77.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="210"/>
+      <c r="B55" s="207"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -9926,10 +9923,10 @@
     <col min="4" max="4" width="30" style="147" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="147" customWidth="1"/>
     <col min="6" max="7" width="13.875" style="150" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="204"/>
+    <col min="8" max="16384" width="8.875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="201" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -9948,11 +9945,11 @@
       <c r="F1" s="182" t="s">
         <v>647</v>
       </c>
-      <c r="G1" s="206" t="s">
+      <c r="G1" s="197" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -9968,14 +9965,14 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="203">
+      <c r="F2" s="200">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="186">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -9991,37 +9988,37 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="203">
-        <v>12.115555555555554</v>
+      <c r="F3" s="200">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G3" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="197" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="197" t="s">
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="180" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="200" t="s">
+      <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="202">
-        <v>7.4</v>
-      </c>
-      <c r="G4" s="190">
+      <c r="F4" s="201">
+        <v>3.8</v>
+      </c>
+      <c r="G4" s="189">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -10037,14 +10034,14 @@
       <c r="E5" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F5" s="202">
-        <v>7.4</v>
-      </c>
-      <c r="G5" s="190">
+      <c r="F5" s="201">
+        <v>3.8</v>
+      </c>
+      <c r="G5" s="189">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -10060,14 +10057,14 @@
       <c r="E6" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F6" s="189">
-        <v>12.379943502824856</v>
-      </c>
-      <c r="G6" s="190">
+      <c r="F6" s="202">
+        <v>12.379943502824901</v>
+      </c>
+      <c r="G6" s="189">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -10083,14 +10080,14 @@
       <c r="E7" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F7" s="189">
-        <v>12.072378043916389</v>
-      </c>
-      <c r="G7" s="207">
+      <c r="F7" s="202">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G7" s="198">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="201" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="145" t="s">
         <v>162</v>
       </c>
@@ -10106,14 +10103,14 @@
       <c r="E8" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F8" s="189">
-        <v>13.333333333333334</v>
-      </c>
-      <c r="G8" s="190">
+      <c r="F8" s="202">
+        <v>6.6666666666666696</v>
+      </c>
+      <c r="G8" s="189">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="145" t="s">
         <v>162</v>
       </c>
@@ -10129,14 +10126,14 @@
       <c r="E9" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F9" s="203">
-        <v>11.158095238095235</v>
+      <c r="F9" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G9" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -10146,66 +10143,66 @@
       <c r="C10" s="177" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="199" t="s">
+      <c r="D10" s="180" t="s">
         <v>196</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F10" s="189">
-        <v>8.9485714285714266</v>
-      </c>
-      <c r="G10" s="190">
+      <c r="F10" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G10" s="189">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="191" t="s">
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="192" t="s">
+      <c r="C11" s="191" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="193" t="s">
+      <c r="D11" s="192" t="s">
         <v>198</v>
       </c>
-      <c r="E11" s="194" t="s">
+      <c r="E11" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F11" s="205">
+      <c r="F11" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G11" s="194">
+      <c r="G11" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B12" s="191" t="s">
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="192" t="s">
+      <c r="C12" s="191" t="s">
         <v>199</v>
       </c>
-      <c r="D12" s="193" t="s">
+      <c r="D12" s="192" t="s">
         <v>200</v>
       </c>
-      <c r="E12" s="194" t="s">
+      <c r="E12" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F12" s="205">
+      <c r="F12" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G12" s="194">
+      <c r="G12" s="193">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="145" t="s">
         <v>162</v>
       </c>
@@ -10221,14 +10218,14 @@
       <c r="E13" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F13" s="203">
-        <v>11.158095238095235</v>
+      <c r="F13" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G13" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -10244,14 +10241,14 @@
       <c r="E14" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F14" s="203">
-        <v>11.158095238095235</v>
+      <c r="F14" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G14" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -10267,21 +10264,21 @@
       <c r="E15" s="186" t="s">
         <v>633</v>
       </c>
-      <c r="F15" s="203">
+      <c r="F15" s="200">
         <v>13.333333333333334</v>
       </c>
       <c r="G15" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B16" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C16" s="177" t="s">
+      <c r="C16" s="199" t="s">
         <v>650</v>
       </c>
       <c r="D16" s="180" t="s">
@@ -10290,14 +10287,14 @@
       <c r="E16" s="186" t="s">
         <v>633</v>
       </c>
-      <c r="F16" s="203">
-        <v>8.16</v>
+      <c r="F16" s="200">
+        <v>4.8</v>
       </c>
       <c r="G16" s="186">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A17" s="145" t="s">
         <v>162</v>
       </c>
@@ -10313,14 +10310,14 @@
       <c r="E17" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F17" s="189">
+      <c r="F17" s="202">
         <v>3.9080000000000004</v>
       </c>
       <c r="G17" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="145" t="s">
         <v>162</v>
       </c>
@@ -10336,14 +10333,14 @@
       <c r="E18" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F18" s="203">
-        <v>10.275555555555552</v>
+      <c r="F18" s="200">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G18" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="145" t="s">
         <v>162</v>
       </c>
@@ -10359,14 +10356,14 @@
       <c r="E19" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F19" s="203">
-        <v>10.275555555555552</v>
+      <c r="F19" s="200">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G19" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="145" t="s">
         <v>162</v>
       </c>
@@ -10382,14 +10379,14 @@
       <c r="E20" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F20" s="203">
-        <v>3.9439999999999995</v>
+      <c r="F20" s="200">
+        <v>2.3199999999999998</v>
       </c>
       <c r="G20" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A21" s="145" t="s">
         <v>162</v>
       </c>
@@ -10405,14 +10402,14 @@
       <c r="E21" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F21" s="203">
-        <v>12.5138888888889</v>
+      <c r="F21" s="200">
+        <v>4.63657407407407</v>
       </c>
       <c r="G21" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="145" t="s">
         <v>162</v>
       </c>
@@ -10422,89 +10419,89 @@
       <c r="C22" s="177" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="199" t="s">
+      <c r="D22" s="180" t="s">
         <v>236</v>
       </c>
       <c r="E22" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F22" s="203">
-        <v>8.9485714285714302</v>
+      <c r="F22" s="202">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G22" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="191" t="s">
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C23" s="192" t="s">
+      <c r="C23" s="191" t="s">
         <v>237</v>
       </c>
-      <c r="D23" s="193" t="s">
+      <c r="D23" s="192" t="s">
         <v>238</v>
       </c>
-      <c r="E23" s="194" t="s">
+      <c r="E23" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F23" s="205">
+      <c r="F23" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G23" s="194">
+      <c r="G23" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B24" s="191" t="s">
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="192" t="s">
+      <c r="C24" s="191" t="s">
         <v>239</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="192" t="s">
         <v>240</v>
       </c>
-      <c r="E24" s="194" t="s">
+      <c r="E24" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F24" s="205">
+      <c r="F24" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G24" s="194">
+      <c r="G24" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="191" t="s">
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="192" t="s">
+      <c r="C25" s="191" t="s">
         <v>243</v>
       </c>
-      <c r="D25" s="193" t="s">
+      <c r="D25" s="192" t="s">
         <v>244</v>
       </c>
-      <c r="E25" s="194" t="s">
+      <c r="E25" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F25" s="205">
+      <c r="F25" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G25" s="194">
+      <c r="G25" s="193">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -10520,14 +10517,14 @@
       <c r="E26" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F26" s="203">
-        <v>11.158095238095235</v>
+      <c r="F26" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G26" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A27" s="145" t="s">
         <v>162</v>
       </c>
@@ -10543,14 +10540,14 @@
       <c r="E27" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F27" s="203">
-        <v>12.115555555555554</v>
+      <c r="F27" s="200">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G27" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A28" s="145" t="s">
         <v>162</v>
       </c>
@@ -10566,14 +10563,14 @@
       <c r="E28" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F28" s="202">
-        <v>7.4</v>
-      </c>
-      <c r="G28" s="190">
+      <c r="F28" s="201">
+        <v>3.8</v>
+      </c>
+      <c r="G28" s="189">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="145" t="s">
         <v>162</v>
       </c>
@@ -10589,14 +10586,14 @@
       <c r="E29" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F29" s="189">
-        <v>12.379943502824856</v>
-      </c>
-      <c r="G29" s="190">
+      <c r="F29" s="202">
+        <v>12.379943502824901</v>
+      </c>
+      <c r="G29" s="189">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A30" s="145" t="s">
         <v>162</v>
       </c>
@@ -10612,14 +10609,14 @@
       <c r="E30" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F30" s="189">
-        <v>12.072378043916389</v>
-      </c>
-      <c r="G30" s="207">
+      <c r="F30" s="202">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G30" s="198">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A31" s="145" t="s">
         <v>162</v>
       </c>
@@ -10635,14 +10632,14 @@
       <c r="E31" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F31" s="189">
-        <v>13.333333333333334</v>
-      </c>
-      <c r="G31" s="190">
+      <c r="F31" s="202">
+        <v>6.6666666666666696</v>
+      </c>
+      <c r="G31" s="189">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A32" s="145" t="s">
         <v>162</v>
       </c>
@@ -10658,14 +10655,14 @@
       <c r="E32" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F32" s="203">
-        <v>11.158095238095235</v>
+      <c r="F32" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G32" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -10681,14 +10678,14 @@
       <c r="E33" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F33" s="203">
-        <v>12.115555555555554</v>
+      <c r="F33" s="200">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G33" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
@@ -10704,14 +10701,14 @@
       <c r="E34" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F34" s="203">
-        <v>12.851999999999999</v>
+      <c r="F34" s="200">
+        <v>4.76</v>
       </c>
       <c r="G34" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="201" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="145" t="s">
         <v>162</v>
       </c>
@@ -10727,14 +10724,14 @@
       <c r="E35" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F35" s="203">
-        <v>13.5</v>
+      <c r="F35" s="200">
+        <v>5</v>
       </c>
       <c r="G35" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="201" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="145" t="s">
         <v>162</v>
       </c>
@@ -10750,14 +10747,14 @@
       <c r="E36" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F36" s="203">
-        <v>8.94</v>
+      <c r="F36" s="200">
+        <v>3.31111111111111</v>
       </c>
       <c r="G36" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A37" s="145" t="s">
         <v>162</v>
       </c>
@@ -10773,37 +10770,37 @@
       <c r="E37" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F37" s="203">
-        <v>4.1759999999999993</v>
+      <c r="F37" s="200">
+        <v>1.54666666666667</v>
       </c>
       <c r="G37" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="191" t="s">
+    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="192" t="s">
+      <c r="C38" s="191" t="s">
         <v>281</v>
       </c>
-      <c r="D38" s="193" t="s">
+      <c r="D38" s="192" t="s">
         <v>282</v>
       </c>
-      <c r="E38" s="194" t="s">
+      <c r="E38" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F38" s="205">
+      <c r="F38" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G38" s="194">
+      <c r="G38" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A39" s="145" t="s">
         <v>162</v>
       </c>
@@ -10819,14 +10816,14 @@
       <c r="E39" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F39" s="203">
-        <v>11.25</v>
+      <c r="F39" s="200">
+        <v>4.1666666666666696</v>
       </c>
       <c r="G39" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="145" t="s">
         <v>162</v>
       </c>
@@ -10836,89 +10833,89 @@
       <c r="C40" s="177" t="s">
         <v>291</v>
       </c>
-      <c r="D40" s="199" t="s">
+      <c r="D40" s="180" t="s">
         <v>196</v>
       </c>
       <c r="E40" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F40" s="203">
-        <v>8.9485714285714302</v>
+      <c r="F40" s="202">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G40" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B41" s="191" t="s">
+    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="192" t="s">
+      <c r="C41" s="191" t="s">
         <v>292</v>
       </c>
-      <c r="D41" s="193" t="s">
+      <c r="D41" s="192" t="s">
         <v>293</v>
       </c>
-      <c r="E41" s="194" t="s">
+      <c r="E41" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F41" s="205">
+      <c r="F41" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G41" s="194">
+      <c r="G41" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="191" t="s">
+    <row r="42" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="192" t="s">
+      <c r="C42" s="191" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="193" t="s">
+      <c r="D42" s="192" t="s">
         <v>295</v>
       </c>
-      <c r="E42" s="194" t="s">
+      <c r="E42" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F42" s="205">
+      <c r="F42" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G42" s="194">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="191" t="s">
+      <c r="G42" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="192" t="s">
+      <c r="C43" s="191" t="s">
         <v>296</v>
       </c>
-      <c r="D43" s="193" t="s">
+      <c r="D43" s="192" t="s">
         <v>297</v>
       </c>
-      <c r="E43" s="194" t="s">
+      <c r="E43" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F43" s="205">
+      <c r="F43" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G43" s="194">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="G43" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="145" t="s">
         <v>162</v>
       </c>
@@ -10934,21 +10931,21 @@
       <c r="E44" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F44" s="203">
-        <v>11.158095238095235</v>
+      <c r="F44" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G44" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B45" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C45" s="177" t="s">
+      <c r="C45" s="199" t="s">
         <v>650</v>
       </c>
       <c r="D45" s="180" t="s">
@@ -10957,14 +10954,14 @@
       <c r="E45" s="186" t="s">
         <v>633</v>
       </c>
-      <c r="F45" s="203">
-        <v>8.16</v>
+      <c r="F45" s="200">
+        <v>4.8</v>
       </c>
       <c r="G45" s="186">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="145" t="s">
         <v>162</v>
       </c>
@@ -10980,14 +10977,14 @@
       <c r="E46" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F46" s="189">
+      <c r="F46" s="202">
         <v>3.9080000000000004</v>
       </c>
       <c r="G46" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="145" t="s">
         <v>162</v>
       </c>
@@ -11003,14 +11000,14 @@
       <c r="E47" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F47" s="203">
-        <v>10.275555555555552</v>
+      <c r="F47" s="200">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G47" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="145" t="s">
         <v>162</v>
       </c>
@@ -11026,14 +11023,14 @@
       <c r="E48" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F48" s="203">
-        <v>10.275555555555552</v>
+      <c r="F48" s="200">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G48" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="145" t="s">
         <v>162</v>
       </c>
@@ -11049,14 +11046,14 @@
       <c r="E49" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F49" s="203">
-        <v>3.9439999999999995</v>
+      <c r="F49" s="200">
+        <v>2.3199999999999998</v>
       </c>
       <c r="G49" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A50" s="145" t="s">
         <v>162</v>
       </c>
@@ -11072,14 +11069,14 @@
       <c r="E50" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F50" s="203">
-        <v>12.5138888888889</v>
+      <c r="F50" s="200">
+        <v>4.63657407407407</v>
       </c>
       <c r="G50" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="145" t="s">
         <v>162</v>
       </c>
@@ -11089,89 +11086,89 @@
       <c r="C51" s="177" t="s">
         <v>324</v>
       </c>
-      <c r="D51" s="199" t="s">
+      <c r="D51" s="180" t="s">
         <v>325</v>
       </c>
       <c r="E51" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F51" s="203">
-        <v>8.9485714285714266</v>
-      </c>
-      <c r="G51" s="190">
+      <c r="F51" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G51" s="189">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="191" t="s">
+    <row r="52" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C52" s="192" t="s">
+      <c r="C52" s="191" t="s">
         <v>328</v>
       </c>
-      <c r="D52" s="193" t="s">
+      <c r="D52" s="192" t="s">
         <v>329</v>
       </c>
-      <c r="E52" s="194" t="s">
+      <c r="E52" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F52" s="205">
+      <c r="F52" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G52" s="194">
+      <c r="G52" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="191" t="s">
+    <row r="53" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="192" t="s">
+      <c r="C53" s="191" t="s">
         <v>330</v>
       </c>
-      <c r="D53" s="193" t="s">
+      <c r="D53" s="192" t="s">
         <v>331</v>
       </c>
-      <c r="E53" s="194" t="s">
+      <c r="E53" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F53" s="205">
+      <c r="F53" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G53" s="194">
+      <c r="G53" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" s="191" t="s">
+    <row r="54" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C54" s="192" t="s">
+      <c r="C54" s="191" t="s">
         <v>334</v>
       </c>
-      <c r="D54" s="193" t="s">
+      <c r="D54" s="192" t="s">
         <v>335</v>
       </c>
-      <c r="E54" s="194" t="s">
+      <c r="E54" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F54" s="205">
+      <c r="F54" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G54" s="194">
+      <c r="G54" s="193">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A55" s="145" t="s">
         <v>162</v>
       </c>
@@ -11187,14 +11184,14 @@
       <c r="E55" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F55" s="203">
-        <v>11.158095238095235</v>
+      <c r="F55" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G55" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A56" s="145" t="s">
         <v>162</v>
       </c>
@@ -11210,14 +11207,14 @@
       <c r="E56" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F56" s="203">
-        <v>12.115555555555554</v>
+      <c r="F56" s="200">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G56" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A57" s="145" t="s">
         <v>162</v>
       </c>
@@ -11233,14 +11230,14 @@
       <c r="E57" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F57" s="203">
-        <v>12.851999999999999</v>
+      <c r="F57" s="200">
+        <v>4.76</v>
       </c>
       <c r="G57" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A58" s="145" t="s">
         <v>162</v>
       </c>
@@ -11256,14 +11253,14 @@
       <c r="E58" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F58" s="203">
-        <v>13.5</v>
+      <c r="F58" s="200">
+        <v>5</v>
       </c>
       <c r="G58" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A59" s="145" t="s">
         <v>162</v>
       </c>
@@ -11279,14 +11276,14 @@
       <c r="E59" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F59" s="203">
-        <v>8.94</v>
+      <c r="F59" s="200">
+        <v>3.31111111111111</v>
       </c>
       <c r="G59" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A60" s="145" t="s">
         <v>162</v>
       </c>
@@ -11302,37 +11299,37 @@
       <c r="E60" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F60" s="203">
-        <v>4.1759999999999993</v>
+      <c r="F60" s="200">
+        <v>1.54666666666667</v>
       </c>
       <c r="G60" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="191" t="s">
+    <row r="61" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C61" s="192" t="s">
+      <c r="C61" s="191" t="s">
         <v>352</v>
       </c>
-      <c r="D61" s="193" t="s">
+      <c r="D61" s="192" t="s">
         <v>353</v>
       </c>
-      <c r="E61" s="194" t="s">
+      <c r="E61" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F61" s="205">
+      <c r="F61" s="196">
         <v>5.5</v>
       </c>
-      <c r="G61" s="194">
+      <c r="G61" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A62" s="145" t="s">
         <v>162</v>
       </c>
@@ -11348,14 +11345,14 @@
       <c r="E62" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F62" s="203">
-        <v>11.25</v>
+      <c r="F62" s="200">
+        <v>4.1666666666666696</v>
       </c>
       <c r="G62" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A63" s="145" t="s">
         <v>162</v>
       </c>
@@ -11371,14 +11368,14 @@
       <c r="E63" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F63" s="203">
-        <v>11.158095238095235</v>
+      <c r="F63" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G63" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A64" s="145" t="s">
         <v>162</v>
       </c>
@@ -11394,14 +11391,14 @@
       <c r="E64" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F64" s="203">
-        <v>12.115555555555554</v>
+      <c r="F64" s="200">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G64" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A65" s="145" t="s">
         <v>162</v>
       </c>
@@ -11417,14 +11414,14 @@
       <c r="E65" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F65" s="203">
-        <v>12.851999999999999</v>
+      <c r="F65" s="200">
+        <v>4.76</v>
       </c>
       <c r="G65" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A66" s="145" t="s">
         <v>162</v>
       </c>
@@ -11440,14 +11437,14 @@
       <c r="E66" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F66" s="203">
-        <v>13.5</v>
+      <c r="F66" s="200">
+        <v>5</v>
       </c>
       <c r="G66" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="145" t="s">
         <v>162</v>
       </c>
@@ -11463,14 +11460,14 @@
       <c r="E67" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F67" s="203">
-        <v>8.94</v>
+      <c r="F67" s="200">
+        <v>3.31111111111111</v>
       </c>
       <c r="G67" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A68" s="145" t="s">
         <v>162</v>
       </c>
@@ -11486,37 +11483,37 @@
       <c r="E68" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F68" s="203">
-        <v>4.1759999999999993</v>
+      <c r="F68" s="200">
+        <v>1.54666666666667</v>
       </c>
       <c r="G68" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B69" s="191" t="s">
+    <row r="69" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="192" t="s">
+      <c r="C69" s="191" t="s">
         <v>375</v>
       </c>
-      <c r="D69" s="193" t="s">
+      <c r="D69" s="192" t="s">
         <v>376</v>
       </c>
-      <c r="E69" s="194" t="s">
+      <c r="E69" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F69" s="205">
+      <c r="F69" s="196">
         <v>5.5</v>
       </c>
-      <c r="G69" s="194">
+      <c r="G69" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A70" s="145" t="s">
         <v>162</v>
       </c>
@@ -11532,14 +11529,14 @@
       <c r="E70" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F70" s="203">
-        <v>11.25</v>
+      <c r="F70" s="200">
+        <v>4.1666666666666696</v>
       </c>
       <c r="G70" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A71" s="145" t="s">
         <v>162</v>
       </c>
@@ -11555,14 +11552,14 @@
       <c r="E71" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F71" s="203">
+      <c r="F71" s="200">
         <v>1.0311111111111111</v>
       </c>
       <c r="G71" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A72" s="145" t="s">
         <v>162</v>
       </c>
@@ -11578,14 +11575,14 @@
       <c r="E72" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F72" s="203">
-        <v>11.158095238095235</v>
+      <c r="F72" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G72" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A73" s="145" t="s">
         <v>162</v>
       </c>
@@ -11601,60 +11598,60 @@
       <c r="E73" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F73" s="203">
-        <v>12.5138888888889</v>
+      <c r="F73" s="200">
+        <v>4.63657407407407</v>
       </c>
       <c r="G73" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B74" s="191" t="s">
+    <row r="74" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C74" s="192" t="s">
+      <c r="C74" s="191" t="s">
         <v>393</v>
       </c>
-      <c r="D74" s="193" t="s">
+      <c r="D74" s="192" t="s">
         <v>394</v>
       </c>
-      <c r="E74" s="194" t="s">
+      <c r="E74" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F74" s="205">
+      <c r="F74" s="196">
         <v>5.5</v>
       </c>
-      <c r="G74" s="194">
+      <c r="G74" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" s="191" t="s">
+    <row r="75" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C75" s="192" t="s">
+      <c r="C75" s="191" t="s">
         <v>395</v>
       </c>
-      <c r="D75" s="193" t="s">
+      <c r="D75" s="192" t="s">
         <v>396</v>
       </c>
-      <c r="E75" s="194" t="s">
+      <c r="E75" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F75" s="205">
+      <c r="F75" s="196">
         <v>5.5</v>
       </c>
-      <c r="G75" s="194">
+      <c r="G75" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="145" t="s">
         <v>162</v>
       </c>
@@ -11670,14 +11667,14 @@
       <c r="E76" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F76" s="203">
-        <v>11.158095238095235</v>
+      <c r="F76" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G76" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A77" s="145" t="s">
         <v>162</v>
       </c>
@@ -11693,60 +11690,60 @@
       <c r="E77" s="186" t="s">
         <v>635</v>
       </c>
-      <c r="F77" s="203">
+      <c r="F77" s="200">
         <v>3</v>
       </c>
       <c r="G77" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B78" s="191" t="s">
+    <row r="78" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="192" t="s">
+      <c r="C78" s="191" t="s">
         <v>403</v>
       </c>
-      <c r="D78" s="193" t="s">
+      <c r="D78" s="192" t="s">
         <v>404</v>
       </c>
-      <c r="E78" s="194" t="s">
+      <c r="E78" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F78" s="205">
+      <c r="F78" s="196">
         <v>15</v>
       </c>
-      <c r="G78" s="194">
+      <c r="G78" s="193">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="191" t="s">
+    <row r="79" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C79" s="192" t="s">
+      <c r="C79" s="191" t="s">
         <v>407</v>
       </c>
-      <c r="D79" s="193" t="s">
+      <c r="D79" s="192" t="s">
         <v>408</v>
       </c>
-      <c r="E79" s="194" t="s">
+      <c r="E79" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F79" s="205">
+      <c r="F79" s="196">
         <v>12.166666666666666</v>
       </c>
-      <c r="G79" s="194">
+      <c r="G79" s="193">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A80" s="145" t="s">
         <v>162</v>
       </c>
@@ -11762,8 +11759,8 @@
       <c r="E80" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F80" s="203">
-        <v>11.158095238095235</v>
+      <c r="F80" s="200">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G80" s="186">
         <v>3</v>
@@ -11789,10 +11786,10 @@
     <col min="4" max="4" width="29" style="147" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="150" customWidth="1"/>
     <col min="6" max="7" width="13.875" style="150" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="204"/>
+    <col min="8" max="16384" width="8.875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="201" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -11811,11 +11808,11 @@
       <c r="F1" s="182" t="s">
         <v>473</v>
       </c>
-      <c r="G1" s="206" t="s">
+      <c r="G1" s="197" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -11831,14 +11828,14 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="183">
+      <c r="F2" s="203">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="149">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -11854,14 +11851,14 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="183">
-        <v>12.115555555555554</v>
+      <c r="F3" s="203">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G3" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="145" t="s">
         <v>162</v>
       </c>
@@ -11877,14 +11874,14 @@
       <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="183">
-        <v>7.4</v>
+      <c r="F4" s="203">
+        <v>3.8</v>
       </c>
       <c r="G4" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -11900,14 +11897,14 @@
       <c r="E5" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F5" s="183">
-        <v>7.4</v>
+      <c r="F5" s="203">
+        <v>3.8</v>
       </c>
       <c r="G5" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -11923,14 +11920,14 @@
       <c r="E6" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F6" s="183">
-        <v>12.379943502824856</v>
+      <c r="F6" s="203">
+        <v>12.379943502824901</v>
       </c>
       <c r="G6" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -11946,14 +11943,14 @@
       <c r="E7" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F7" s="183">
-        <v>13.333333333333334</v>
+      <c r="F7" s="203">
+        <v>6.666666666666667</v>
       </c>
       <c r="G7" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="145" t="s">
         <v>162</v>
       </c>
@@ -11969,14 +11966,14 @@
       <c r="E8" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F8" s="183">
-        <v>11.158095238095235</v>
+      <c r="F8" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G8" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="145" t="s">
         <v>162</v>
       </c>
@@ -11992,14 +11989,14 @@
       <c r="E9" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F9" s="183">
-        <v>12.115555555555554</v>
+      <c r="F9" s="203">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G9" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -12015,14 +12012,14 @@
       <c r="E10" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F10" s="183">
-        <v>7.4</v>
+      <c r="F10" s="203">
+        <v>3.8</v>
       </c>
       <c r="G10" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="145" t="s">
         <v>162</v>
       </c>
@@ -12038,14 +12035,14 @@
       <c r="E11" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F11" s="183">
-        <v>12.379943502824856</v>
+      <c r="F11" s="203">
+        <v>12.379943502824901</v>
       </c>
       <c r="G11" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="145" t="s">
         <v>162</v>
       </c>
@@ -12061,14 +12058,14 @@
       <c r="E12" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F12" s="183">
+      <c r="F12" s="203">
         <v>12.072378043916389</v>
       </c>
       <c r="G12" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="145" t="s">
         <v>162</v>
       </c>
@@ -12084,14 +12081,14 @@
       <c r="E13" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F13" s="183">
+      <c r="F13" s="203">
         <v>12.072378043916389</v>
       </c>
       <c r="G13" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="201" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -12107,14 +12104,14 @@
       <c r="E14" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F14" s="183">
-        <v>13.333333333333334</v>
+      <c r="F14" s="203">
+        <v>6.666666666666667</v>
       </c>
       <c r="G14" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -12130,14 +12127,14 @@
       <c r="E15" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F15" s="183">
-        <v>11.158095238095235</v>
+      <c r="F15" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G15" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
@@ -12147,66 +12144,66 @@
       <c r="C16" s="177" t="s">
         <v>195</v>
       </c>
-      <c r="D16" s="199" t="s">
+      <c r="D16" s="180" t="s">
         <v>196</v>
       </c>
       <c r="E16" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F16" s="183">
-        <v>11.268571428571425</v>
+      <c r="F16" s="203">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G16" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="191" t="s">
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C17" s="192" t="s">
+      <c r="C17" s="191" t="s">
         <v>441</v>
       </c>
-      <c r="D17" s="193" t="s">
+      <c r="D17" s="192" t="s">
         <v>442</v>
       </c>
-      <c r="E17" s="194" t="s">
+      <c r="E17" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F17" s="195">
+      <c r="F17" s="194">
         <v>4.666666666666667</v>
       </c>
-      <c r="G17" s="196">
+      <c r="G17" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="191" t="s">
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="191" t="s">
         <v>199</v>
       </c>
-      <c r="D18" s="193" t="s">
+      <c r="D18" s="192" t="s">
         <v>200</v>
       </c>
-      <c r="E18" s="194" t="s">
+      <c r="E18" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F18" s="195">
+      <c r="F18" s="194">
         <v>12.166666666666666</v>
       </c>
-      <c r="G18" s="196">
+      <c r="G18" s="195">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="145" t="s">
         <v>162</v>
       </c>
@@ -12222,14 +12219,14 @@
       <c r="E19" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F19" s="183">
-        <v>11.158095238095235</v>
+      <c r="F19" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G19" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="145" t="s">
         <v>162</v>
       </c>
@@ -12245,14 +12242,14 @@
       <c r="E20" s="186" t="s">
         <v>633</v>
       </c>
-      <c r="F20" s="179">
-        <v>8.16</v>
+      <c r="F20" s="204">
+        <v>4.8</v>
       </c>
       <c r="G20" s="176">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A21" s="145" t="s">
         <v>162</v>
       </c>
@@ -12268,14 +12265,14 @@
       <c r="E21" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F21" s="183">
+      <c r="F21" s="203">
         <v>3.9080000000000004</v>
       </c>
       <c r="G21" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="145" t="s">
         <v>162</v>
       </c>
@@ -12291,14 +12288,14 @@
       <c r="E22" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F22" s="183">
-        <v>10.275555555555552</v>
+      <c r="F22" s="203">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G22" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A23" s="145" t="s">
         <v>162</v>
       </c>
@@ -12314,14 +12311,14 @@
       <c r="E23" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F23" s="183">
-        <v>10.275555555555552</v>
+      <c r="F23" s="203">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G23" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A24" s="145" t="s">
         <v>162</v>
       </c>
@@ -12337,14 +12334,14 @@
       <c r="E24" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F24" s="183">
-        <v>3.9439999999999995</v>
+      <c r="F24" s="203">
+        <v>2.3199999999999998</v>
       </c>
       <c r="G24" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A25" s="145" t="s">
         <v>162</v>
       </c>
@@ -12360,14 +12357,14 @@
       <c r="E25" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F25" s="183">
-        <v>12.513888888888888</v>
+      <c r="F25" s="203">
+        <v>4.63657407407407</v>
       </c>
       <c r="G25" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -12377,112 +12374,112 @@
       <c r="C26" s="177" t="s">
         <v>324</v>
       </c>
-      <c r="D26" s="199" t="s">
+      <c r="D26" s="180" t="s">
         <v>325</v>
       </c>
       <c r="E26" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F26" s="183">
-        <v>11.268571428571425</v>
+      <c r="F26" s="203">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G26" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" s="191" t="s">
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C27" s="192" t="s">
+      <c r="C27" s="191" t="s">
         <v>459</v>
       </c>
-      <c r="D27" s="193" t="s">
+      <c r="D27" s="192" t="s">
         <v>460</v>
       </c>
-      <c r="E27" s="194" t="s">
+      <c r="E27" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F27" s="195">
+      <c r="F27" s="194">
         <v>4.666666666666667</v>
       </c>
-      <c r="G27" s="196">
+      <c r="G27" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" s="191" t="s">
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C28" s="192" t="s">
+      <c r="C28" s="191" t="s">
         <v>237</v>
       </c>
-      <c r="D28" s="193" t="s">
+      <c r="D28" s="192" t="s">
         <v>238</v>
       </c>
-      <c r="E28" s="194" t="s">
+      <c r="E28" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F28" s="195">
+      <c r="F28" s="194">
         <v>4.666666666666667</v>
       </c>
-      <c r="G28" s="196">
+      <c r="G28" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B29" s="191" t="s">
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C29" s="192" t="s">
+      <c r="C29" s="191" t="s">
         <v>328</v>
       </c>
-      <c r="D29" s="193" t="s">
+      <c r="D29" s="192" t="s">
         <v>329</v>
       </c>
-      <c r="E29" s="194" t="s">
+      <c r="E29" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F29" s="195">
+      <c r="F29" s="194">
         <v>4.666666666666667</v>
       </c>
-      <c r="G29" s="196">
+      <c r="G29" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B30" s="191" t="s">
+    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C30" s="192" t="s">
+      <c r="C30" s="191" t="s">
         <v>241</v>
       </c>
-      <c r="D30" s="193" t="s">
+      <c r="D30" s="192" t="s">
         <v>242</v>
       </c>
-      <c r="E30" s="194" t="s">
+      <c r="E30" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F30" s="195">
+      <c r="F30" s="194">
         <v>12.166666666666666</v>
       </c>
-      <c r="G30" s="196">
+      <c r="G30" s="195">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A31" s="145" t="s">
         <v>162</v>
       </c>
@@ -12498,14 +12495,14 @@
       <c r="E31" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F31" s="183">
-        <v>11.158095238095235</v>
+      <c r="F31" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G31" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A32" s="145" t="s">
         <v>162</v>
       </c>
@@ -12521,14 +12518,14 @@
       <c r="E32" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F32" s="183">
-        <v>12.115555555555554</v>
+      <c r="F32" s="203">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G32" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -12544,14 +12541,14 @@
       <c r="E33" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F33" s="183">
-        <v>12.851999999999999</v>
+      <c r="F33" s="203">
+        <v>4.76</v>
       </c>
       <c r="G33" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
@@ -12567,14 +12564,14 @@
       <c r="E34" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F34" s="183">
-        <v>13.5</v>
+      <c r="F34" s="203">
+        <v>5</v>
       </c>
       <c r="G34" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A35" s="145" t="s">
         <v>162</v>
       </c>
@@ -12590,14 +12587,14 @@
       <c r="E35" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F35" s="183">
-        <v>8.94</v>
+      <c r="F35" s="203">
+        <v>3.31111111111111</v>
       </c>
       <c r="G35" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A36" s="145" t="s">
         <v>162</v>
       </c>
@@ -12613,37 +12610,37 @@
       <c r="E36" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F36" s="183">
-        <v>4.1759999999999993</v>
+      <c r="F36" s="203">
+        <v>1.54666666666667</v>
       </c>
       <c r="G36" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B37" s="191" t="s">
+    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C37" s="192" t="s">
+      <c r="C37" s="191" t="s">
         <v>352</v>
       </c>
-      <c r="D37" s="193" t="s">
+      <c r="D37" s="192" t="s">
         <v>353</v>
       </c>
-      <c r="E37" s="194" t="s">
+      <c r="E37" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F37" s="195">
+      <c r="F37" s="194">
         <v>5.5</v>
       </c>
-      <c r="G37" s="196">
+      <c r="G37" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A38" s="145" t="s">
         <v>162</v>
       </c>
@@ -12659,14 +12656,14 @@
       <c r="E38" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F38" s="183">
-        <v>11.25</v>
+      <c r="F38" s="203">
+        <v>4.1666666666666696</v>
       </c>
       <c r="G38" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A39" s="145" t="s">
         <v>162</v>
       </c>
@@ -12682,14 +12679,14 @@
       <c r="E39" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F39" s="183">
-        <v>11.158095238095235</v>
+      <c r="F39" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G39" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="145" t="s">
         <v>162</v>
       </c>
@@ -12705,14 +12702,14 @@
       <c r="E40" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F40" s="183">
-        <v>12.115555555555554</v>
+      <c r="F40" s="203">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G40" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="145" t="s">
         <v>162</v>
       </c>
@@ -12728,14 +12725,14 @@
       <c r="E41" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F41" s="183">
-        <v>12.851999999999999</v>
+      <c r="F41" s="203">
+        <v>4.76</v>
       </c>
       <c r="G41" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="145" t="s">
         <v>162</v>
       </c>
@@ -12751,14 +12748,14 @@
       <c r="E42" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F42" s="183">
-        <v>13.5</v>
+      <c r="F42" s="203">
+        <v>5</v>
       </c>
       <c r="G42" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="145" t="s">
         <v>162</v>
       </c>
@@ -12774,14 +12771,14 @@
       <c r="E43" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F43" s="183">
-        <v>8.94</v>
+      <c r="F43" s="203">
+        <v>3.31111111111111</v>
       </c>
       <c r="G43" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="145" t="s">
         <v>162</v>
       </c>
@@ -12797,37 +12794,37 @@
       <c r="E44" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F44" s="183">
-        <v>4.1759999999999993</v>
+      <c r="F44" s="203">
+        <v>1.54666666666667</v>
       </c>
       <c r="G44" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B45" s="191" t="s">
+    <row r="45" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C45" s="192" t="s">
+      <c r="C45" s="191" t="s">
         <v>375</v>
       </c>
-      <c r="D45" s="193" t="s">
+      <c r="D45" s="192" t="s">
         <v>376</v>
       </c>
-      <c r="E45" s="194" t="s">
+      <c r="E45" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F45" s="195">
+      <c r="F45" s="194">
         <v>5.5</v>
       </c>
-      <c r="G45" s="196">
+      <c r="G45" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="145" t="s">
         <v>162</v>
       </c>
@@ -12843,14 +12840,14 @@
       <c r="E46" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F46" s="183">
-        <v>11.25</v>
+      <c r="F46" s="203">
+        <v>4.1666666666666696</v>
       </c>
       <c r="G46" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="145" t="s">
         <v>162</v>
       </c>
@@ -12860,20 +12857,20 @@
       <c r="C47" s="177" t="s">
         <v>385</v>
       </c>
-      <c r="D47" s="199" t="s">
+      <c r="D47" s="180" t="s">
         <v>386</v>
       </c>
       <c r="E47" s="186" t="s">
         <v>636</v>
       </c>
-      <c r="F47" s="183">
+      <c r="F47" s="203">
         <v>1.0311111111111111</v>
       </c>
       <c r="G47" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="145" t="s">
         <v>162</v>
       </c>
@@ -12889,14 +12886,14 @@
       <c r="E48" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F48" s="183">
-        <v>11.158095238095235</v>
+      <c r="F48" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G48" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="145" t="s">
         <v>162</v>
       </c>
@@ -12912,60 +12909,60 @@
       <c r="E49" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F49" s="183">
-        <v>12.513888888888888</v>
+      <c r="F49" s="203">
+        <v>4.63657407407407</v>
       </c>
       <c r="G49" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B50" s="191" t="s">
+    <row r="50" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C50" s="192" t="s">
+      <c r="C50" s="191" t="s">
         <v>393</v>
       </c>
-      <c r="D50" s="193" t="s">
+      <c r="D50" s="192" t="s">
         <v>394</v>
       </c>
-      <c r="E50" s="194" t="s">
+      <c r="E50" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F50" s="195">
+      <c r="F50" s="194">
         <v>5.5</v>
       </c>
-      <c r="G50" s="196">
+      <c r="G50" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="191" t="s">
+    <row r="51" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C51" s="192" t="s">
+      <c r="C51" s="191" t="s">
         <v>395</v>
       </c>
-      <c r="D51" s="193" t="s">
+      <c r="D51" s="192" t="s">
         <v>396</v>
       </c>
-      <c r="E51" s="194" t="s">
+      <c r="E51" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F51" s="195">
+      <c r="F51" s="194">
         <v>5.5</v>
       </c>
-      <c r="G51" s="196">
+      <c r="G51" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="145" t="s">
         <v>162</v>
       </c>
@@ -12981,14 +12978,14 @@
       <c r="E52" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F52" s="183">
-        <v>11.158095238095235</v>
+      <c r="F52" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G52" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A53" s="145" t="s">
         <v>162</v>
       </c>
@@ -13004,60 +13001,60 @@
       <c r="E53" s="186" t="s">
         <v>635</v>
       </c>
-      <c r="F53" s="183">
+      <c r="F53" s="203">
         <v>3</v>
       </c>
       <c r="G53" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" s="191" t="s">
+    <row r="54" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C54" s="192" t="s">
+      <c r="C54" s="191" t="s">
         <v>403</v>
       </c>
-      <c r="D54" s="193" t="s">
+      <c r="D54" s="192" t="s">
         <v>404</v>
       </c>
-      <c r="E54" s="194" t="s">
+      <c r="E54" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F54" s="195">
+      <c r="F54" s="194">
         <v>15</v>
       </c>
-      <c r="G54" s="196">
+      <c r="G54" s="195">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="191" t="s">
-        <v>162</v>
-      </c>
-      <c r="B55" s="191" t="s">
+    <row r="55" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C55" s="192" t="s">
+      <c r="C55" s="191" t="s">
         <v>407</v>
       </c>
-      <c r="D55" s="193" t="s">
+      <c r="D55" s="192" t="s">
         <v>408</v>
       </c>
-      <c r="E55" s="194" t="s">
+      <c r="E55" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F55" s="195">
+      <c r="F55" s="194">
         <v>12.166666666666666</v>
       </c>
-      <c r="G55" s="196">
+      <c r="G55" s="195">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="201" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A56" s="145" t="s">
         <v>162</v>
       </c>
@@ -13073,8 +13070,8 @@
       <c r="E56" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F56" s="183">
-        <v>11.158095238095235</v>
+      <c r="F56" s="203">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G56" s="149">
         <v>3</v>

--- a/doc/SourceData2.xlsx
+++ b/doc/SourceData2.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YH.CHIU\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725A7D44-79A0-4843-A795-E76F5B203E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51117AF5-F8C8-47F5-AB85-278C3C89F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
   <sheets>
     <sheet name="黃光CT總表" sheetId="2" r:id="rId1"/>
     <sheet name="設備加工上限" sheetId="5" r:id="rId2"/>
-    <sheet name="2代-03SEC CT (2+2)" sheetId="6" r:id="rId3"/>
-    <sheet name="2代-01SG CT (1+1)" sheetId="7" r:id="rId4"/>
+    <sheet name="2代-03SEC CT (2+2)" sheetId="8" r:id="rId3"/>
+    <sheet name="2代-01SG CT (1+1)" sheetId="9" r:id="rId4"/>
     <sheet name="03SEC CT (2+2)" sheetId="3" r:id="rId5"/>
     <sheet name="01SG CT (1+1)" sheetId="4" r:id="rId6"/>
   </sheets>
@@ -28,9 +28,14 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
+    <definedName name="___________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="___________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_________DAT1">#REF!</definedName>
     <definedName name="_________DAT10">#REF!</definedName>
@@ -54,6 +59,8 @@
     <definedName name="_________DAT7">#REF!</definedName>
     <definedName name="_________DAT8">#REF!</definedName>
     <definedName name="_________DAT9">#REF!</definedName>
+    <definedName name="_________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="________DAT23">#REF!</definedName>
     <definedName name="________DAT24">#REF!</definedName>
@@ -65,34 +72,50 @@
     <definedName name="_______DAT25">#REF!</definedName>
     <definedName name="_______DAT26">#REF!</definedName>
     <definedName name="_______DAT27">#REF!</definedName>
+    <definedName name="_______gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_______gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_______gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="______DAT23">#REF!</definedName>
     <definedName name="______DAT24">#REF!</definedName>
     <definedName name="______DAT25">#REF!</definedName>
     <definedName name="______DAT26">#REF!</definedName>
     <definedName name="______DAT27">#REF!</definedName>
+    <definedName name="______gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="______gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="______gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_____AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_____AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_____AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_____DAT23">#REF!</definedName>
     <definedName name="_____DAT24">#REF!</definedName>
     <definedName name="_____DAT25">#REF!</definedName>
     <definedName name="_____DAT26">#REF!</definedName>
     <definedName name="_____DAT27">#REF!</definedName>
+    <definedName name="_____gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_____gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_____gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="____AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="____AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="____AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="____DAT23">#REF!</definedName>
     <definedName name="____DAT24">#REF!</definedName>
     <definedName name="____DAT25">#REF!</definedName>
     <definedName name="____DAT26">#REF!</definedName>
     <definedName name="____DAT27">#REF!</definedName>
+    <definedName name="___AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="___AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="___AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="___DAT23">#REF!</definedName>
     <definedName name="___DAT24">#REF!</definedName>
     <definedName name="___DAT25">#REF!</definedName>
     <definedName name="___DAT26">#REF!</definedName>
     <definedName name="___DAT27">#REF!</definedName>
+    <definedName name="___gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="___gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__1dg1_">#REF!</definedName>
+    <definedName name="__AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="__AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="__AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="__DAT23">#REF!</definedName>
     <definedName name="__DAT24">#REF!</definedName>
@@ -148,12 +171,16 @@
     <definedName name="__DAT74">#REF!</definedName>
     <definedName name="__DAT75">#REF!</definedName>
     <definedName name="__dat88">#REF!</definedName>
+    <definedName name="__gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__IntlFixup" hidden="1">TRUE</definedName>
     <definedName name="__SPS1">#REF!</definedName>
     <definedName name="__SPS2">#REF!</definedName>
     <definedName name="__STD12">#REF!</definedName>
     <definedName name="_1dg1_">#REF!</definedName>
+    <definedName name="_AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_DAT1">#REF!</definedName>
     <definedName name="_DAT100">#REF!</definedName>
@@ -213,11 +240,13 @@
     <definedName name="_Fill" hidden="1">[1]DETAILS!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'01SG CT (1+1)'!$A$1:$AF$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03SEC CT (2+2)'!$A$1:$AE$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2代-01SG CT (1+1)'!$A$1:$G$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2代-03SEC CT (2+2)'!$A$1:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2代-01SG CT (1+1)'!$A$1:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2代-03SEC CT (2+2)'!$A$1:$G$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">設備加工上限!$A$1:$F$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">黃光CT總表!$B$9:$R$55</definedName>
     <definedName name="_xlnm._FilterDatabase" hidden="1">[2]分類表!$A$18:$B$30</definedName>
+    <definedName name="_gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_ok3">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
@@ -232,11 +261,19 @@
     <definedName name="_查詢1">#REF!</definedName>
     <definedName name="aaa">#REF!</definedName>
     <definedName name="aaaa">#REF!</definedName>
+    <definedName name="AAAAA" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAA" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAAAA" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAAAAAAAAV" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAAAAAAAAV" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAAAAAAAAAAV" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AABB">#REF!</definedName>
     <definedName name="aaddd">#REF!</definedName>
+    <definedName name="AAZ" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAZ" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAZ" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ab" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ab" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="ab" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AccessDatabase" hidden="1">"E:\JOB\21日提供資料\Rolling Forecast\Rolling2006002.mdb"</definedName>
     <definedName name="Apr_SAP_saving">#REF!</definedName>
@@ -244,7 +281,11 @@
     <definedName name="asb">#REF!</definedName>
     <definedName name="ASD">#REF!</definedName>
     <definedName name="AVD">#REF!</definedName>
+    <definedName name="ax" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ax" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="ax" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AZ" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AZ" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AZ" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="B">#REF!</definedName>
     <definedName name="ballast">#REF!</definedName>
@@ -285,6 +326,8 @@
     <definedName name="da">#REF!</definedName>
     <definedName name="daqe">#REF!</definedName>
     <definedName name="DATA">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
+    <definedName name="DATA1" localSheetId="3">#REF!</definedName>
+    <definedName name="DATA1" localSheetId="2">#REF!</definedName>
     <definedName name="DATA1">#REF!</definedName>
     <definedName name="DATA10">#REF!</definedName>
     <definedName name="DATA11">#REF!</definedName>
@@ -377,6 +420,8 @@
     <definedName name="detail">#REF!</definedName>
     <definedName name="df">#REF!</definedName>
     <definedName name="DG">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
+    <definedName name="DGA" localSheetId="3">#REF!</definedName>
+    <definedName name="DGA" localSheetId="2">#REF!</definedName>
     <definedName name="DGA">#REF!</definedName>
     <definedName name="dgg">#REF!</definedName>
     <definedName name="DIIP3ST">#REF!</definedName>
@@ -393,12 +438,16 @@
     <definedName name="eeee">#REF!</definedName>
     <definedName name="END">#REF!</definedName>
     <definedName name="EP_DATA">#REF!</definedName>
+    <definedName name="erty" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="erty" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="erty" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="fd">#REF!</definedName>
     <definedName name="ff">#REF!</definedName>
     <definedName name="fhg">#REF!</definedName>
     <definedName name="fi">#REF!</definedName>
     <definedName name="filter" hidden="1">[4]分類表!$A$18:$B$30</definedName>
+    <definedName name="Format" localSheetId="3">#REF!</definedName>
+    <definedName name="Format" localSheetId="2">#REF!</definedName>
     <definedName name="Format">#REF!</definedName>
     <definedName name="Format_MSBU" hidden="1">[1]DETAILS!#REF!</definedName>
     <definedName name="gg">#REF!</definedName>
@@ -417,6 +466,8 @@
     <definedName name="HKG">#REF!</definedName>
     <definedName name="HPQ">#REF!</definedName>
     <definedName name="HTML_CodePage" hidden="1">950</definedName>
+    <definedName name="HTML_Control" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="HTML_Control" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="HTML_Control" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="HTML_Description" hidden="1">""</definedName>
     <definedName name="HTML_Email" hidden="1">""</definedName>
@@ -512,6 +563,8 @@
     <definedName name="ps">#REF!</definedName>
     <definedName name="PSBG">#REF!</definedName>
     <definedName name="PSBG1">#REF!</definedName>
+    <definedName name="PSD20161T" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="PSD20161T" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="PSD20161T" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="q">#REF!</definedName>
     <definedName name="RawData">#REF!</definedName>
@@ -524,12 +577,20 @@
     <definedName name="Revised_ISR_Date">#REF!</definedName>
     <definedName name="Revision_Level">#REF!</definedName>
     <definedName name="rr">#REF!</definedName>
+    <definedName name="RT2C" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="RT2C" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="RT2C" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="s">#REF!</definedName>
     <definedName name="SALMIN">[5]TT!$U$21</definedName>
     <definedName name="SALMINDF">[5]TT!$U$20</definedName>
+    <definedName name="Sample_Size" localSheetId="3">#REF!</definedName>
+    <definedName name="Sample_Size" localSheetId="2">#REF!</definedName>
     <definedName name="Sample_Size">#REF!</definedName>
+    <definedName name="SAV" localSheetId="3">#REF!</definedName>
+    <definedName name="SAV" localSheetId="2">#REF!</definedName>
     <definedName name="SAV">#REF!</definedName>
+    <definedName name="SCP" localSheetId="3">#REF!</definedName>
+    <definedName name="SCP" localSheetId="2">#REF!</definedName>
     <definedName name="SCP">#REF!</definedName>
     <definedName name="SDA">#REF!</definedName>
     <definedName name="SEM">#REF!</definedName>
@@ -638,6 +699,8 @@
     <definedName name="tooling">#REF!</definedName>
     <definedName name="Trend_No">#REF!</definedName>
     <definedName name="Trial">#REF!</definedName>
+    <definedName name="tttt" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="tttt" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="tttt" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="TW">#REF!</definedName>
     <definedName name="TWA">#REF!</definedName>
@@ -662,41 +725,69 @@
     <definedName name="VSDL">#REF!</definedName>
     <definedName name="VSMTL">#REF!</definedName>
     <definedName name="VSOH">#REF!</definedName>
+    <definedName name="VV" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="VV" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="VV" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="vvv">#REF!</definedName>
     <definedName name="vvvvv">#REF!</definedName>
     <definedName name="Weight">#REF!</definedName>
     <definedName name="WGP">#REF!</definedName>
     <definedName name="WJ">#REF!</definedName>
+    <definedName name="wo" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="wo" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="wo" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="WPV">#REF!</definedName>
+    <definedName name="wrn.niwat." localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="wrn.niwat." localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="wrn.niwat." hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="xxxx">#REF!</definedName>
+    <definedName name="yuity" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="yuity" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="yuity" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="yyyy">#REF!</definedName>
     <definedName name="YYYYYYYY">#REF!</definedName>
     <definedName name="人員">#REF!</definedName>
     <definedName name="下一站進料方式">'[6]List Of Values'!$A$10:$A$12</definedName>
+    <definedName name="工作" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="工作" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="工作" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="工單出站方式">'[6]List Of Values'!$A$87:$A$91</definedName>
+    <definedName name="出口銷售收入" localSheetId="3">#REF!</definedName>
+    <definedName name="出口銷售收入" localSheetId="2">#REF!</definedName>
     <definedName name="出口銷售收入">#REF!</definedName>
+    <definedName name="本次请购" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="本次请购" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="本次请购" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="生產情況">#REF!</definedName>
     <definedName name="年數">#REF!</definedName>
     <definedName name="作業者操作介面">'[6]List Of Values'!$A$32:$A$35</definedName>
+    <definedName name="我" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="我" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="我" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="技術專案匯總2" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="技術專案匯總2" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="技術專案匯總2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="投資情況">#REF!</definedName>
     <definedName name="材料成本分析">#REF!</definedName>
+    <definedName name="其他全问题" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="其他全问题" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="其他全问题" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="固定資產投資">#REF!</definedName>
+    <definedName name="治工具" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="治工具" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具01" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具01" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="治工具01" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="能源">#REF!</definedName>
     <definedName name="動作">'[6]List Of Values'!$A$19:$A$22</definedName>
+    <definedName name="啊啊啊啊" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="啊啊啊啊" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="啊啊啊啊" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="設備型態">'[6]List Of Values'!$A$2:$A$3</definedName>
     <definedName name="設備資訊取得方式">'[6]List Of Values'!$A$49:$A$54</definedName>
+    <definedName name="陳帥虎" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="陳帥虎" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="陳帥虎" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="稅">#REF!</definedName>
     <definedName name="答案">'[6]List Of Values'!$A$44:$A$45</definedName>
@@ -705,16 +796,28 @@
     <definedName name="量測值取得時機">'[6]List Of Values'!$A$111:$A$112</definedName>
     <definedName name="量測值圖表">'[6]List Of Values'!$A$135:$A$138</definedName>
     <definedName name="量測值管制">'[6]List Of Values'!$A$129:$A$131</definedName>
+    <definedName name="匯率" localSheetId="3">#REF!</definedName>
+    <definedName name="匯率" localSheetId="2">#REF!</definedName>
     <definedName name="匯率">#REF!</definedName>
+    <definedName name="暗示" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="暗示" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="暗示" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="資料格式">'[6]List Of Values'!$A$68:$A$72</definedName>
+    <definedName name="實際出口情況" localSheetId="3">#REF!</definedName>
+    <definedName name="實際出口情況" localSheetId="2">#REF!</definedName>
     <definedName name="實際出口情況">#REF!</definedName>
+    <definedName name="實際進口情況" localSheetId="3">#REF!</definedName>
+    <definedName name="實際進口情況" localSheetId="2">#REF!</definedName>
     <definedName name="實際進口情況">#REF!</definedName>
     <definedName name="廠商支援整合方式">'[6]List Of Values'!$A$59:$A$64</definedName>
+    <definedName name="請購" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="請購" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="請購" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="機械手">#REF!</definedName>
     <definedName name="點檢頻率">'[6]List Of Values'!$A$123:$A$125</definedName>
     <definedName name="簡化">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
+    <definedName name="舊我" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="舊我" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="舊我" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1158,7 +1261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3960" uniqueCount="658">
   <si>
     <t>片材長邊尺寸 (mm) mm</t>
   </si>
@@ -3536,6 +3639,30 @@
   </si>
   <si>
     <t>B-RDL1、A-RDL1-化銅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷射</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed layer(Sputter)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed layer(化銅)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠漆蝕刻清洗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外觀檢查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厚度量測</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5123,20 +5250,104 @@
     <xf numFmtId="0" fontId="17" fillId="22" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="18" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="18" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5146,6 +5357,63 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5157,9 +5425,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5189,158 +5454,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6022,6 +6149,24 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="revised 2代-03SEC CT (2+2)"/>
+      <sheetName val="revised 2代-01SG CT (1+1)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
@@ -6344,38 +6489,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:R55"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="52.125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="52.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="10" style="113" customWidth="1"/>
-    <col min="6" max="6" width="62.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="51.125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="62.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="19.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="51.109375" style="1" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="64" style="2" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="24.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.875" style="1"/>
+    <col min="18" max="18" width="24.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="1"/>
     <col min="20" max="20" width="17" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.875" style="1"/>
+    <col min="21" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:17" ht="21" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="21" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:17" ht="21" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F4" s="4"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F5" s="4"/>
       <c r="J5" s="1" t="s">
         <v>94</v>
@@ -6384,7 +6529,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
@@ -6410,7 +6555,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
@@ -6436,25 +6581,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G8" s="263" t="s">
+    <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G8" s="200" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="264"/>
-      <c r="I8" s="265"/>
-      <c r="J8" s="266" t="s">
+      <c r="H8" s="201"/>
+      <c r="I8" s="202"/>
+      <c r="J8" s="203" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="266"/>
-      <c r="L8" s="266"/>
-      <c r="M8" s="267" t="s">
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="204" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="267"/>
-      <c r="O8" s="267"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="204"/>
       <c r="P8" s="2"/>
     </row>
-    <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
@@ -6504,8 +6649,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="106.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="250" t="s">
+    <row r="10" spans="2:17" ht="106.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="211" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6557,15 +6702,15 @@
       <c r="P10" s="12"/>
       <c r="Q10" s="13"/>
     </row>
-    <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="251"/>
-      <c r="C11" s="253" t="s">
+    <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="212"/>
+      <c r="C11" s="214" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="255">
+      <c r="E11" s="216">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6610,13 +6755,13 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="19"/>
     </row>
-    <row r="12" spans="2:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="251"/>
-      <c r="C12" s="254"/>
+    <row r="12" spans="2:17" ht="86.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="212"/>
+      <c r="C12" s="215"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="256"/>
+      <c r="E12" s="217"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6659,15 +6804,15 @@
       <c r="P12" s="12"/>
       <c r="Q12" s="19"/>
     </row>
-    <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="251"/>
-      <c r="C13" s="257" t="s">
+    <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="212"/>
+      <c r="C13" s="218" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="260">
+      <c r="E13" s="220">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6698,16 +6843,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="242"/>
-    </row>
-    <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="251"/>
-      <c r="C14" s="258"/>
+      <c r="P13" s="223"/>
+      <c r="Q13" s="224"/>
+    </row>
+    <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="212"/>
+      <c r="C14" s="219"/>
       <c r="D14" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="E14" s="261"/>
+      <c r="E14" s="221"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6727,16 +6872,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="236"/>
-      <c r="Q14" s="242"/>
-    </row>
-    <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="251"/>
-      <c r="C15" s="259"/>
+      <c r="P14" s="223"/>
+      <c r="Q14" s="224"/>
+    </row>
+    <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="212"/>
+      <c r="C15" s="208"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="262"/>
+      <c r="E15" s="222"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6774,11 +6919,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="242"/>
-    </row>
-    <row r="16" spans="2:17" ht="100.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="251"/>
+      <c r="P15" s="223"/>
+      <c r="Q15" s="224"/>
+    </row>
+    <row r="16" spans="2:17" ht="100.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="212"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6827,8 +6972,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="98.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="252"/>
+    <row r="17" spans="2:18" ht="98.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="213"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -6882,8 +7027,8 @@
       </c>
       <c r="Q17" s="31"/>
     </row>
-    <row r="18" spans="2:18" ht="122.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="205" t="s">
+    <row r="18" spans="2:18" ht="122.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="233" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -6937,8 +7082,8 @@
       <c r="P18" s="12"/>
       <c r="Q18" s="34"/>
     </row>
-    <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="206"/>
+    <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="234"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -6991,15 +7136,15 @@
       <c r="Q19" s="36"/>
       <c r="R19" s="37"/>
     </row>
-    <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="206"/>
+    <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="234"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="243">
+      <c r="E20" s="225">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -7041,19 +7186,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="245"/>
-      <c r="Q20" s="247"/>
+      <c r="P20" s="228"/>
+      <c r="Q20" s="230"/>
       <c r="R20" s="41"/>
     </row>
-    <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="206"/>
+    <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="234"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="244"/>
+      <c r="E21" s="226"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -7084,19 +7229,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="248"/>
+      <c r="P21" s="223"/>
+      <c r="Q21" s="231"/>
       <c r="R21" s="41"/>
     </row>
-    <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="206"/>
+    <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="234"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="236" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="244"/>
+      <c r="E22" s="226"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7136,17 +7281,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="236"/>
-      <c r="Q22" s="248"/>
+      <c r="P22" s="223"/>
+      <c r="Q22" s="231"/>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="206"/>
+    <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="234"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="223"/>
-      <c r="E23" s="229"/>
+      <c r="D23" s="237"/>
+      <c r="E23" s="227"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7186,12 +7331,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="246"/>
-      <c r="Q23" s="249"/>
+      <c r="P23" s="229"/>
+      <c r="Q23" s="232"/>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="2:18" ht="133.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="207"/>
+    <row r="24" spans="2:18" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="235"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7244,30 +7389,30 @@
       <c r="Q24" s="19"/>
       <c r="R24" s="49"/>
     </row>
-    <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="226" t="s">
+    <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="240" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="212" t="s">
+      <c r="C25" s="247" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="212" t="s">
+      <c r="D25" s="247" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="234">
+      <c r="E25" s="248">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="271">
+      <c r="G25" s="209">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="270">
+      <c r="H25" s="207">
         <v>8</v>
       </c>
-      <c r="I25" s="268">
+      <c r="I25" s="205">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7283,31 +7428,31 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="268">
+      <c r="M25" s="205">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="270">
+      <c r="N25" s="207">
         <v>10</v>
       </c>
-      <c r="O25" s="268">
+      <c r="O25" s="205">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="P25" s="12"/>
       <c r="Q25" s="51"/>
     </row>
-    <row r="26" spans="2:18" ht="136.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="226"/>
-      <c r="C26" s="212"/>
-      <c r="D26" s="212"/>
-      <c r="E26" s="235"/>
+    <row r="26" spans="2:18" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="240"/>
+      <c r="C26" s="247"/>
+      <c r="D26" s="247"/>
+      <c r="E26" s="249"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="272"/>
-      <c r="H26" s="259"/>
-      <c r="I26" s="269"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="206"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7320,21 +7465,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="269"/>
-      <c r="N26" s="259"/>
-      <c r="O26" s="269"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="208"/>
+      <c r="O26" s="206"/>
       <c r="P26" s="141"/>
       <c r="Q26" s="23"/>
     </row>
-    <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="226"/>
+    <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="240"/>
       <c r="C27" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="227" t="s">
+      <c r="D27" s="241" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="228">
+      <c r="E27" s="242">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7376,16 +7521,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="230"/>
-      <c r="Q27" s="224"/>
-    </row>
-    <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="226"/>
+      <c r="P27" s="243"/>
+      <c r="Q27" s="238"/>
+    </row>
+    <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="240"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="223"/>
-      <c r="E28" s="229"/>
+      <c r="D28" s="237"/>
+      <c r="E28" s="227"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7422,11 +7567,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="231"/>
-      <c r="Q28" s="225"/>
-    </row>
-    <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="226"/>
+      <c r="P28" s="244"/>
+      <c r="Q28" s="239"/>
+    </row>
+    <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="240"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7478,8 +7623,8 @@
       <c r="P29" s="29"/>
       <c r="Q29" s="31"/>
     </row>
-    <row r="30" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="226"/>
+    <row r="30" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="240"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7531,15 +7676,15 @@
       <c r="P30" s="40"/>
       <c r="Q30" s="58"/>
     </row>
-    <row r="31" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="226"/>
-      <c r="C31" s="211" t="s">
+    <row r="31" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="240"/>
+      <c r="C31" s="258" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="212" t="s">
+      <c r="D31" s="247" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="208">
+      <c r="E31" s="255">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7578,11 +7723,11 @@
       <c r="P31" s="59"/>
       <c r="Q31" s="60"/>
     </row>
-    <row r="32" spans="2:18" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="226"/>
-      <c r="C32" s="211"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="209"/>
+    <row r="32" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="240"/>
+      <c r="C32" s="258"/>
+      <c r="D32" s="247"/>
+      <c r="E32" s="256"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7619,11 +7764,11 @@
       <c r="P32" s="59"/>
       <c r="Q32" s="60"/>
     </row>
-    <row r="33" spans="2:17" ht="53.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="226"/>
-      <c r="C33" s="211"/>
-      <c r="D33" s="212"/>
-      <c r="E33" s="210"/>
+    <row r="33" spans="2:17" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="240"/>
+      <c r="C33" s="258"/>
+      <c r="D33" s="247"/>
+      <c r="E33" s="257"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7660,15 +7805,15 @@
       <c r="P33" s="59"/>
       <c r="Q33" s="60"/>
     </row>
-    <row r="34" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="226"/>
-      <c r="C34" s="211" t="s">
+    <row r="34" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="240"/>
+      <c r="C34" s="258" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="212" t="s">
+      <c r="D34" s="247" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="213">
+      <c r="E34" s="259">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7706,11 +7851,11 @@
       <c r="P34" s="29"/>
       <c r="Q34" s="31"/>
     </row>
-    <row r="35" spans="2:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="226"/>
-      <c r="C35" s="211"/>
-      <c r="D35" s="212"/>
-      <c r="E35" s="213"/>
+    <row r="35" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="240"/>
+      <c r="C35" s="258"/>
+      <c r="D35" s="247"/>
+      <c r="E35" s="259"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7750,8 +7895,8 @@
       <c r="P35" s="29"/>
       <c r="Q35" s="31"/>
     </row>
-    <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="226"/>
+    <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="240"/>
       <c r="C36" s="139" t="s">
         <v>97</v>
       </c>
@@ -7800,15 +7945,15 @@
       <c r="P36" s="125"/>
       <c r="Q36" s="126"/>
     </row>
-    <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="226"/>
-      <c r="C37" s="220" t="s">
+    <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="240"/>
+      <c r="C37" s="266" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="232">
+      <c r="E37" s="245">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7850,18 +7995,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="236"/>
-      <c r="Q37" s="238" t="s">
+      <c r="P37" s="223"/>
+      <c r="Q37" s="251" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="226"/>
-      <c r="C38" s="221"/>
+    <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="240"/>
+      <c r="C38" s="267"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="233"/>
+      <c r="E38" s="246"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -7901,18 +8046,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="236"/>
-      <c r="Q38" s="239"/>
-    </row>
-    <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="226"/>
+      <c r="P38" s="223"/>
+      <c r="Q38" s="252"/>
+    </row>
+    <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="240"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="233"/>
+      <c r="E39" s="246"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -7952,20 +8097,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="236"/>
-      <c r="Q39" s="240" t="s">
+      <c r="P39" s="223"/>
+      <c r="Q39" s="253" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="226"/>
+    <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="240"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="233"/>
+      <c r="E40" s="246"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -8005,11 +8150,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="237"/>
-      <c r="Q40" s="241"/>
-    </row>
-    <row r="41" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="205" t="s">
+      <c r="P40" s="250"/>
+      <c r="Q40" s="254"/>
+    </row>
+    <row r="41" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="233" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -8018,7 +8163,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="213">
+      <c r="E41" s="259">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -8065,15 +8210,15 @@
       </c>
       <c r="Q41" s="59"/>
     </row>
-    <row r="42" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="206"/>
+    <row r="42" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="234"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="213"/>
+      <c r="E42" s="259"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8118,8 +8263,8 @@
       </c>
       <c r="Q42" s="66"/>
     </row>
-    <row r="43" spans="2:17" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="206"/>
+    <row r="43" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="234"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8170,8 +8315,8 @@
       </c>
       <c r="Q43" s="121"/>
     </row>
-    <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="206"/>
+    <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="234"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8223,8 +8368,8 @@
       <c r="P44" s="22"/>
       <c r="Q44" s="68"/>
     </row>
-    <row r="45" spans="2:17" ht="97.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="206"/>
+    <row r="45" spans="2:17" ht="97.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="234"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8276,15 +8421,15 @@
       <c r="P45" s="12"/>
       <c r="Q45" s="51"/>
     </row>
-    <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="206"/>
-      <c r="C46" s="214" t="s">
+    <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="234"/>
+      <c r="C46" s="260" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="217" t="s">
+      <c r="D46" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="208">
+      <c r="E46" s="255">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8329,11 +8474,11 @@
       <c r="P46" s="29"/>
       <c r="Q46" s="69"/>
     </row>
-    <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="206"/>
-      <c r="C47" s="215"/>
-      <c r="D47" s="218"/>
-      <c r="E47" s="209"/>
+    <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="234"/>
+      <c r="C47" s="261"/>
+      <c r="D47" s="264"/>
+      <c r="E47" s="256"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8376,11 +8521,11 @@
       <c r="P47" s="29"/>
       <c r="Q47" s="69"/>
     </row>
-    <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="206"/>
-      <c r="C48" s="216"/>
-      <c r="D48" s="219"/>
-      <c r="E48" s="210"/>
+    <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="234"/>
+      <c r="C48" s="262"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="257"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8420,8 +8565,8 @@
       <c r="P48" s="29"/>
       <c r="Q48" s="69"/>
     </row>
-    <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="206"/>
+    <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="234"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8473,8 +8618,8 @@
       <c r="P49" s="12"/>
       <c r="Q49" s="71"/>
     </row>
-    <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="207"/>
+    <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="235"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8523,8 +8668,8 @@
       <c r="P50" s="59"/>
       <c r="Q50" s="72"/>
     </row>
-    <row r="51" spans="2:17" ht="88.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="205" t="s">
+    <row r="51" spans="2:17" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="233" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8578,8 +8723,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="206"/>
+    <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="234"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8628,8 +8773,8 @@
       </c>
       <c r="Q52" s="30"/>
     </row>
-    <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="206"/>
+    <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="234"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8678,8 +8823,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="2:17" ht="71.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="206"/>
+    <row r="54" spans="2:17" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="234"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8726,8 +8871,8 @@
       <c r="P54" s="75"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" s="113" customFormat="1" ht="77.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="207"/>
+    <row r="55" spans="2:17" s="113" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="235"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -8780,25 +8925,18 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="P20:P23"/>
-    <mergeCell ref="Q20:Q23"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C37:C38"/>
     <mergeCell ref="B18:B24"/>
     <mergeCell ref="B41:B50"/>
     <mergeCell ref="D22:D23"/>
@@ -8814,18 +8952,25 @@
     <mergeCell ref="P37:P40"/>
     <mergeCell ref="Q37:Q38"/>
     <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="P20:P23"/>
+    <mergeCell ref="Q20:Q23"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8838,16 +8983,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4663F9A2-2FF2-405B-9CB3-206C88390DE1}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.875" style="170" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" style="170" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="155" t="s">
         <v>476</v>
       </c>
@@ -8870,7 +9015,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="161" t="s">
         <v>483</v>
       </c>
@@ -8891,7 +9036,7 @@
       </c>
       <c r="G2" s="166"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="161" t="s">
         <v>83</v>
       </c>
@@ -8912,7 +9057,7 @@
       </c>
       <c r="G3" s="166"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="161" t="s">
         <v>81</v>
       </c>
@@ -8933,7 +9078,7 @@
       </c>
       <c r="G4" s="166"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="161" t="s">
         <v>92</v>
       </c>
@@ -8954,7 +9099,7 @@
       </c>
       <c r="G5" s="166"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="161" t="s">
         <v>93</v>
       </c>
@@ -8975,7 +9120,7 @@
       </c>
       <c r="G6" s="166"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="161" t="s">
         <v>497</v>
       </c>
@@ -8996,7 +9141,7 @@
       </c>
       <c r="G7" s="166"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="168" t="s">
         <v>91</v>
       </c>
@@ -9017,7 +9162,7 @@
       </c>
       <c r="G8" s="166"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="168" t="s">
         <v>502</v>
       </c>
@@ -9038,7 +9183,7 @@
       </c>
       <c r="G9" s="166"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="161" t="s">
         <v>505</v>
       </c>
@@ -9059,7 +9204,7 @@
       </c>
       <c r="G10" s="166"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="161" t="s">
         <v>111</v>
       </c>
@@ -9080,7 +9225,7 @@
       </c>
       <c r="G11" s="166"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="161" t="s">
         <v>110</v>
       </c>
@@ -9101,7 +9246,7 @@
       </c>
       <c r="G12" s="166"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="168" t="s">
         <v>512</v>
       </c>
@@ -9120,7 +9265,7 @@
       </c>
       <c r="G13" s="166"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="168" t="s">
         <v>515</v>
       </c>
@@ -9139,7 +9284,7 @@
       </c>
       <c r="G14" s="166"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="168" t="s">
         <v>518</v>
       </c>
@@ -9158,7 +9303,7 @@
       </c>
       <c r="G15" s="166"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="161" t="s">
         <v>521</v>
       </c>
@@ -9179,7 +9324,7 @@
       </c>
       <c r="G16" s="166"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="161" t="s">
         <v>524</v>
       </c>
@@ -9200,7 +9345,7 @@
       </c>
       <c r="G17" s="166"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="168" t="s">
         <v>101</v>
       </c>
@@ -9221,7 +9366,7 @@
       </c>
       <c r="G18" s="166"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="168" t="s">
         <v>96</v>
       </c>
@@ -9242,7 +9387,7 @@
       </c>
       <c r="G19" s="166"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="168" t="s">
         <v>612</v>
       </c>
@@ -9257,7 +9402,7 @@
       </c>
       <c r="G20" s="166"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="168" t="s">
         <v>87</v>
       </c>
@@ -9278,7 +9423,7 @@
       </c>
       <c r="G21" s="166"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="168" t="s">
         <v>76</v>
       </c>
@@ -9299,7 +9444,7 @@
       </c>
       <c r="G22" s="166"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="168" t="s">
         <v>86</v>
       </c>
@@ -9320,7 +9465,7 @@
       </c>
       <c r="G23" s="166"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="168" t="s">
         <v>105</v>
       </c>
@@ -9341,7 +9486,7 @@
       </c>
       <c r="G24" s="166"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="161" t="s">
         <v>539</v>
       </c>
@@ -9362,7 +9507,7 @@
       </c>
       <c r="G25" s="166"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="168" t="s">
         <v>103</v>
       </c>
@@ -9383,7 +9528,7 @@
       </c>
       <c r="G26" s="166"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="161" t="s">
         <v>543</v>
       </c>
@@ -9402,7 +9547,7 @@
       </c>
       <c r="G27" s="166"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="168" t="s">
         <v>546</v>
       </c>
@@ -9423,7 +9568,7 @@
       </c>
       <c r="G28" s="166"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="168" t="s">
         <v>549</v>
       </c>
@@ -9444,7 +9589,7 @@
       </c>
       <c r="G29" s="166"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="168" t="s">
         <v>552</v>
       </c>
@@ -9465,7 +9610,7 @@
       </c>
       <c r="G30" s="166"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="168" t="s">
         <v>555</v>
       </c>
@@ -9486,7 +9631,7 @@
       </c>
       <c r="G31" s="166"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="161" t="s">
         <v>558</v>
       </c>
@@ -9509,7 +9654,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="161" t="s">
         <v>562</v>
       </c>
@@ -9532,7 +9677,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="161" t="s">
         <v>565</v>
       </c>
@@ -9553,7 +9698,7 @@
       </c>
       <c r="G34" s="166"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="161" t="s">
         <v>568</v>
       </c>
@@ -9574,7 +9719,7 @@
       </c>
       <c r="G35" s="166"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="161" t="s">
         <v>98</v>
       </c>
@@ -9595,7 +9740,7 @@
       </c>
       <c r="G36" s="166"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="168" t="s">
         <v>102</v>
       </c>
@@ -9614,7 +9759,7 @@
       </c>
       <c r="G37" s="166"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="168" t="s">
         <v>97</v>
       </c>
@@ -9635,7 +9780,7 @@
       </c>
       <c r="G38" s="166"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="168" t="s">
         <v>577</v>
       </c>
@@ -9654,7 +9799,7 @@
       </c>
       <c r="G39" s="166"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="168" t="s">
         <v>580</v>
       </c>
@@ -9673,7 +9818,7 @@
       </c>
       <c r="G40" s="166"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="168" t="s">
         <v>583</v>
       </c>
@@ -9692,7 +9837,7 @@
       </c>
       <c r="G41" s="166"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="168" t="s">
         <v>640</v>
       </c>
@@ -9707,7 +9852,7 @@
       </c>
       <c r="G42" s="166"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="161" t="s">
         <v>586</v>
       </c>
@@ -9728,7 +9873,7 @@
       </c>
       <c r="G43" s="166"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="168" t="s">
         <v>589</v>
       </c>
@@ -9749,7 +9894,7 @@
       </c>
       <c r="G44" s="166"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="161" t="s">
         <v>99</v>
       </c>
@@ -9770,7 +9915,7 @@
       </c>
       <c r="G45" s="166"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="168" t="s">
         <v>594</v>
       </c>
@@ -9791,7 +9936,7 @@
       </c>
       <c r="G46" s="166"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="161" t="s">
         <v>597</v>
       </c>
@@ -9810,7 +9955,7 @@
       </c>
       <c r="G47" s="166"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="161" t="s">
         <v>621</v>
       </c>
@@ -9829,7 +9974,7 @@
       </c>
       <c r="G48" s="169"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="168" t="s">
         <v>601</v>
       </c>
@@ -9852,7 +9997,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="168" t="s">
         <v>605</v>
       </c>
@@ -9910,23 +10055,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B940DB27-33FF-4B35-A1F7-92CEECDE6891}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D81907-B370-479F-A63F-759394FFDDBB}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="147" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="147" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="147" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="147" customWidth="1"/>
-    <col min="6" max="7" width="13.875" style="150" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="147"/>
+    <col min="5" max="5" width="18.6640625" style="147" customWidth="1"/>
+    <col min="6" max="7" width="13.88671875" style="150" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -9949,7 +10094,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -9965,14 +10110,14 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="200">
+      <c r="F2" s="268">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="186">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -9988,14 +10133,14 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="200">
+      <c r="F3" s="268">
         <v>2.5777777777777775</v>
       </c>
       <c r="G3" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="145" t="s">
         <v>162</v>
       </c>
@@ -10003,22 +10148,22 @@
         <v>163</v>
       </c>
       <c r="C4" s="177" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D4" s="180" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="201">
+      <c r="F4" s="269">
         <v>3.8</v>
       </c>
       <c r="G4" s="189">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -10026,22 +10171,22 @@
         <v>163</v>
       </c>
       <c r="C5" s="177" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D5" s="180" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E5" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F5" s="201">
-        <v>3.8</v>
-      </c>
-      <c r="G5" s="189">
+        <v>652</v>
+      </c>
+      <c r="F5" s="270">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G5" s="198">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -10049,22 +10194,22 @@
         <v>163</v>
       </c>
       <c r="C6" s="177" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D6" s="180" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E6" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F6" s="202">
-        <v>12.379943502824901</v>
-      </c>
-      <c r="G6" s="189">
+        <v>637</v>
+      </c>
+      <c r="F6" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G6" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -10072,68 +10217,68 @@
         <v>163</v>
       </c>
       <c r="C7" s="177" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D7" s="180" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E7" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F7" s="202">
-        <v>12.0723780439164</v>
-      </c>
-      <c r="G7" s="198">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="144" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="145" t="s">
+        <v>631</v>
+      </c>
+      <c r="F7" s="270">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G7" s="189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="177" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="180" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F8" s="202">
-        <v>6.6666666666666696</v>
-      </c>
-      <c r="G8" s="189">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" s="145" t="s">
+      <c r="C8" s="191" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F8" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G8" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="177" t="s">
-        <v>191</v>
-      </c>
-      <c r="D9" s="180" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F9" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G9" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C9" s="191" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F9" s="196">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G9" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -10141,91 +10286,91 @@
         <v>163</v>
       </c>
       <c r="C10" s="177" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D10" s="180" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E10" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F10" s="202">
-        <v>3.3142857142857101</v>
-      </c>
-      <c r="G10" s="189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="190" t="s">
+        <v>637</v>
+      </c>
+      <c r="F10" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G10" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="191" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="192" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F11" s="196">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G11" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B12" s="190" t="s">
+      <c r="C11" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="180" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F11" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G11" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="191" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="192" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F12" s="196">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G12" s="193">
+      <c r="C12" s="177" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="180" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="186" t="s">
+        <v>653</v>
+      </c>
+      <c r="F12" s="268">
+        <v>10</v>
+      </c>
+      <c r="G12" s="186">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B13" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="177" t="s">
-        <v>205</v>
+      <c r="C13" s="199" t="s">
+        <v>650</v>
       </c>
       <c r="D13" s="180" t="s">
-        <v>206</v>
+        <v>649</v>
       </c>
       <c r="E13" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F13" s="200">
-        <v>1.1047619047618999</v>
+        <v>654</v>
+      </c>
+      <c r="F13" s="268">
+        <v>4.8</v>
       </c>
       <c r="G13" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -10233,22 +10378,22 @@
         <v>163</v>
       </c>
       <c r="C14" s="177" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D14" s="180" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E14" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F14" s="200">
-        <v>1.1047619047618999</v>
+        <v>629</v>
+      </c>
+      <c r="F14" s="268">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G14" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -10256,45 +10401,45 @@
         <v>163</v>
       </c>
       <c r="C15" s="177" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D15" s="180" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E15" s="186" t="s">
-        <v>633</v>
-      </c>
-      <c r="F15" s="200">
-        <v>13.333333333333334</v>
+        <v>629</v>
+      </c>
+      <c r="F15" s="268">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G15" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B16" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C16" s="199" t="s">
-        <v>650</v>
+      <c r="C16" s="177" t="s">
+        <v>229</v>
       </c>
       <c r="D16" s="180" t="s">
-        <v>649</v>
+        <v>230</v>
       </c>
       <c r="E16" s="186" t="s">
-        <v>633</v>
-      </c>
-      <c r="F16" s="200">
-        <v>4.8</v>
+        <v>630</v>
+      </c>
+      <c r="F16" s="268">
+        <v>4.63657407407407</v>
       </c>
       <c r="G16" s="186">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="145" t="s">
         <v>162</v>
       </c>
@@ -10302,91 +10447,91 @@
         <v>163</v>
       </c>
       <c r="C17" s="177" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="D17" s="180" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="E17" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F17" s="202">
-        <v>3.9080000000000004</v>
+        <v>631</v>
+      </c>
+      <c r="F17" s="270">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G17" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="145" t="s">
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="177" t="s">
-        <v>217</v>
-      </c>
-      <c r="D18" s="180" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F18" s="200">
-        <v>3.0222222222222199</v>
-      </c>
-      <c r="G18" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="145" t="s">
+      <c r="C18" s="191" t="s">
+        <v>237</v>
+      </c>
+      <c r="D18" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F18" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G18" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="177" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="180" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F19" s="200">
-        <v>3.0222222222222199</v>
-      </c>
-      <c r="G19" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="145" t="s">
+      <c r="C19" s="191" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F19" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G19" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C20" s="177" t="s">
-        <v>223</v>
-      </c>
-      <c r="D20" s="180" t="s">
-        <v>224</v>
-      </c>
-      <c r="E20" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F20" s="200">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="G20" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C20" s="191" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F20" s="196">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G20" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="145" t="s">
         <v>162</v>
       </c>
@@ -10394,22 +10539,22 @@
         <v>163</v>
       </c>
       <c r="C21" s="177" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D21" s="180" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="E21" s="186" t="s">
-        <v>630</v>
-      </c>
-      <c r="F21" s="200">
-        <v>4.63657407407407</v>
+        <v>637</v>
+      </c>
+      <c r="F21" s="268">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G21" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="145" t="s">
         <v>162</v>
       </c>
@@ -10417,91 +10562,91 @@
         <v>163</v>
       </c>
       <c r="C22" s="177" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D22" s="180" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="E22" s="186" t="s">
-        <v>631</v>
-      </c>
-      <c r="F22" s="202">
-        <v>3.3142857142857101</v>
+        <v>634</v>
+      </c>
+      <c r="F22" s="268">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G22" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="190" t="s">
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C23" s="191" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" s="192" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F23" s="196">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G23" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B24" s="190" t="s">
+      <c r="C23" s="177" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="180" t="s">
+        <v>258</v>
+      </c>
+      <c r="E23" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="F23" s="269">
+        <v>3.8</v>
+      </c>
+      <c r="G23" s="189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="191" t="s">
-        <v>239</v>
-      </c>
-      <c r="D24" s="192" t="s">
-        <v>240</v>
-      </c>
-      <c r="E24" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F24" s="196">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G24" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="190" t="s">
+      <c r="C24" s="177" t="s">
+        <v>263</v>
+      </c>
+      <c r="D24" s="180" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" s="186" t="s">
+        <v>652</v>
+      </c>
+      <c r="F24" s="270">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G24" s="198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="191" t="s">
-        <v>243</v>
-      </c>
-      <c r="D25" s="192" t="s">
-        <v>244</v>
-      </c>
-      <c r="E25" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F25" s="196">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G25" s="193">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C25" s="177" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="180" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F25" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G25" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -10509,22 +10654,22 @@
         <v>163</v>
       </c>
       <c r="C26" s="177" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="D26" s="180" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="E26" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F26" s="200">
-        <v>1.1047619047618999</v>
+        <v>634</v>
+      </c>
+      <c r="F26" s="268">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G26" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="145" t="s">
         <v>162</v>
       </c>
@@ -10532,45 +10677,43 @@
         <v>163</v>
       </c>
       <c r="C27" s="177" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="D27" s="180" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="E27" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F27" s="200">
-        <v>2.5777777777777775</v>
+        <v>628</v>
+      </c>
+      <c r="F27" s="268">
+        <v>3.31111111111111</v>
       </c>
       <c r="G27" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" s="145" t="s">
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C28" s="177" t="s">
-        <v>257</v>
-      </c>
-      <c r="D28" s="180" t="s">
-        <v>258</v>
-      </c>
-      <c r="E28" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F28" s="201">
-        <v>3.8</v>
-      </c>
-      <c r="G28" s="189">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C28" s="191" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F28" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G28" s="193"/>
+    </row>
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="145" t="s">
         <v>162</v>
       </c>
@@ -10578,91 +10721,91 @@
         <v>163</v>
       </c>
       <c r="C29" s="177" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="D29" s="180" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="E29" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F29" s="202">
-        <v>12.379943502824901</v>
-      </c>
-      <c r="G29" s="189">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B30" s="145" t="s">
+        <v>631</v>
+      </c>
+      <c r="F29" s="270">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G29" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="177" t="s">
-        <v>263</v>
-      </c>
-      <c r="D30" s="180" t="s">
-        <v>264</v>
-      </c>
-      <c r="E30" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F30" s="202">
-        <v>12.0723780439164</v>
-      </c>
-      <c r="G30" s="198">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="145" t="s">
+      <c r="C30" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" s="192" t="s">
+        <v>293</v>
+      </c>
+      <c r="E30" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F30" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G30" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C31" s="177" t="s">
-        <v>265</v>
-      </c>
-      <c r="D31" s="180" t="s">
-        <v>266</v>
-      </c>
-      <c r="E31" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F31" s="202">
-        <v>6.6666666666666696</v>
-      </c>
-      <c r="G31" s="189">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="145" t="s">
+      <c r="C31" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="E31" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F31" s="196">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G31" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="177" t="s">
-        <v>267</v>
-      </c>
-      <c r="D32" s="180" t="s">
-        <v>268</v>
-      </c>
-      <c r="E32" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F32" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G32" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C32" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32" s="192" t="s">
+        <v>297</v>
+      </c>
+      <c r="E32" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F32" s="196">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G32" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -10670,45 +10813,45 @@
         <v>163</v>
       </c>
       <c r="C33" s="177" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="D33" s="180" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E33" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F33" s="200">
-        <v>2.5777777777777775</v>
+        <v>637</v>
+      </c>
+      <c r="F33" s="268">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G33" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B34" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C34" s="177" t="s">
-        <v>273</v>
+      <c r="C34" s="199" t="s">
+        <v>650</v>
       </c>
       <c r="D34" s="180" t="s">
-        <v>274</v>
+        <v>648</v>
       </c>
       <c r="E34" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F34" s="200">
-        <v>4.76</v>
+        <v>654</v>
+      </c>
+      <c r="F34" s="268">
+        <v>4.8</v>
       </c>
       <c r="G34" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="145" t="s">
         <v>162</v>
       </c>
@@ -10716,22 +10859,22 @@
         <v>163</v>
       </c>
       <c r="C35" s="177" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="D35" s="180" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="E35" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F35" s="200">
-        <v>5</v>
+        <v>629</v>
+      </c>
+      <c r="F35" s="268">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G35" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="145" t="s">
         <v>162</v>
       </c>
@@ -10739,22 +10882,22 @@
         <v>163</v>
       </c>
       <c r="C36" s="177" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D36" s="180" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="E36" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F36" s="200">
-        <v>3.31111111111111</v>
+        <v>629</v>
+      </c>
+      <c r="F36" s="268">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G36" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="145" t="s">
         <v>162</v>
       </c>
@@ -10762,91 +10905,91 @@
         <v>163</v>
       </c>
       <c r="C37" s="177" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="D37" s="180" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="E37" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F37" s="200">
-        <v>1.54666666666667</v>
+        <v>630</v>
+      </c>
+      <c r="F37" s="268">
+        <v>4.63657407407407</v>
       </c>
       <c r="G37" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="190" t="s">
+    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="191" t="s">
-        <v>281</v>
-      </c>
-      <c r="D38" s="192" t="s">
-        <v>282</v>
-      </c>
-      <c r="E38" s="193" t="s">
+      <c r="C38" s="177" t="s">
+        <v>324</v>
+      </c>
+      <c r="D38" s="180" t="s">
+        <v>325</v>
+      </c>
+      <c r="E38" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F38" s="270">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G38" s="189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="190" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="191" t="s">
+        <v>328</v>
+      </c>
+      <c r="D39" s="192" t="s">
+        <v>329</v>
+      </c>
+      <c r="E39" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F38" s="196">
+      <c r="F39" s="196">
         <v>4.666666666666667</v>
       </c>
-      <c r="G38" s="193">
+      <c r="G39" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B39" s="145" t="s">
+    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C39" s="177" t="s">
-        <v>287</v>
-      </c>
-      <c r="D39" s="180" t="s">
-        <v>288</v>
-      </c>
-      <c r="E39" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F39" s="200">
-        <v>4.1666666666666696</v>
-      </c>
-      <c r="G39" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B40" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C40" s="177" t="s">
-        <v>291</v>
-      </c>
-      <c r="D40" s="180" t="s">
-        <v>196</v>
-      </c>
-      <c r="E40" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F40" s="202">
-        <v>3.3142857142857101</v>
-      </c>
-      <c r="G40" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C40" s="191" t="s">
+        <v>330</v>
+      </c>
+      <c r="D40" s="192" t="s">
+        <v>331</v>
+      </c>
+      <c r="E40" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F40" s="196">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G40" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="190" t="s">
         <v>162</v>
       </c>
@@ -10854,68 +10997,68 @@
         <v>163</v>
       </c>
       <c r="C41" s="191" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="D41" s="192" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="E41" s="193" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="F41" s="196">
-        <v>4.666666666666667</v>
+        <v>12.166666666666666</v>
       </c>
       <c r="G41" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="190" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="191" t="s">
-        <v>294</v>
-      </c>
-      <c r="D42" s="192" t="s">
-        <v>295</v>
-      </c>
-      <c r="E42" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F42" s="196">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G42" s="193">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="190" t="s">
+      <c r="C42" s="177" t="s">
+        <v>338</v>
+      </c>
+      <c r="D42" s="180" t="s">
+        <v>339</v>
+      </c>
+      <c r="E42" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F42" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G42" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="191" t="s">
-        <v>296</v>
-      </c>
-      <c r="D43" s="192" t="s">
-        <v>297</v>
-      </c>
-      <c r="E43" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F43" s="196">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G43" s="193">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C43" s="177" t="s">
+        <v>340</v>
+      </c>
+      <c r="D43" s="180" t="s">
+        <v>341</v>
+      </c>
+      <c r="E43" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F43" s="268">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G43" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="145" t="s">
         <v>162</v>
       </c>
@@ -10923,45 +11066,45 @@
         <v>163</v>
       </c>
       <c r="C44" s="177" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="D44" s="180" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="E44" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F44" s="200">
-        <v>1.1047619047618999</v>
+        <v>628</v>
+      </c>
+      <c r="F44" s="268">
+        <v>3.31111111111111</v>
       </c>
       <c r="G44" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B45" s="145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C45" s="199" t="s">
-        <v>650</v>
-      </c>
-      <c r="D45" s="180" t="s">
-        <v>648</v>
-      </c>
-      <c r="E45" s="186" t="s">
-        <v>633</v>
-      </c>
-      <c r="F45" s="200">
-        <v>4.8</v>
-      </c>
-      <c r="G45" s="186">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C45" s="191" t="s">
+        <v>352</v>
+      </c>
+      <c r="D45" s="192" t="s">
+        <v>353</v>
+      </c>
+      <c r="E45" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F45" s="196">
+        <v>5.5</v>
+      </c>
+      <c r="G45" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="145" t="s">
         <v>162</v>
       </c>
@@ -10969,22 +11112,22 @@
         <v>163</v>
       </c>
       <c r="C46" s="177" t="s">
-        <v>306</v>
+        <v>360</v>
       </c>
       <c r="D46" s="180" t="s">
-        <v>307</v>
+        <v>361</v>
       </c>
       <c r="E46" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F46" s="202">
-        <v>3.9080000000000004</v>
+        <v>637</v>
+      </c>
+      <c r="F46" s="268">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G46" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="145" t="s">
         <v>162</v>
       </c>
@@ -10992,22 +11135,22 @@
         <v>163</v>
       </c>
       <c r="C47" s="177" t="s">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="D47" s="180" t="s">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="E47" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F47" s="200">
-        <v>3.0222222222222199</v>
+        <v>634</v>
+      </c>
+      <c r="F47" s="268">
+        <v>2.5777777777777775</v>
       </c>
       <c r="G47" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="145" t="s">
         <v>162</v>
       </c>
@@ -11015,45 +11158,45 @@
         <v>163</v>
       </c>
       <c r="C48" s="177" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="D48" s="180" t="s">
-        <v>311</v>
+        <v>372</v>
       </c>
       <c r="E48" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F48" s="200">
-        <v>3.0222222222222199</v>
+        <v>628</v>
+      </c>
+      <c r="F48" s="268">
+        <v>3.31111111111111</v>
       </c>
       <c r="G48" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" s="145" t="s">
+    <row r="49" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C49" s="177" t="s">
-        <v>314</v>
-      </c>
-      <c r="D49" s="180" t="s">
-        <v>315</v>
-      </c>
-      <c r="E49" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F49" s="200">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="G49" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C49" s="191" t="s">
+        <v>375</v>
+      </c>
+      <c r="D49" s="192" t="s">
+        <v>376</v>
+      </c>
+      <c r="E49" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F49" s="196">
+        <v>5.5</v>
+      </c>
+      <c r="G49" s="193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="145" t="s">
         <v>162</v>
       </c>
@@ -11061,22 +11204,22 @@
         <v>163</v>
       </c>
       <c r="C50" s="177" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="D50" s="180" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="E50" s="186" t="s">
-        <v>630</v>
-      </c>
-      <c r="F50" s="200">
-        <v>4.63657407407407</v>
+        <v>655</v>
+      </c>
+      <c r="F50" s="268">
+        <v>1.0311111111111111</v>
       </c>
       <c r="G50" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="145" t="s">
         <v>162</v>
       </c>
@@ -11084,45 +11227,45 @@
         <v>163</v>
       </c>
       <c r="C51" s="177" t="s">
-        <v>324</v>
+        <v>387</v>
       </c>
       <c r="D51" s="180" t="s">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="E51" s="186" t="s">
-        <v>631</v>
-      </c>
-      <c r="F51" s="202">
-        <v>3.3142857142857101</v>
-      </c>
-      <c r="G51" s="189">
+        <v>637</v>
+      </c>
+      <c r="F51" s="268">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G51" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="177" t="s">
+        <v>391</v>
+      </c>
+      <c r="D52" s="180" t="s">
+        <v>392</v>
+      </c>
+      <c r="E52" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F52" s="268">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G52" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="191" t="s">
-        <v>328</v>
-      </c>
-      <c r="D52" s="192" t="s">
-        <v>329</v>
-      </c>
-      <c r="E52" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F52" s="196">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G52" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="190" t="s">
         <v>162</v>
       </c>
@@ -11130,22 +11273,22 @@
         <v>163</v>
       </c>
       <c r="C53" s="191" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="D53" s="192" t="s">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="E53" s="193" t="s">
         <v>638</v>
       </c>
       <c r="F53" s="196">
-        <v>4.666666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="G53" s="193">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="190" t="s">
         <v>162</v>
       </c>
@@ -11153,22 +11296,22 @@
         <v>163</v>
       </c>
       <c r="C54" s="191" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="D54" s="192" t="s">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="E54" s="193" t="s">
         <v>638</v>
       </c>
       <c r="F54" s="196">
-        <v>12.166666666666666</v>
+        <v>5.5</v>
       </c>
       <c r="G54" s="193">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="145" t="s">
         <v>162</v>
       </c>
@@ -11176,22 +11319,22 @@
         <v>163</v>
       </c>
       <c r="C55" s="177" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="D55" s="180" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="E55" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F55" s="200">
+      <c r="F55" s="268">
         <v>1.1047619047618999</v>
       </c>
       <c r="G55" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="145" t="s">
         <v>162</v>
       </c>
@@ -11199,68 +11342,68 @@
         <v>163</v>
       </c>
       <c r="C56" s="177" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
       <c r="D56" s="180" t="s">
-        <v>341</v>
+        <v>402</v>
       </c>
       <c r="E56" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F56" s="200">
-        <v>2.5777777777777775</v>
+        <v>635</v>
+      </c>
+      <c r="F56" s="268">
+        <v>3</v>
       </c>
       <c r="G56" s="186">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B57" s="145" t="s">
+    <row r="57" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="177" t="s">
-        <v>344</v>
-      </c>
-      <c r="D57" s="180" t="s">
-        <v>345</v>
-      </c>
-      <c r="E57" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F57" s="200">
-        <v>4.76</v>
-      </c>
-      <c r="G57" s="186">
+      <c r="C57" s="191" t="s">
+        <v>403</v>
+      </c>
+      <c r="D57" s="192" t="s">
+        <v>404</v>
+      </c>
+      <c r="E57" s="193" t="s">
+        <v>657</v>
+      </c>
+      <c r="F57" s="196">
+        <v>15</v>
+      </c>
+      <c r="G57" s="193">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="145" t="s">
+    <row r="58" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B58" s="190" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="177" t="s">
-        <v>346</v>
-      </c>
-      <c r="D58" s="180" t="s">
-        <v>347</v>
-      </c>
-      <c r="E58" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F58" s="200">
-        <v>5</v>
-      </c>
-      <c r="G58" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C58" s="191" t="s">
+        <v>407</v>
+      </c>
+      <c r="D58" s="192" t="s">
+        <v>408</v>
+      </c>
+      <c r="E58" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F58" s="196">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G58" s="193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="145" t="s">
         <v>162</v>
       </c>
@@ -11268,528 +11411,45 @@
         <v>163</v>
       </c>
       <c r="C59" s="177" t="s">
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="D59" s="180" t="s">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="E59" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F59" s="200">
-        <v>3.31111111111111</v>
+        <v>637</v>
+      </c>
+      <c r="F59" s="268">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G59" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C60" s="177" t="s">
-        <v>350</v>
-      </c>
-      <c r="D60" s="180" t="s">
-        <v>351</v>
-      </c>
-      <c r="E60" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F60" s="200">
-        <v>1.54666666666667</v>
-      </c>
-      <c r="G60" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C61" s="191" t="s">
-        <v>352</v>
-      </c>
-      <c r="D61" s="192" t="s">
-        <v>353</v>
-      </c>
-      <c r="E61" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F61" s="196">
-        <v>5.5</v>
-      </c>
-      <c r="G61" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B62" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="177" t="s">
-        <v>358</v>
-      </c>
-      <c r="D62" s="180" t="s">
-        <v>359</v>
-      </c>
-      <c r="E62" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F62" s="200">
-        <v>4.1666666666666696</v>
-      </c>
-      <c r="G62" s="186">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B63" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" s="177" t="s">
-        <v>360</v>
-      </c>
-      <c r="D63" s="180" t="s">
-        <v>361</v>
-      </c>
-      <c r="E63" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F63" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G63" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B64" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C64" s="177" t="s">
-        <v>362</v>
-      </c>
-      <c r="D64" s="180" t="s">
-        <v>363</v>
-      </c>
-      <c r="E64" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F64" s="200">
-        <v>2.5777777777777775</v>
-      </c>
-      <c r="G64" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B65" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="177" t="s">
-        <v>366</v>
-      </c>
-      <c r="D65" s="180" t="s">
-        <v>367</v>
-      </c>
-      <c r="E65" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F65" s="200">
-        <v>4.76</v>
-      </c>
-      <c r="G65" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B66" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C66" s="177" t="s">
-        <v>368</v>
-      </c>
-      <c r="D66" s="180" t="s">
-        <v>369</v>
-      </c>
-      <c r="E66" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F66" s="200">
-        <v>5</v>
-      </c>
-      <c r="G66" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B67" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C67" s="177" t="s">
-        <v>371</v>
-      </c>
-      <c r="D67" s="180" t="s">
-        <v>372</v>
-      </c>
-      <c r="E67" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F67" s="200">
-        <v>3.31111111111111</v>
-      </c>
-      <c r="G67" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B68" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C68" s="177" t="s">
-        <v>373</v>
-      </c>
-      <c r="D68" s="180" t="s">
-        <v>374</v>
-      </c>
-      <c r="E68" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F68" s="200">
-        <v>1.54666666666667</v>
-      </c>
-      <c r="G68" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B69" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C69" s="191" t="s">
-        <v>375</v>
-      </c>
-      <c r="D69" s="192" t="s">
-        <v>376</v>
-      </c>
-      <c r="E69" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F69" s="196">
-        <v>5.5</v>
-      </c>
-      <c r="G69" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B70" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C70" s="177" t="s">
-        <v>381</v>
-      </c>
-      <c r="D70" s="180" t="s">
-        <v>382</v>
-      </c>
-      <c r="E70" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F70" s="200">
-        <v>4.1666666666666696</v>
-      </c>
-      <c r="G70" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C71" s="177" t="s">
-        <v>385</v>
-      </c>
-      <c r="D71" s="180" t="s">
-        <v>386</v>
-      </c>
-      <c r="E71" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F71" s="200">
-        <v>1.0311111111111111</v>
-      </c>
-      <c r="G71" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B72" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C72" s="177" t="s">
-        <v>387</v>
-      </c>
-      <c r="D72" s="180" t="s">
-        <v>388</v>
-      </c>
-      <c r="E72" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F72" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G72" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B73" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C73" s="177" t="s">
-        <v>391</v>
-      </c>
-      <c r="D73" s="180" t="s">
-        <v>392</v>
-      </c>
-      <c r="E73" s="186" t="s">
-        <v>630</v>
-      </c>
-      <c r="F73" s="200">
-        <v>4.63657407407407</v>
-      </c>
-      <c r="G73" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B74" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C74" s="191" t="s">
-        <v>393</v>
-      </c>
-      <c r="D74" s="192" t="s">
-        <v>394</v>
-      </c>
-      <c r="E74" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F74" s="196">
-        <v>5.5</v>
-      </c>
-      <c r="G74" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C75" s="191" t="s">
-        <v>395</v>
-      </c>
-      <c r="D75" s="192" t="s">
-        <v>396</v>
-      </c>
-      <c r="E75" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F75" s="196">
-        <v>5.5</v>
-      </c>
-      <c r="G75" s="193">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B76" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="177" t="s">
-        <v>397</v>
-      </c>
-      <c r="D76" s="180" t="s">
-        <v>398</v>
-      </c>
-      <c r="E76" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F76" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G76" s="186">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B77" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C77" s="177" t="s">
-        <v>401</v>
-      </c>
-      <c r="D77" s="180" t="s">
-        <v>402</v>
-      </c>
-      <c r="E77" s="186" t="s">
-        <v>635</v>
-      </c>
-      <c r="F77" s="200">
-        <v>3</v>
-      </c>
-      <c r="G77" s="186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B78" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C78" s="191" t="s">
-        <v>403</v>
-      </c>
-      <c r="D78" s="192" t="s">
-        <v>404</v>
-      </c>
-      <c r="E78" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F78" s="196">
-        <v>15</v>
-      </c>
-      <c r="G78" s="193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" s="191" t="s">
-        <v>407</v>
-      </c>
-      <c r="D79" s="192" t="s">
-        <v>408</v>
-      </c>
-      <c r="E79" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F79" s="196">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G79" s="193">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B80" s="145" t="s">
-        <v>163</v>
-      </c>
-      <c r="C80" s="177" t="s">
-        <v>415</v>
-      </c>
-      <c r="D80" s="180" t="s">
-        <v>416</v>
-      </c>
-      <c r="E80" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F80" s="200">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G80" s="186">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G80" xr:uid="{6728E53C-434A-495F-8AAB-EEEFA7B7F41D}"/>
+  <autoFilter ref="A1:G59" xr:uid="{6728E53C-434A-495F-8AAB-EEEFA7B7F41D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAB5271-26E0-4296-9BB6-CB6852186E40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6E6311-E6B9-426D-B9CD-C1804811A06D}">
   <sheetPr>
-    <tabColor theme="8"/>
+    <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G77"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.5" style="147" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5546875" style="147" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="147" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="150" customWidth="1"/>
-    <col min="6" max="7" width="13.875" style="150" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="147"/>
+    <col min="5" max="5" width="16.88671875" style="150" customWidth="1"/>
+    <col min="6" max="7" width="13.88671875" style="150" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -11812,7 +11472,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -11828,14 +11488,14 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="203">
+      <c r="F2" s="271">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="149">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -11851,14 +11511,14 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="203">
+      <c r="F3" s="271">
         <v>2.5777777777777802</v>
       </c>
       <c r="G3" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="145" t="s">
         <v>162</v>
       </c>
@@ -11866,22 +11526,22 @@
         <v>419</v>
       </c>
       <c r="C4" s="177" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D4" s="180" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="203">
+      <c r="F4" s="271">
         <v>3.8</v>
       </c>
       <c r="G4" s="149">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -11889,22 +11549,22 @@
         <v>419</v>
       </c>
       <c r="C5" s="177" t="s">
-        <v>427</v>
+        <v>251</v>
       </c>
       <c r="D5" s="180" t="s">
-        <v>428</v>
+        <v>252</v>
       </c>
       <c r="E5" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F5" s="203">
-        <v>3.8</v>
+        <v>637</v>
+      </c>
+      <c r="F5" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G5" s="149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -11912,22 +11572,22 @@
         <v>419</v>
       </c>
       <c r="C6" s="177" t="s">
-        <v>429</v>
+        <v>253</v>
       </c>
       <c r="D6" s="180" t="s">
-        <v>475</v>
+        <v>254</v>
       </c>
       <c r="E6" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F6" s="203">
-        <v>12.379943502824901</v>
+        <v>634</v>
+      </c>
+      <c r="F6" s="271">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G6" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -11935,22 +11595,22 @@
         <v>419</v>
       </c>
       <c r="C7" s="177" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D7" s="180" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F7" s="203">
-        <v>6.666666666666667</v>
+      <c r="F7" s="271">
+        <v>3.8</v>
       </c>
       <c r="G7" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="145" t="s">
         <v>162</v>
       </c>
@@ -11958,22 +11618,22 @@
         <v>419</v>
       </c>
       <c r="C8" s="177" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D8" s="180" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E8" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F8" s="203">
-        <v>1.1047619047618999</v>
+        <v>652</v>
+      </c>
+      <c r="F8" s="271">
+        <v>12.072378043916389</v>
       </c>
       <c r="G8" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="145" t="s">
         <v>162</v>
       </c>
@@ -11981,22 +11641,22 @@
         <v>419</v>
       </c>
       <c r="C9" s="177" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="D9" s="180" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="E9" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F9" s="203">
-        <v>2.5777777777777802</v>
+        <v>652</v>
+      </c>
+      <c r="F9" s="271">
+        <v>12.072378043916389</v>
       </c>
       <c r="G9" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -12004,22 +11664,22 @@
         <v>419</v>
       </c>
       <c r="C10" s="177" t="s">
-        <v>437</v>
+        <v>191</v>
       </c>
       <c r="D10" s="180" t="s">
-        <v>438</v>
+        <v>192</v>
       </c>
       <c r="E10" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F10" s="203">
-        <v>3.8</v>
+        <v>637</v>
+      </c>
+      <c r="F10" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G10" s="149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="145" t="s">
         <v>162</v>
       </c>
@@ -12027,68 +11687,68 @@
         <v>419</v>
       </c>
       <c r="C11" s="177" t="s">
-        <v>439</v>
+        <v>195</v>
       </c>
       <c r="D11" s="180" t="s">
-        <v>440</v>
+        <v>196</v>
       </c>
       <c r="E11" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F11" s="203">
-        <v>12.379943502824901</v>
+        <v>631</v>
+      </c>
+      <c r="F11" s="271">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G11" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B12" s="145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C12" s="177" t="s">
-        <v>263</v>
-      </c>
-      <c r="D12" s="180" t="s">
-        <v>264</v>
-      </c>
-      <c r="E12" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F12" s="203">
-        <v>12.072378043916389</v>
-      </c>
-      <c r="G12" s="149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B13" s="145" t="s">
+      <c r="C12" s="191" t="s">
+        <v>441</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>442</v>
+      </c>
+      <c r="E12" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F12" s="194">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G12" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C13" s="177" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="180" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F13" s="203">
-        <v>12.072378043916389</v>
-      </c>
-      <c r="G13" s="149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="191" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="192" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F13" s="194">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G13" s="195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -12096,22 +11756,22 @@
         <v>419</v>
       </c>
       <c r="C14" s="177" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D14" s="180" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E14" s="186" t="s">
-        <v>632</v>
-      </c>
-      <c r="F14" s="203">
-        <v>6.666666666666667</v>
+        <v>637</v>
+      </c>
+      <c r="F14" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G14" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -12119,22 +11779,22 @@
         <v>419</v>
       </c>
       <c r="C15" s="177" t="s">
-        <v>191</v>
+        <v>650</v>
       </c>
       <c r="D15" s="180" t="s">
-        <v>192</v>
+        <v>651</v>
       </c>
       <c r="E15" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F15" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G15" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+      <c r="F15" s="272">
+        <v>4.8</v>
+      </c>
+      <c r="G15" s="176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
@@ -12142,68 +11802,68 @@
         <v>419</v>
       </c>
       <c r="C16" s="177" t="s">
-        <v>195</v>
+        <v>447</v>
       </c>
       <c r="D16" s="180" t="s">
-        <v>196</v>
+        <v>448</v>
       </c>
       <c r="E16" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F16" s="203">
-        <v>3.3142857142857101</v>
+        <v>629</v>
+      </c>
+      <c r="F16" s="271">
+        <v>3.0222222222222199</v>
       </c>
       <c r="G16" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="190" t="s">
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="145" t="s">
         <v>419</v>
       </c>
-      <c r="C17" s="191" t="s">
-        <v>441</v>
-      </c>
-      <c r="D17" s="192" t="s">
-        <v>442</v>
-      </c>
-      <c r="E17" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F17" s="194">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G17" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="190" t="s">
+      <c r="C17" s="177" t="s">
+        <v>449</v>
+      </c>
+      <c r="D17" s="180" t="s">
+        <v>450</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F17" s="271">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G17" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="145" t="s">
         <v>419</v>
       </c>
-      <c r="C18" s="191" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="192" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F18" s="194">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G18" s="195">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C18" s="177" t="s">
+        <v>457</v>
+      </c>
+      <c r="D18" s="180" t="s">
+        <v>458</v>
+      </c>
+      <c r="E18" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F18" s="271">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G18" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="145" t="s">
         <v>162</v>
       </c>
@@ -12211,114 +11871,114 @@
         <v>419</v>
       </c>
       <c r="C19" s="177" t="s">
-        <v>207</v>
+        <v>324</v>
       </c>
       <c r="D19" s="180" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E19" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F19" s="203">
-        <v>1.1047619047618999</v>
+        <v>631</v>
+      </c>
+      <c r="F19" s="271">
+        <v>3.3142857142857101</v>
       </c>
       <c r="G19" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C20" s="177" t="s">
-        <v>650</v>
-      </c>
-      <c r="D20" s="180" t="s">
-        <v>651</v>
-      </c>
-      <c r="E20" s="186" t="s">
-        <v>633</v>
-      </c>
-      <c r="F20" s="204">
-        <v>4.8</v>
-      </c>
-      <c r="G20" s="176">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="145" t="s">
+      <c r="C20" s="191" t="s">
+        <v>459</v>
+      </c>
+      <c r="D20" s="192" t="s">
+        <v>460</v>
+      </c>
+      <c r="E20" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F20" s="194">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G20" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="177" t="s">
-        <v>445</v>
-      </c>
-      <c r="D21" s="180" t="s">
-        <v>446</v>
-      </c>
-      <c r="E21" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F21" s="203">
-        <v>3.9080000000000004</v>
-      </c>
-      <c r="G21" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22" s="145" t="s">
+      <c r="C21" s="191" t="s">
+        <v>237</v>
+      </c>
+      <c r="D21" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F21" s="194">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G21" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C22" s="177" t="s">
-        <v>447</v>
-      </c>
-      <c r="D22" s="180" t="s">
-        <v>448</v>
-      </c>
-      <c r="E22" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F22" s="203">
-        <v>3.0222222222222199</v>
-      </c>
-      <c r="G22" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="145" t="s">
+      <c r="C22" s="191" t="s">
+        <v>328</v>
+      </c>
+      <c r="D22" s="192" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F22" s="194">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G22" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C23" s="177" t="s">
-        <v>449</v>
-      </c>
-      <c r="D23" s="180" t="s">
-        <v>450</v>
-      </c>
-      <c r="E23" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F23" s="203">
-        <v>3.0222222222222199</v>
-      </c>
-      <c r="G23" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C23" s="191" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F23" s="194">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G23" s="195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="145" t="s">
         <v>162</v>
       </c>
@@ -12326,22 +11986,22 @@
         <v>419</v>
       </c>
       <c r="C24" s="177" t="s">
-        <v>453</v>
+        <v>338</v>
       </c>
       <c r="D24" s="180" t="s">
-        <v>454</v>
+        <v>339</v>
       </c>
       <c r="E24" s="186" t="s">
-        <v>629</v>
-      </c>
-      <c r="F24" s="203">
-        <v>2.3199999999999998</v>
+        <v>637</v>
+      </c>
+      <c r="F24" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G24" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="145" t="s">
         <v>162</v>
       </c>
@@ -12349,22 +12009,22 @@
         <v>419</v>
       </c>
       <c r="C25" s="177" t="s">
-        <v>457</v>
+        <v>340</v>
       </c>
       <c r="D25" s="180" t="s">
-        <v>458</v>
+        <v>341</v>
       </c>
       <c r="E25" s="186" t="s">
-        <v>630</v>
-      </c>
-      <c r="F25" s="203">
-        <v>4.63657407407407</v>
+        <v>634</v>
+      </c>
+      <c r="F25" s="271">
+        <v>2.5777777777777802</v>
       </c>
       <c r="G25" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -12372,22 +12032,22 @@
         <v>419</v>
       </c>
       <c r="C26" s="177" t="s">
-        <v>324</v>
+        <v>461</v>
       </c>
       <c r="D26" s="180" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="E26" s="186" t="s">
-        <v>631</v>
-      </c>
-      <c r="F26" s="203">
-        <v>3.3142857142857101</v>
+        <v>628</v>
+      </c>
+      <c r="F26" s="271">
+        <v>3.31111111111111</v>
       </c>
       <c r="G26" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="190" t="s">
         <v>162</v>
       </c>
@@ -12395,114 +12055,114 @@
         <v>419</v>
       </c>
       <c r="C27" s="191" t="s">
-        <v>459</v>
+        <v>352</v>
       </c>
       <c r="D27" s="192" t="s">
-        <v>460</v>
+        <v>353</v>
       </c>
       <c r="E27" s="193" t="s">
         <v>638</v>
       </c>
       <c r="F27" s="194">
-        <v>4.666666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="G27" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" s="190" t="s">
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="145" t="s">
         <v>419</v>
       </c>
-      <c r="C28" s="191" t="s">
-        <v>237</v>
-      </c>
-      <c r="D28" s="192" t="s">
-        <v>238</v>
-      </c>
-      <c r="E28" s="193" t="s">
+      <c r="C28" s="177" t="s">
+        <v>360</v>
+      </c>
+      <c r="D28" s="180" t="s">
+        <v>361</v>
+      </c>
+      <c r="E28" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F28" s="271">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G28" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C29" s="177" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="180" t="s">
+        <v>363</v>
+      </c>
+      <c r="E29" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F29" s="271">
+        <v>2.5777777777777802</v>
+      </c>
+      <c r="G29" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>465</v>
+      </c>
+      <c r="D30" s="180" t="s">
+        <v>466</v>
+      </c>
+      <c r="E30" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F30" s="271">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G30" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="190" t="s">
+        <v>419</v>
+      </c>
+      <c r="C31" s="191" t="s">
+        <v>375</v>
+      </c>
+      <c r="D31" s="192" t="s">
+        <v>376</v>
+      </c>
+      <c r="E31" s="193" t="s">
         <v>638</v>
       </c>
-      <c r="F28" s="194">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G28" s="195">
+      <c r="F31" s="194">
+        <v>5.5</v>
+      </c>
+      <c r="G31" s="195">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B29" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C29" s="191" t="s">
-        <v>328</v>
-      </c>
-      <c r="D29" s="192" t="s">
-        <v>329</v>
-      </c>
-      <c r="E29" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F29" s="194">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G29" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B30" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C30" s="191" t="s">
-        <v>241</v>
-      </c>
-      <c r="D30" s="192" t="s">
-        <v>242</v>
-      </c>
-      <c r="E30" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F30" s="194">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G30" s="195">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C31" s="177" t="s">
-        <v>338</v>
-      </c>
-      <c r="D31" s="180" t="s">
-        <v>339</v>
-      </c>
-      <c r="E31" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F31" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G31" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="145" t="s">
         <v>162</v>
       </c>
@@ -12510,22 +12170,22 @@
         <v>419</v>
       </c>
       <c r="C32" s="177" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="D32" s="180" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="E32" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F32" s="203">
-        <v>2.5777777777777802</v>
+        <v>655</v>
+      </c>
+      <c r="F32" s="271">
+        <v>1.0311111111111111</v>
       </c>
       <c r="G32" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -12533,22 +12193,22 @@
         <v>419</v>
       </c>
       <c r="C33" s="177" t="s">
-        <v>344</v>
+        <v>387</v>
       </c>
       <c r="D33" s="180" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="E33" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F33" s="203">
-        <v>4.76</v>
+        <v>637</v>
+      </c>
+      <c r="F33" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G33" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
@@ -12556,91 +12216,91 @@
         <v>419</v>
       </c>
       <c r="C34" s="177" t="s">
-        <v>346</v>
+        <v>469</v>
       </c>
       <c r="D34" s="180" t="s">
-        <v>347</v>
+        <v>470</v>
       </c>
       <c r="E34" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F34" s="203">
-        <v>5</v>
+        <v>630</v>
+      </c>
+      <c r="F34" s="271">
+        <v>4.63657407407407</v>
       </c>
       <c r="G34" s="149">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="145" t="s">
+    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C35" s="177" t="s">
-        <v>461</v>
-      </c>
-      <c r="D35" s="180" t="s">
-        <v>462</v>
-      </c>
-      <c r="E35" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F35" s="203">
-        <v>3.31111111111111</v>
-      </c>
-      <c r="G35" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B36" s="145" t="s">
+      <c r="C35" s="191" t="s">
+        <v>393</v>
+      </c>
+      <c r="D35" s="192" t="s">
+        <v>394</v>
+      </c>
+      <c r="E35" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F35" s="194">
+        <v>5.5</v>
+      </c>
+      <c r="G35" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C36" s="177" t="s">
-        <v>350</v>
-      </c>
-      <c r="D36" s="180" t="s">
-        <v>351</v>
-      </c>
-      <c r="E36" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F36" s="203">
-        <v>1.54666666666667</v>
-      </c>
-      <c r="G36" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B37" s="190" t="s">
+      <c r="C36" s="191" t="s">
+        <v>395</v>
+      </c>
+      <c r="D36" s="192" t="s">
+        <v>396</v>
+      </c>
+      <c r="E36" s="193" t="s">
+        <v>638</v>
+      </c>
+      <c r="F36" s="194">
+        <v>5.5</v>
+      </c>
+      <c r="G36" s="195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="145" t="s">
         <v>419</v>
       </c>
-      <c r="C37" s="191" t="s">
-        <v>352</v>
-      </c>
-      <c r="D37" s="192" t="s">
-        <v>353</v>
-      </c>
-      <c r="E37" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F37" s="194">
-        <v>5.5</v>
-      </c>
-      <c r="G37" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C37" s="177" t="s">
+        <v>397</v>
+      </c>
+      <c r="D37" s="180" t="s">
+        <v>398</v>
+      </c>
+      <c r="E37" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F37" s="271">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G37" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="145" t="s">
         <v>162</v>
       </c>
@@ -12648,68 +12308,68 @@
         <v>419</v>
       </c>
       <c r="C38" s="177" t="s">
-        <v>358</v>
+        <v>471</v>
       </c>
       <c r="D38" s="180" t="s">
-        <v>359</v>
+        <v>472</v>
       </c>
       <c r="E38" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F38" s="203">
-        <v>4.1666666666666696</v>
+        <v>635</v>
+      </c>
+      <c r="F38" s="271">
+        <v>3</v>
       </c>
       <c r="G38" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B39" s="145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C39" s="177" t="s">
-        <v>360</v>
-      </c>
-      <c r="D39" s="180" t="s">
-        <v>361</v>
-      </c>
-      <c r="E39" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F39" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G39" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B40" s="145" t="s">
+      <c r="C39" s="191" t="s">
+        <v>403</v>
+      </c>
+      <c r="D39" s="192" t="s">
+        <v>404</v>
+      </c>
+      <c r="E39" s="193" t="s">
+        <v>657</v>
+      </c>
+      <c r="F39" s="194">
+        <v>15</v>
+      </c>
+      <c r="G39" s="195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="190" t="s">
         <v>419</v>
       </c>
-      <c r="C40" s="177" t="s">
-        <v>362</v>
-      </c>
-      <c r="D40" s="180" t="s">
-        <v>363</v>
-      </c>
-      <c r="E40" s="186" t="s">
-        <v>634</v>
-      </c>
-      <c r="F40" s="203">
-        <v>2.5777777777777802</v>
-      </c>
-      <c r="G40" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="C40" s="191" t="s">
+        <v>407</v>
+      </c>
+      <c r="D40" s="192" t="s">
+        <v>408</v>
+      </c>
+      <c r="E40" s="193" t="s">
+        <v>656</v>
+      </c>
+      <c r="F40" s="194">
+        <v>12.166666666666666</v>
+      </c>
+      <c r="G40" s="195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="145" t="s">
         <v>162</v>
       </c>
@@ -12717,512 +12377,167 @@
         <v>419</v>
       </c>
       <c r="C41" s="177" t="s">
-        <v>366</v>
+        <v>415</v>
       </c>
       <c r="D41" s="180" t="s">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="E41" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F41" s="203">
-        <v>4.76</v>
+        <v>637</v>
+      </c>
+      <c r="F41" s="271">
+        <v>1.1047619047618999</v>
       </c>
       <c r="G41" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C42" s="177" t="s">
-        <v>368</v>
-      </c>
-      <c r="D42" s="180" t="s">
-        <v>369</v>
-      </c>
-      <c r="E42" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F42" s="203">
-        <v>5</v>
-      </c>
-      <c r="G42" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C43" s="177" t="s">
-        <v>465</v>
-      </c>
-      <c r="D43" s="180" t="s">
-        <v>466</v>
-      </c>
-      <c r="E43" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F43" s="203">
-        <v>3.31111111111111</v>
-      </c>
-      <c r="G43" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B44" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C44" s="177" t="s">
-        <v>373</v>
-      </c>
-      <c r="D44" s="180" t="s">
-        <v>374</v>
-      </c>
-      <c r="E44" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F44" s="203">
-        <v>1.54666666666667</v>
-      </c>
-      <c r="G44" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B45" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C45" s="191" t="s">
-        <v>375</v>
-      </c>
-      <c r="D45" s="192" t="s">
-        <v>376</v>
-      </c>
-      <c r="E45" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F45" s="194">
-        <v>5.5</v>
-      </c>
-      <c r="G45" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B46" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C46" s="177" t="s">
-        <v>381</v>
-      </c>
-      <c r="D46" s="180" t="s">
-        <v>382</v>
-      </c>
-      <c r="E46" s="186" t="s">
-        <v>628</v>
-      </c>
-      <c r="F46" s="203">
-        <v>4.1666666666666696</v>
-      </c>
-      <c r="G46" s="149">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C47" s="177" t="s">
-        <v>385</v>
-      </c>
-      <c r="D47" s="180" t="s">
-        <v>386</v>
-      </c>
-      <c r="E47" s="186" t="s">
-        <v>636</v>
-      </c>
-      <c r="F47" s="203">
-        <v>1.0311111111111111</v>
-      </c>
-      <c r="G47" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C48" s="177" t="s">
-        <v>387</v>
-      </c>
-      <c r="D48" s="180" t="s">
-        <v>388</v>
-      </c>
-      <c r="E48" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F48" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G48" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C49" s="177" t="s">
-        <v>469</v>
-      </c>
-      <c r="D49" s="180" t="s">
-        <v>470</v>
-      </c>
-      <c r="E49" s="186" t="s">
-        <v>630</v>
-      </c>
-      <c r="F49" s="203">
-        <v>4.63657407407407</v>
-      </c>
-      <c r="G49" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B50" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C50" s="191" t="s">
-        <v>393</v>
-      </c>
-      <c r="D50" s="192" t="s">
-        <v>394</v>
-      </c>
-      <c r="E50" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F50" s="194">
-        <v>5.5</v>
-      </c>
-      <c r="G50" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C51" s="191" t="s">
-        <v>395</v>
-      </c>
-      <c r="D51" s="192" t="s">
-        <v>396</v>
-      </c>
-      <c r="E51" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F51" s="194">
-        <v>5.5</v>
-      </c>
-      <c r="G51" s="195">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C52" s="177" t="s">
-        <v>397</v>
-      </c>
-      <c r="D52" s="180" t="s">
-        <v>398</v>
-      </c>
-      <c r="E52" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F52" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G52" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C53" s="177" t="s">
-        <v>471</v>
-      </c>
-      <c r="D53" s="180" t="s">
-        <v>472</v>
-      </c>
-      <c r="E53" s="186" t="s">
-        <v>635</v>
-      </c>
-      <c r="F53" s="203">
-        <v>3</v>
-      </c>
-      <c r="G53" s="149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C54" s="191" t="s">
-        <v>403</v>
-      </c>
-      <c r="D54" s="192" t="s">
-        <v>404</v>
-      </c>
-      <c r="E54" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F54" s="194">
-        <v>15</v>
-      </c>
-      <c r="G54" s="195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="190" t="s">
-        <v>162</v>
-      </c>
-      <c r="B55" s="190" t="s">
-        <v>419</v>
-      </c>
-      <c r="C55" s="191" t="s">
-        <v>407</v>
-      </c>
-      <c r="D55" s="192" t="s">
-        <v>408</v>
-      </c>
-      <c r="E55" s="193" t="s">
-        <v>638</v>
-      </c>
-      <c r="F55" s="194">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="G55" s="195">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="145" t="s">
-        <v>162</v>
-      </c>
-      <c r="B56" s="145" t="s">
-        <v>419</v>
-      </c>
-      <c r="C56" s="177" t="s">
-        <v>415</v>
-      </c>
-      <c r="D56" s="180" t="s">
-        <v>416</v>
-      </c>
-      <c r="E56" s="186" t="s">
-        <v>637</v>
-      </c>
-      <c r="F56" s="203">
-        <v>1.1047619047618999</v>
-      </c>
-      <c r="G56" s="149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F42" s="151"/>
+      <c r="G42" s="152"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="151"/>
+      <c r="G43" s="152"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="151"/>
+      <c r="G44" s="152"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F45" s="151"/>
+      <c r="G45" s="152"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F46" s="151"/>
+      <c r="G46" s="152"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="151"/>
+      <c r="G47" s="152"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F48" s="151"/>
+      <c r="G48" s="152"/>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F49" s="151"/>
+      <c r="G49" s="152"/>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F50" s="151"/>
+      <c r="G50" s="152"/>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F51" s="151"/>
+      <c r="G51" s="152"/>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F52" s="151"/>
+      <c r="G52" s="152"/>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F53" s="151"/>
+      <c r="G53" s="152"/>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F54" s="151"/>
+      <c r="G54" s="152"/>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F55" s="151"/>
+      <c r="G55" s="152"/>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F56" s="151"/>
+      <c r="G56" s="152"/>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F57" s="151"/>
       <c r="G57" s="152"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F58" s="151"/>
       <c r="G58" s="152"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F59" s="151"/>
       <c r="G59" s="152"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F60" s="151"/>
       <c r="G60" s="152"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F61" s="151"/>
       <c r="G61" s="152"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F62" s="151"/>
       <c r="G62" s="152"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F63" s="151"/>
       <c r="G63" s="152"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F64" s="151"/>
       <c r="G64" s="152"/>
     </row>
-    <row r="65" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F65" s="151"/>
       <c r="G65" s="152"/>
     </row>
-    <row r="66" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F66" s="151"/>
       <c r="G66" s="152"/>
     </row>
-    <row r="67" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F67" s="151"/>
       <c r="G67" s="152"/>
     </row>
-    <row r="68" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F68" s="151"/>
       <c r="G68" s="152"/>
     </row>
-    <row r="69" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F69" s="151"/>
       <c r="G69" s="152"/>
     </row>
-    <row r="70" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F70" s="151"/>
       <c r="G70" s="152"/>
     </row>
-    <row r="71" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F71" s="151"/>
       <c r="G71" s="152"/>
     </row>
-    <row r="72" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F72" s="151"/>
       <c r="G72" s="152"/>
     </row>
-    <row r="73" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F73" s="151"/>
       <c r="G73" s="152"/>
     </row>
-    <row r="74" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F74" s="151"/>
       <c r="G74" s="152"/>
     </row>
-    <row r="75" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F75" s="151"/>
       <c r="G75" s="152"/>
     </row>
-    <row r="76" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F76" s="151"/>
       <c r="G76" s="152"/>
     </row>
-    <row r="77" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F77" s="151"/>
       <c r="G77" s="152"/>
     </row>
-    <row r="78" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F78" s="151"/>
-      <c r="G78" s="152"/>
-    </row>
-    <row r="79" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F79" s="151"/>
-      <c r="G79" s="152"/>
-    </row>
-    <row r="80" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F80" s="151"/>
-      <c r="G80" s="152"/>
-    </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F81" s="151"/>
-      <c r="G81" s="152"/>
-    </row>
-    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F82" s="151"/>
-      <c r="G82" s="152"/>
-    </row>
-    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F83" s="151"/>
-      <c r="G83" s="152"/>
-    </row>
-    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F84" s="151"/>
-      <c r="G84" s="152"/>
-    </row>
-    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F85" s="151"/>
-      <c r="G85" s="152"/>
-    </row>
-    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F86" s="151"/>
-      <c r="G86" s="152"/>
-    </row>
-    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F87" s="151"/>
-      <c r="G87" s="152"/>
-    </row>
-    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F88" s="151"/>
-      <c r="G88" s="152"/>
-    </row>
-    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F89" s="151"/>
-      <c r="G89" s="152"/>
-    </row>
-    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F90" s="151"/>
-      <c r="G90" s="152"/>
-    </row>
-    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F91" s="151"/>
-      <c r="G91" s="152"/>
-    </row>
-    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F92" s="151"/>
-      <c r="G92" s="152"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G92" xr:uid="{E3665249-3B56-4736-82A3-8BF617843F28}"/>
+  <autoFilter ref="A1:G77" xr:uid="{E3665249-3B56-4736-82A3-8BF617843F28}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13235,31 +12550,31 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE127"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="147" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="147" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="147" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="147" customWidth="1"/>
-    <col min="6" max="15" width="13.875" style="150" customWidth="1"/>
-    <col min="16" max="17" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="5.375" style="147" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.375" style="147" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="8.875" style="147"/>
+    <col min="5" max="5" width="13.33203125" style="147" customWidth="1"/>
+    <col min="6" max="15" width="13.88671875" style="150" customWidth="1"/>
+    <col min="16" max="17" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="5.33203125" style="147" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.33203125" style="147" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="8.88671875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -13354,7 +12669,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -13429,7 +12744,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -13512,7 +12827,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="145" t="s">
         <v>162</v>
       </c>
@@ -13589,7 +12904,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -13664,7 +12979,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -13739,7 +13054,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -13814,7 +13129,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="145" t="s">
         <v>162</v>
       </c>
@@ -13889,7 +13204,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="145" t="s">
         <v>162</v>
       </c>
@@ -13976,7 +13291,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -14051,7 +13366,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="145" t="s">
         <v>162</v>
       </c>
@@ -14126,7 +13441,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="12" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="145" t="s">
         <v>162</v>
       </c>
@@ -14203,7 +13518,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="144" customFormat="1" ht="12.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="144" customFormat="1" ht="12.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="145" t="s">
         <v>162</v>
       </c>
@@ -14278,7 +13593,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="144" customFormat="1" ht="27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" s="144" customFormat="1" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -14355,7 +13670,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -14432,7 +13747,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="16" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
@@ -14507,7 +13822,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="17" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="145" t="s">
         <v>162</v>
       </c>
@@ -14582,7 +13897,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="18" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="145" t="s">
         <v>162</v>
       </c>
@@ -14657,7 +13972,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="19" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="145" t="s">
         <v>162</v>
       </c>
@@ -14732,7 +14047,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="20" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="145" t="s">
         <v>162</v>
       </c>
@@ -14807,7 +14122,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="21" spans="1:31" s="144" customFormat="1" ht="27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" s="144" customFormat="1" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="145" t="s">
         <v>162</v>
       </c>
@@ -14884,7 +14199,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="22" spans="1:31" s="144" customFormat="1" ht="27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" s="144" customFormat="1" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="145" t="s">
         <v>162</v>
       </c>
@@ -14961,7 +14276,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="23" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="145" t="s">
         <v>162</v>
       </c>
@@ -15038,7 +14353,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="24" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="145" t="s">
         <v>162</v>
       </c>
@@ -15117,7 +14432,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="25" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="145" t="s">
         <v>162</v>
       </c>
@@ -15196,7 +14511,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -15271,7 +14586,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="27" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="145" t="s">
         <v>162</v>
       </c>
@@ -15346,7 +14661,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="145" t="s">
         <v>162</v>
       </c>
@@ -15421,7 +14736,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="145" t="s">
         <v>162</v>
       </c>
@@ -15496,7 +14811,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="30" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="145" t="s">
         <v>162</v>
       </c>
@@ -15571,7 +14886,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="31" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="145" t="s">
         <v>162</v>
       </c>
@@ -15646,7 +14961,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="32" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="145" t="s">
         <v>162</v>
       </c>
@@ -15723,7 +15038,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="33" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -15798,7 +15113,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="34" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
@@ -15873,7 +15188,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="35" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="145" t="s">
         <v>162</v>
       </c>
@@ -15948,7 +15263,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="36" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="145" t="s">
         <v>162</v>
       </c>
@@ -16023,7 +15338,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="37" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="145" t="s">
         <v>162</v>
       </c>
@@ -16098,7 +15413,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="38" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="145" t="s">
         <v>162</v>
       </c>
@@ -16173,7 +15488,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="145" t="s">
         <v>162</v>
       </c>
@@ -16248,7 +15563,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="40" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="145" t="s">
         <v>162</v>
       </c>
@@ -16323,7 +15638,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="41" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="145" t="s">
         <v>162</v>
       </c>
@@ -16398,7 +15713,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="42" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="145" t="s">
         <v>162</v>
       </c>
@@ -16473,7 +15788,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="43" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="145" t="s">
         <v>162</v>
       </c>
@@ -16548,7 +15863,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="44" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="145" t="s">
         <v>162</v>
       </c>
@@ -16625,7 +15940,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="145" t="s">
         <v>162</v>
       </c>
@@ -16700,7 +16015,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="46" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="145" t="s">
         <v>162</v>
       </c>
@@ -16775,7 +16090,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="145" t="s">
         <v>162</v>
       </c>
@@ -16850,7 +16165,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="48" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="145" t="s">
         <v>162</v>
       </c>
@@ -16937,7 +16252,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="49" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="145" t="s">
         <v>162</v>
       </c>
@@ -17012,7 +16327,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="50" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="145" t="s">
         <v>162</v>
       </c>
@@ -17089,7 +16404,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="51" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="145" t="s">
         <v>162</v>
       </c>
@@ -17164,7 +16479,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="52" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="145" t="s">
         <v>162</v>
       </c>
@@ -17241,7 +16556,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="53" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="145" t="s">
         <v>162</v>
       </c>
@@ -17316,7 +16631,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="54" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="145" t="s">
         <v>162</v>
       </c>
@@ -17391,7 +16706,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="145" t="s">
         <v>162</v>
       </c>
@@ -17468,7 +16783,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="56" spans="1:31" s="144" customFormat="1" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" s="144" customFormat="1" ht="13.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="145" t="s">
         <v>162</v>
       </c>
@@ -17555,7 +16870,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="57" spans="1:31" s="144" customFormat="1" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" s="144" customFormat="1" ht="13.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="145" t="s">
         <v>162</v>
       </c>
@@ -17630,7 +16945,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="58" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="145" t="s">
         <v>162</v>
       </c>
@@ -17705,7 +17020,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="59" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="145" t="s">
         <v>162</v>
       </c>
@@ -17780,7 +17095,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="60" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="145" t="s">
         <v>162</v>
       </c>
@@ -17855,7 +17170,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="61" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="145" t="s">
         <v>162</v>
       </c>
@@ -17930,7 +17245,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="62" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="145" t="s">
         <v>162</v>
       </c>
@@ -18017,7 +17332,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="63" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="145" t="s">
         <v>162</v>
       </c>
@@ -18094,7 +17409,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="64" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="145" t="s">
         <v>162</v>
       </c>
@@ -18169,7 +17484,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="65" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="145" t="s">
         <v>162</v>
       </c>
@@ -18244,7 +17559,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="66" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="145" t="s">
         <v>162</v>
       </c>
@@ -18319,7 +17634,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="67" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="145" t="s">
         <v>162</v>
       </c>
@@ -18394,7 +17709,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="68" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="145" t="s">
         <v>162</v>
       </c>
@@ -18471,7 +17786,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="69" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="145" t="s">
         <v>162</v>
       </c>
@@ -18548,7 +17863,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="70" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="145" t="s">
         <v>162</v>
       </c>
@@ -18627,7 +17942,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="71" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="145" t="s">
         <v>162</v>
       </c>
@@ -18706,7 +18021,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="72" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="145" t="s">
         <v>162</v>
       </c>
@@ -18781,7 +18096,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="73" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="145" t="s">
         <v>162</v>
       </c>
@@ -18856,7 +18171,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="74" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="145" t="s">
         <v>162</v>
       </c>
@@ -18931,7 +18246,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="75" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="145" t="s">
         <v>162</v>
       </c>
@@ -19006,7 +18321,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="76" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="145" t="s">
         <v>162</v>
       </c>
@@ -19081,7 +18396,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="77" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="145" t="s">
         <v>162</v>
       </c>
@@ -19156,7 +18471,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="78" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="145" t="s">
         <v>162</v>
       </c>
@@ -19233,7 +18548,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="79" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="145" t="s">
         <v>162</v>
       </c>
@@ -19308,7 +18623,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="80" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="145" t="s">
         <v>162</v>
       </c>
@@ -19383,7 +18698,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="81" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="145" t="s">
         <v>162</v>
       </c>
@@ -19458,7 +18773,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="82" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="145" t="s">
         <v>162</v>
       </c>
@@ -19533,7 +18848,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="83" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="145" t="s">
         <v>162</v>
       </c>
@@ -19608,7 +18923,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="84" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A84" s="145" t="s">
         <v>162</v>
       </c>
@@ -19683,7 +18998,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="85" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="145" t="s">
         <v>162</v>
       </c>
@@ -19758,7 +19073,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="86" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="145" t="s">
         <v>162</v>
       </c>
@@ -19833,7 +19148,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="87" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="145" t="s">
         <v>162</v>
       </c>
@@ -19908,7 +19223,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="88" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="145" t="s">
         <v>162</v>
       </c>
@@ -19985,7 +19300,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="89" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="145" t="s">
         <v>162</v>
       </c>
@@ -20060,7 +19375,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="90" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="145" t="s">
         <v>162</v>
       </c>
@@ -20135,7 +19450,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="91" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="145" t="s">
         <v>162</v>
       </c>
@@ -20212,7 +19527,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="92" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="145" t="s">
         <v>162</v>
       </c>
@@ -20299,7 +19614,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="93" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="145" t="s">
         <v>162</v>
       </c>
@@ -20374,7 +19689,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="94" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="145" t="s">
         <v>162</v>
       </c>
@@ -20449,7 +19764,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="95" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="145" t="s">
         <v>162</v>
       </c>
@@ -20524,7 +19839,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="96" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="145" t="s">
         <v>162</v>
       </c>
@@ -20599,7 +19914,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="97" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="145" t="s">
         <v>162</v>
       </c>
@@ -20674,7 +19989,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="98" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="145" t="s">
         <v>162</v>
       </c>
@@ -20761,7 +20076,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="99" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="145" t="s">
         <v>162</v>
       </c>
@@ -20838,7 +20153,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="100" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="145" t="s">
         <v>162</v>
       </c>
@@ -20913,7 +20228,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="101" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="145" t="s">
         <v>162</v>
       </c>
@@ -20988,7 +20303,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="102" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="145" t="s">
         <v>162</v>
       </c>
@@ -21065,7 +20380,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="103" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="145" t="s">
         <v>162</v>
       </c>
@@ -21154,7 +20469,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="104" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="145" t="s">
         <v>162</v>
       </c>
@@ -21229,7 +20544,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="105" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="145" t="s">
         <v>162</v>
       </c>
@@ -21304,7 +20619,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="106" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="145" t="s">
         <v>162</v>
       </c>
@@ -21379,7 +20694,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="107" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="145" t="s">
         <v>162</v>
       </c>
@@ -21454,7 +20769,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="108" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="145" t="s">
         <v>162</v>
       </c>
@@ -21529,7 +20844,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="109" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="145" t="s">
         <v>162</v>
       </c>
@@ -21616,7 +20931,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="110" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="145" t="s">
         <v>162</v>
       </c>
@@ -21693,7 +21008,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="111" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="145" t="s">
         <v>162</v>
       </c>
@@ -21768,7 +21083,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="112" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="145" t="s">
         <v>162</v>
       </c>
@@ -21845,7 +21160,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="113" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="145" t="s">
         <v>162</v>
       </c>
@@ -21920,7 +21235,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="114" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="145" t="s">
         <v>162</v>
       </c>
@@ -21995,7 +21310,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="115" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="145" t="s">
         <v>162</v>
       </c>
@@ -22070,7 +21385,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="116" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="145" t="s">
         <v>162</v>
       </c>
@@ -22145,7 +21460,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="117" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="145" t="s">
         <v>162</v>
       </c>
@@ -22222,7 +21537,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="118" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="145" t="s">
         <v>162</v>
       </c>
@@ -22297,7 +21612,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="119" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="145" t="s">
         <v>162</v>
       </c>
@@ -22372,7 +21687,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="120" spans="1:31" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="145" t="s">
         <v>162</v>
       </c>
@@ -22447,7 +21762,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="121" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="145" t="s">
         <v>162</v>
       </c>
@@ -22522,7 +21837,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="122" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="145" t="s">
         <v>162</v>
       </c>
@@ -22597,7 +21912,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="123" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="145" t="s">
         <v>162</v>
       </c>
@@ -22672,7 +21987,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="124" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="145" t="s">
         <v>162</v>
       </c>
@@ -22747,7 +22062,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="125" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="145" t="s">
         <v>162</v>
       </c>
@@ -22822,7 +22137,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="126" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="145" t="s">
         <v>162</v>
       </c>
@@ -22899,7 +22214,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="127" spans="1:31" s="144" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" s="144" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="145" t="s">
         <v>162</v>
       </c>
@@ -23006,30 +22321,30 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AF126"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.5" style="147" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.44140625" style="147" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="147" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="150" customWidth="1"/>
-    <col min="6" max="16" width="13.875" style="150" customWidth="1"/>
-    <col min="17" max="18" width="9.625" style="147" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="150" customWidth="1"/>
+    <col min="6" max="16" width="13.88671875" style="150" customWidth="1"/>
+    <col min="17" max="18" width="9.6640625" style="147" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" style="147" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14" style="147" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.875" style="147" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.125" style="147" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="5.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.5" style="147" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.625" style="147" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.25" style="147" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.625" style="147" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="8.875" style="147"/>
+    <col min="21" max="21" width="13.88671875" style="147" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="9.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="5.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.44140625" style="147" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.6640625" style="147" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.6640625" style="147" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="8.88671875" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="144" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="143" t="s">
         <v>142</v>
       </c>
@@ -23127,7 +22442,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="145" t="s">
         <v>162</v>
       </c>
@@ -23203,7 +22518,7 @@
         <v>735772</v>
       </c>
     </row>
-    <row r="3" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="145" t="s">
         <v>162</v>
       </c>
@@ -23287,7 +22602,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="4" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="145" t="s">
         <v>162</v>
       </c>
@@ -23365,7 +22680,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
         <v>162</v>
       </c>
@@ -23441,7 +22756,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="6" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
@@ -23518,7 +22833,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="145" t="s">
         <v>162</v>
       </c>
@@ -23595,7 +22910,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="145" t="s">
         <v>162</v>
       </c>
@@ -23671,7 +22986,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="9" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="145" t="s">
         <v>162</v>
       </c>
@@ -23759,7 +23074,7 @@
         <v>735772</v>
       </c>
     </row>
-    <row r="10" spans="1:32" s="144" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" s="144" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="145" t="s">
         <v>162</v>
       </c>
@@ -23835,7 +23150,7 @@
         <v>735772</v>
       </c>
     </row>
-    <row r="11" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="145" t="s">
         <v>162</v>
       </c>
@@ -23923,7 +23238,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="12" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="145" t="s">
         <v>162</v>
       </c>
@@ -23999,7 +23314,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="145" t="s">
         <v>162</v>
       </c>
@@ -24077,7 +23392,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="145" t="s">
         <v>162</v>
       </c>
@@ -24153,7 +23468,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="15" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="145" t="s">
         <v>162</v>
       </c>
@@ -24230,7 +23545,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="145" t="s">
         <v>162</v>
       </c>
@@ -24306,7 +23621,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="17" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="145" t="s">
         <v>162</v>
       </c>
@@ -24394,7 +23709,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="18" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="145" t="s">
         <v>162</v>
       </c>
@@ -24472,7 +23787,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="19" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="145" t="s">
         <v>162</v>
       </c>
@@ -24550,7 +23865,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="20" spans="1:32" s="144" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" s="144" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="145" t="s">
         <v>162</v>
       </c>
@@ -24626,7 +23941,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="21" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="145" t="s">
         <v>162</v>
       </c>
@@ -24704,7 +24019,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="22" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="145" t="s">
         <v>162</v>
       </c>
@@ -24782,7 +24097,7 @@
         <v>765042</v>
       </c>
     </row>
-    <row r="23" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="145" t="s">
         <v>162</v>
       </c>
@@ -24858,7 +24173,7 @@
         <v>765042</v>
       </c>
     </row>
-    <row r="24" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="145" t="s">
         <v>162</v>
       </c>
@@ -24934,7 +24249,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="25" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="145" t="s">
         <v>162</v>
       </c>
@@ -25010,7 +24325,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="26" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="145" t="s">
         <v>162</v>
       </c>
@@ -25086,7 +24401,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="27" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="145" t="s">
         <v>162</v>
       </c>
@@ -25162,7 +24477,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="28" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="145" t="s">
         <v>162</v>
       </c>
@@ -25237,7 +24552,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="29" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="145" t="s">
         <v>162</v>
       </c>
@@ -25315,7 +24630,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="30" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="145" t="s">
         <v>162</v>
       </c>
@@ -25393,7 +24708,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="145" t="s">
         <v>162</v>
       </c>
@@ -25473,7 +24788,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="145" t="s">
         <v>162</v>
       </c>
@@ -25553,7 +24868,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="33" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="145" t="s">
         <v>162</v>
       </c>
@@ -25629,7 +24944,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="34" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="145" t="s">
         <v>162</v>
       </c>
@@ -25705,7 +25020,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="35" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="145" t="s">
         <v>162</v>
       </c>
@@ -25781,7 +25096,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="36" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="145" t="s">
         <v>162</v>
       </c>
@@ -25857,7 +25172,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="37" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="145" t="s">
         <v>162</v>
       </c>
@@ -25933,7 +25248,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="38" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="145" t="s">
         <v>162</v>
       </c>
@@ -26009,7 +25324,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="39" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="145" t="s">
         <v>162</v>
       </c>
@@ -26087,7 +25402,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="40" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="145" t="s">
         <v>162</v>
       </c>
@@ -26163,7 +25478,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="41" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="145" t="s">
         <v>162</v>
       </c>
@@ -26239,7 +25554,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="42" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="145" t="s">
         <v>162</v>
       </c>
@@ -26315,7 +25630,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="43" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="145" t="s">
         <v>162</v>
       </c>
@@ -26391,7 +25706,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="44" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A44" s="145" t="s">
         <v>162</v>
       </c>
@@ -26467,7 +25782,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="45" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A45" s="145" t="s">
         <v>162</v>
       </c>
@@ -26543,7 +25858,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="46" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A46" s="145" t="s">
         <v>162</v>
       </c>
@@ -26619,7 +25934,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="47" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="145" t="s">
         <v>162</v>
       </c>
@@ -26695,7 +26010,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="48" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="145" t="s">
         <v>162</v>
       </c>
@@ -26771,7 +26086,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="49" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="145" t="s">
         <v>162</v>
       </c>
@@ -26847,7 +26162,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="50" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="145" t="s">
         <v>162</v>
       </c>
@@ -26923,7 +26238,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="51" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="145" t="s">
         <v>162</v>
       </c>
@@ -27001,7 +26316,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="145" t="s">
         <v>162</v>
       </c>
@@ -27077,7 +26392,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="53" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="145" t="s">
         <v>162</v>
       </c>
@@ -27154,7 +26469,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="54" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="145" t="s">
         <v>162</v>
       </c>
@@ -27232,7 +26547,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="55" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="145" t="s">
         <v>162</v>
       </c>
@@ -27320,7 +26635,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="56" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="145" t="s">
         <v>162</v>
       </c>
@@ -27396,7 +26711,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="57" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="145" t="s">
         <v>162</v>
       </c>
@@ -27472,7 +26787,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="58" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A58" s="145" t="s">
         <v>162</v>
       </c>
@@ -27548,7 +26863,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="59" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="145" t="s">
         <v>162</v>
       </c>
@@ -27624,7 +26939,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="60" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="145" t="s">
         <v>162</v>
       </c>
@@ -27700,7 +27015,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="61" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="145" t="s">
         <v>162</v>
       </c>
@@ -27788,7 +27103,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="62" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="145" t="s">
         <v>162</v>
       </c>
@@ -27864,7 +27179,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="63" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="145" t="s">
         <v>162</v>
       </c>
@@ -27942,7 +27257,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="145" t="s">
         <v>162</v>
       </c>
@@ -28018,7 +27333,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="65" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="145" t="s">
         <v>162</v>
       </c>
@@ -28094,7 +27409,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="145" t="s">
         <v>162</v>
       </c>
@@ -28174,7 +27489,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="67" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="145" t="s">
         <v>162</v>
       </c>
@@ -28262,7 +27577,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="68" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="145" t="s">
         <v>162</v>
       </c>
@@ -28338,7 +27653,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="69" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="145" t="s">
         <v>162</v>
       </c>
@@ -28414,7 +27729,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="70" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A70" s="145" t="s">
         <v>162</v>
       </c>
@@ -28490,7 +27805,7 @@
         <v>736087</v>
       </c>
     </row>
-    <row r="71" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="145" t="s">
         <v>162</v>
       </c>
@@ -28566,7 +27881,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="72" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="145" t="s">
         <v>162</v>
       </c>
@@ -28642,7 +27957,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="73" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="145" t="s">
         <v>162</v>
       </c>
@@ -28730,7 +28045,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="74" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="145" t="s">
         <v>162</v>
       </c>
@@ -28806,7 +28121,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="75" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="145" t="s">
         <v>162</v>
       </c>
@@ -28882,7 +28197,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="76" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="145" t="s">
         <v>162</v>
       </c>
@@ -28960,7 +28275,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="145" t="s">
         <v>162</v>
       </c>
@@ -29037,7 +28352,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="78" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="145" t="s">
         <v>162</v>
       </c>
@@ -29113,7 +28428,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="79" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A79" s="145" t="s">
         <v>162</v>
       </c>
@@ -29189,7 +28504,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="80" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A80" s="145" t="s">
         <v>162</v>
       </c>
@@ -29265,7 +28580,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="81" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="145" t="s">
         <v>162</v>
       </c>
@@ -29343,7 +28658,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="82" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="145" t="s">
         <v>162</v>
       </c>
@@ -29419,7 +28734,7 @@
         <v>762434</v>
       </c>
     </row>
-    <row r="83" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="145" t="s">
         <v>162</v>
       </c>
@@ -29495,7 +28810,7 @@
         <v>735772</v>
       </c>
     </row>
-    <row r="84" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A84" s="145" t="s">
         <v>162</v>
       </c>
@@ -29571,7 +28886,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="85" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="145" t="s">
         <v>162</v>
       </c>
@@ -29647,7 +28962,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="86" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="145" t="s">
         <v>162</v>
       </c>
@@ -29723,7 +29038,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="87" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A87" s="145" t="s">
         <v>162</v>
       </c>
@@ -29799,7 +29114,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="88" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="145" t="s">
         <v>162</v>
       </c>
@@ -29875,7 +29190,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="89" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A89" s="145" t="s">
         <v>162</v>
       </c>
@@ -29953,7 +29268,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="90" spans="1:32" s="144" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="145" t="s">
         <v>162</v>
       </c>
@@ -30030,7 +29345,7 @@
         <v>752102</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F91" s="151"/>
       <c r="G91" s="152"/>
       <c r="H91" s="152"/>
@@ -30043,7 +29358,7 @@
       <c r="O91" s="152"/>
       <c r="P91" s="152"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F92" s="151"/>
       <c r="G92" s="152"/>
       <c r="H92" s="152"/>
@@ -30056,7 +29371,7 @@
       <c r="O92" s="152"/>
       <c r="P92" s="152"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F93" s="151"/>
       <c r="G93" s="152"/>
       <c r="H93" s="152"/>
@@ -30069,7 +29384,7 @@
       <c r="O93" s="152"/>
       <c r="P93" s="152"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F94" s="151"/>
       <c r="G94" s="152"/>
       <c r="H94" s="152"/>
@@ -30082,7 +29397,7 @@
       <c r="O94" s="152"/>
       <c r="P94" s="152"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F95" s="151"/>
       <c r="G95" s="152"/>
       <c r="H95" s="152"/>
@@ -30095,7 +29410,7 @@
       <c r="O95" s="152"/>
       <c r="P95" s="152"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="F96" s="151"/>
       <c r="G96" s="152"/>
       <c r="H96" s="152"/>
@@ -30108,7 +29423,7 @@
       <c r="O96" s="152"/>
       <c r="P96" s="152"/>
     </row>
-    <row r="97" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F97" s="151"/>
       <c r="G97" s="152"/>
       <c r="H97" s="152"/>
@@ -30121,7 +29436,7 @@
       <c r="O97" s="152"/>
       <c r="P97" s="152"/>
     </row>
-    <row r="98" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F98" s="151"/>
       <c r="G98" s="152"/>
       <c r="H98" s="152"/>
@@ -30134,7 +29449,7 @@
       <c r="O98" s="152"/>
       <c r="P98" s="152"/>
     </row>
-    <row r="99" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F99" s="151"/>
       <c r="G99" s="152"/>
       <c r="H99" s="152"/>
@@ -30147,7 +29462,7 @@
       <c r="O99" s="152"/>
       <c r="P99" s="152"/>
     </row>
-    <row r="100" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F100" s="151"/>
       <c r="G100" s="152"/>
       <c r="H100" s="152"/>
@@ -30160,7 +29475,7 @@
       <c r="O100" s="152"/>
       <c r="P100" s="152"/>
     </row>
-    <row r="101" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F101" s="151"/>
       <c r="G101" s="152"/>
       <c r="H101" s="152"/>
@@ -30173,7 +29488,7 @@
       <c r="O101" s="152"/>
       <c r="P101" s="152"/>
     </row>
-    <row r="102" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F102" s="151"/>
       <c r="G102" s="152"/>
       <c r="H102" s="152"/>
@@ -30186,7 +29501,7 @@
       <c r="O102" s="152"/>
       <c r="P102" s="152"/>
     </row>
-    <row r="103" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F103" s="151"/>
       <c r="G103" s="152"/>
       <c r="H103" s="152"/>
@@ -30199,7 +29514,7 @@
       <c r="O103" s="152"/>
       <c r="P103" s="152"/>
     </row>
-    <row r="104" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F104" s="151"/>
       <c r="G104" s="152"/>
       <c r="H104" s="152"/>
@@ -30212,7 +29527,7 @@
       <c r="O104" s="152"/>
       <c r="P104" s="152"/>
     </row>
-    <row r="105" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F105" s="151"/>
       <c r="G105" s="152"/>
       <c r="H105" s="152"/>
@@ -30225,7 +29540,7 @@
       <c r="O105" s="152"/>
       <c r="P105" s="152"/>
     </row>
-    <row r="106" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F106" s="151"/>
       <c r="G106" s="152"/>
       <c r="H106" s="152"/>
@@ -30238,7 +29553,7 @@
       <c r="O106" s="152"/>
       <c r="P106" s="152"/>
     </row>
-    <row r="107" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F107" s="151"/>
       <c r="G107" s="152"/>
       <c r="H107" s="152"/>
@@ -30251,7 +29566,7 @@
       <c r="O107" s="152"/>
       <c r="P107" s="152"/>
     </row>
-    <row r="108" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F108" s="151"/>
       <c r="G108" s="152"/>
       <c r="H108" s="152"/>
@@ -30264,7 +29579,7 @@
       <c r="O108" s="152"/>
       <c r="P108" s="152"/>
     </row>
-    <row r="109" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F109" s="151"/>
       <c r="G109" s="152"/>
       <c r="H109" s="152"/>
@@ -30277,7 +29592,7 @@
       <c r="O109" s="152"/>
       <c r="P109" s="152"/>
     </row>
-    <row r="110" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F110" s="151"/>
       <c r="G110" s="152"/>
       <c r="H110" s="152"/>
@@ -30290,7 +29605,7 @@
       <c r="O110" s="152"/>
       <c r="P110" s="152"/>
     </row>
-    <row r="111" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F111" s="151"/>
       <c r="G111" s="152"/>
       <c r="H111" s="152"/>
@@ -30303,7 +29618,7 @@
       <c r="O111" s="152"/>
       <c r="P111" s="152"/>
     </row>
-    <row r="112" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F112" s="151"/>
       <c r="G112" s="152"/>
       <c r="H112" s="152"/>
@@ -30316,7 +29631,7 @@
       <c r="O112" s="152"/>
       <c r="P112" s="152"/>
     </row>
-    <row r="113" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F113" s="151"/>
       <c r="G113" s="152"/>
       <c r="H113" s="152"/>
@@ -30329,7 +29644,7 @@
       <c r="O113" s="152"/>
       <c r="P113" s="152"/>
     </row>
-    <row r="114" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F114" s="151"/>
       <c r="G114" s="152"/>
       <c r="H114" s="152"/>
@@ -30342,7 +29657,7 @@
       <c r="O114" s="152"/>
       <c r="P114" s="152"/>
     </row>
-    <row r="115" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F115" s="151"/>
       <c r="G115" s="152"/>
       <c r="H115" s="152"/>
@@ -30355,7 +29670,7 @@
       <c r="O115" s="152"/>
       <c r="P115" s="152"/>
     </row>
-    <row r="116" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F116" s="151"/>
       <c r="G116" s="152"/>
       <c r="H116" s="152"/>
@@ -30368,7 +29683,7 @@
       <c r="O116" s="152"/>
       <c r="P116" s="152"/>
     </row>
-    <row r="117" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F117" s="151"/>
       <c r="G117" s="152"/>
       <c r="H117" s="152"/>
@@ -30381,7 +29696,7 @@
       <c r="O117" s="152"/>
       <c r="P117" s="152"/>
     </row>
-    <row r="118" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F118" s="151"/>
       <c r="G118" s="152"/>
       <c r="H118" s="152"/>
@@ -30394,7 +29709,7 @@
       <c r="O118" s="152"/>
       <c r="P118" s="152"/>
     </row>
-    <row r="119" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F119" s="151"/>
       <c r="G119" s="152"/>
       <c r="H119" s="152"/>
@@ -30407,7 +29722,7 @@
       <c r="O119" s="152"/>
       <c r="P119" s="152"/>
     </row>
-    <row r="120" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F120" s="151"/>
       <c r="G120" s="152"/>
       <c r="H120" s="152"/>
@@ -30420,7 +29735,7 @@
       <c r="O120" s="152"/>
       <c r="P120" s="152"/>
     </row>
-    <row r="121" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F121" s="151"/>
       <c r="G121" s="152"/>
       <c r="H121" s="152"/>
@@ -30433,7 +29748,7 @@
       <c r="O121" s="152"/>
       <c r="P121" s="152"/>
     </row>
-    <row r="122" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F122" s="151"/>
       <c r="G122" s="152"/>
       <c r="H122" s="152"/>
@@ -30446,7 +29761,7 @@
       <c r="O122" s="152"/>
       <c r="P122" s="152"/>
     </row>
-    <row r="123" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F123" s="151"/>
       <c r="G123" s="152"/>
       <c r="H123" s="152"/>
@@ -30459,7 +29774,7 @@
       <c r="O123" s="152"/>
       <c r="P123" s="152"/>
     </row>
-    <row r="124" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F124" s="151"/>
       <c r="G124" s="152"/>
       <c r="H124" s="152"/>
@@ -30472,7 +29787,7 @@
       <c r="O124" s="152"/>
       <c r="P124" s="152"/>
     </row>
-    <row r="125" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F125" s="151"/>
       <c r="G125" s="152"/>
       <c r="H125" s="152"/>
@@ -30485,7 +29800,7 @@
       <c r="O125" s="152"/>
       <c r="P125" s="152"/>
     </row>
-    <row r="126" spans="6:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F126" s="151"/>
       <c r="G126" s="152"/>
       <c r="H126" s="152"/>

--- a/doc/SourceData2.xlsx
+++ b/doc/SourceData2.xlsx
@@ -8,34 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCode\python\ProductionSimulatorDynamic\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51117AF5-F8C8-47F5-AB85-278C3C89F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F46F7BE-547B-4374-9307-64A32C6815FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{42FB03BA-B493-4523-AFA3-A29D55EE9891}"/>
   </bookViews>
   <sheets>
     <sheet name="黃光CT總表" sheetId="2" r:id="rId1"/>
     <sheet name="設備加工上限" sheetId="5" r:id="rId2"/>
-    <sheet name="2代-03SEC CT (2+2)" sheetId="8" r:id="rId3"/>
-    <sheet name="2代-01SG CT (1+1)" sheetId="9" r:id="rId4"/>
-    <sheet name="03SEC CT (2+2)" sheetId="3" r:id="rId5"/>
-    <sheet name="01SG CT (1+1)" sheetId="4" r:id="rId6"/>
+    <sheet name="2代-03SEC CT (2+2)" sheetId="10" r:id="rId3"/>
+    <sheet name="2代-01SG CT (1+1)" sheetId="11" r:id="rId4"/>
+    <sheet name="2代-03SEC CT (2+2)-AOI" sheetId="8" r:id="rId5"/>
+    <sheet name="2代-01SG CT (1+1)-AOI" sheetId="9" r:id="rId6"/>
+    <sheet name="03SEC CT (2+2)" sheetId="3" r:id="rId7"/>
+    <sheet name="01SG CT (1+1)" sheetId="4" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
   </externalReferences>
   <definedNames>
-    <definedName name="___________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="___________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___________gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___________gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="___________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="__________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="__________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__________gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__________gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_________DAT1">#REF!</definedName>
     <definedName name="_________DAT10">#REF!</definedName>
@@ -59,8 +60,8 @@
     <definedName name="_________DAT7">#REF!</definedName>
     <definedName name="_________DAT8">#REF!</definedName>
     <definedName name="_________DAT9">#REF!</definedName>
-    <definedName name="_________gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="_________gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_________gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_________gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_________gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="________DAT23">#REF!</definedName>
     <definedName name="________DAT24">#REF!</definedName>
@@ -72,50 +73,50 @@
     <definedName name="_______DAT25">#REF!</definedName>
     <definedName name="_______DAT26">#REF!</definedName>
     <definedName name="_______DAT27">#REF!</definedName>
-    <definedName name="_______gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="_______gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_______gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_______gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_______gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="______DAT23">#REF!</definedName>
     <definedName name="______DAT24">#REF!</definedName>
     <definedName name="______DAT25">#REF!</definedName>
     <definedName name="______DAT26">#REF!</definedName>
     <definedName name="______DAT27">#REF!</definedName>
-    <definedName name="______gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="______gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="______gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="______gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="______gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="_____AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="_____AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_____AA1" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_____AA1" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_____AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_____DAT23">#REF!</definedName>
     <definedName name="_____DAT24">#REF!</definedName>
     <definedName name="_____DAT25">#REF!</definedName>
     <definedName name="_____DAT26">#REF!</definedName>
     <definedName name="_____DAT27">#REF!</definedName>
-    <definedName name="_____gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="_____gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_____gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_____gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_____gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="____AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="____AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="____AA1" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="____AA1" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="____AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="____DAT23">#REF!</definedName>
     <definedName name="____DAT24">#REF!</definedName>
     <definedName name="____DAT25">#REF!</definedName>
     <definedName name="____DAT26">#REF!</definedName>
     <definedName name="____DAT27">#REF!</definedName>
-    <definedName name="___AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="___AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="___AA1" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="___AA1" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="___AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="___DAT23">#REF!</definedName>
     <definedName name="___DAT24">#REF!</definedName>
     <definedName name="___DAT25">#REF!</definedName>
     <definedName name="___DAT26">#REF!</definedName>
     <definedName name="___DAT27">#REF!</definedName>
-    <definedName name="___gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="___gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="___gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="___gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__1dg1_">#REF!</definedName>
-    <definedName name="__AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="__AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="__AA1" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="__AA1" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="__AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="__DAT23">#REF!</definedName>
     <definedName name="__DAT24">#REF!</definedName>
@@ -171,16 +172,16 @@
     <definedName name="__DAT74">#REF!</definedName>
     <definedName name="__DAT75">#REF!</definedName>
     <definedName name="__dat88">#REF!</definedName>
-    <definedName name="__gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="__gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="__gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="__IntlFixup" hidden="1">TRUE</definedName>
     <definedName name="__SPS1">#REF!</definedName>
     <definedName name="__SPS2">#REF!</definedName>
     <definedName name="__STD12">#REF!</definedName>
     <definedName name="_1dg1_">#REF!</definedName>
-    <definedName name="_AA1" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="_AA1" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_AA1" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="_AA1" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_AA1" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="_DAT1">#REF!</definedName>
     <definedName name="_DAT100">#REF!</definedName>
@@ -238,15 +239,17 @@
     <definedName name="_DAT99">#REF!</definedName>
     <definedName name="_EMS753">#REF!</definedName>
     <definedName name="_Fill" hidden="1">[1]DETAILS!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'01SG CT (1+1)'!$A$1:$AF$126</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03SEC CT (2+2)'!$A$1:$AE$127</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2代-01SG CT (1+1)'!$A$1:$G$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2代-03SEC CT (2+2)'!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'01SG CT (1+1)'!$A$1:$AF$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'03SEC CT (2+2)'!$A$1:$AE$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2代-01SG CT (1+1)'!$A$1:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2代-01SG CT (1+1)-AOI'!$A$1:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2代-03SEC CT (2+2)'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2代-03SEC CT (2+2)-AOI'!$A$1:$G$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">設備加工上限!$A$1:$F$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">黃光CT總表!$B$9:$R$55</definedName>
     <definedName name="_xlnm._FilterDatabase" hidden="1">[2]分類表!$A$18:$B$30</definedName>
-    <definedName name="_gg1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="_gg1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_gg1" localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="_gg1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_gg1" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="_ok3">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
@@ -261,19 +264,19 @@
     <definedName name="_查詢1">#REF!</definedName>
     <definedName name="aaa">#REF!</definedName>
     <definedName name="aaaa">#REF!</definedName>
-    <definedName name="AAAAA" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AAAAA" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAA" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAA" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAAAA" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AAAAAAAAAAAV" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AAAAAAAAAAAV" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAAAAAAAAV" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAAAAAAAAAAV" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAAAAAAAAAAV" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AABB">#REF!</definedName>
     <definedName name="aaddd">#REF!</definedName>
-    <definedName name="AAZ" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AAZ" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAZ" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AAZ" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AAZ" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="ab" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="ab" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ab" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ab" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="ab" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AccessDatabase" hidden="1">"E:\JOB\21日提供資料\Rolling Forecast\Rolling2006002.mdb"</definedName>
     <definedName name="Apr_SAP_saving">#REF!</definedName>
@@ -281,11 +284,11 @@
     <definedName name="asb">#REF!</definedName>
     <definedName name="ASD">#REF!</definedName>
     <definedName name="AVD">#REF!</definedName>
-    <definedName name="ax" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="ax" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ax" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="ax" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="ax" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AZ" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="AZ" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AZ" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="AZ" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="AZ" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="B">#REF!</definedName>
     <definedName name="ballast">#REF!</definedName>
@@ -326,8 +329,8 @@
     <definedName name="da">#REF!</definedName>
     <definedName name="daqe">#REF!</definedName>
     <definedName name="DATA">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
-    <definedName name="DATA1" localSheetId="3">#REF!</definedName>
-    <definedName name="DATA1" localSheetId="2">#REF!</definedName>
+    <definedName name="DATA1" localSheetId="5">#REF!</definedName>
+    <definedName name="DATA1" localSheetId="4">#REF!</definedName>
     <definedName name="DATA1">#REF!</definedName>
     <definedName name="DATA10">#REF!</definedName>
     <definedName name="DATA11">#REF!</definedName>
@@ -420,8 +423,8 @@
     <definedName name="detail">#REF!</definedName>
     <definedName name="df">#REF!</definedName>
     <definedName name="DG">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
-    <definedName name="DGA" localSheetId="3">#REF!</definedName>
-    <definedName name="DGA" localSheetId="2">#REF!</definedName>
+    <definedName name="DGA" localSheetId="5">#REF!</definedName>
+    <definedName name="DGA" localSheetId="4">#REF!</definedName>
     <definedName name="DGA">#REF!</definedName>
     <definedName name="dgg">#REF!</definedName>
     <definedName name="DIIP3ST">#REF!</definedName>
@@ -438,16 +441,16 @@
     <definedName name="eeee">#REF!</definedName>
     <definedName name="END">#REF!</definedName>
     <definedName name="EP_DATA">#REF!</definedName>
-    <definedName name="erty" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="erty" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="erty" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="erty" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="erty" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="fd">#REF!</definedName>
     <definedName name="ff">#REF!</definedName>
     <definedName name="fhg">#REF!</definedName>
     <definedName name="fi">#REF!</definedName>
     <definedName name="filter" hidden="1">[4]分類表!$A$18:$B$30</definedName>
-    <definedName name="Format" localSheetId="3">#REF!</definedName>
-    <definedName name="Format" localSheetId="2">#REF!</definedName>
+    <definedName name="Format" localSheetId="5">#REF!</definedName>
+    <definedName name="Format" localSheetId="4">#REF!</definedName>
     <definedName name="Format">#REF!</definedName>
     <definedName name="Format_MSBU" hidden="1">[1]DETAILS!#REF!</definedName>
     <definedName name="gg">#REF!</definedName>
@@ -466,8 +469,8 @@
     <definedName name="HKG">#REF!</definedName>
     <definedName name="HPQ">#REF!</definedName>
     <definedName name="HTML_CodePage" hidden="1">950</definedName>
-    <definedName name="HTML_Control" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="HTML_Control" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="HTML_Control" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="HTML_Control" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="HTML_Control" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="HTML_Description" hidden="1">""</definedName>
     <definedName name="HTML_Email" hidden="1">""</definedName>
@@ -563,8 +566,8 @@
     <definedName name="ps">#REF!</definedName>
     <definedName name="PSBG">#REF!</definedName>
     <definedName name="PSBG1">#REF!</definedName>
-    <definedName name="PSD20161T" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="PSD20161T" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="PSD20161T" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="PSD20161T" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="PSD20161T" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="q">#REF!</definedName>
     <definedName name="RawData">#REF!</definedName>
@@ -577,20 +580,20 @@
     <definedName name="Revised_ISR_Date">#REF!</definedName>
     <definedName name="Revision_Level">#REF!</definedName>
     <definedName name="rr">#REF!</definedName>
-    <definedName name="RT2C" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="RT2C" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="RT2C" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="RT2C" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="RT2C" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="s">#REF!</definedName>
     <definedName name="SALMIN">[5]TT!$U$21</definedName>
     <definedName name="SALMINDF">[5]TT!$U$20</definedName>
-    <definedName name="Sample_Size" localSheetId="3">#REF!</definedName>
-    <definedName name="Sample_Size" localSheetId="2">#REF!</definedName>
+    <definedName name="Sample_Size" localSheetId="5">#REF!</definedName>
+    <definedName name="Sample_Size" localSheetId="4">#REF!</definedName>
     <definedName name="Sample_Size">#REF!</definedName>
-    <definedName name="SAV" localSheetId="3">#REF!</definedName>
-    <definedName name="SAV" localSheetId="2">#REF!</definedName>
+    <definedName name="SAV" localSheetId="5">#REF!</definedName>
+    <definedName name="SAV" localSheetId="4">#REF!</definedName>
     <definedName name="SAV">#REF!</definedName>
-    <definedName name="SCP" localSheetId="3">#REF!</definedName>
-    <definedName name="SCP" localSheetId="2">#REF!</definedName>
+    <definedName name="SCP" localSheetId="5">#REF!</definedName>
+    <definedName name="SCP" localSheetId="4">#REF!</definedName>
     <definedName name="SCP">#REF!</definedName>
     <definedName name="SDA">#REF!</definedName>
     <definedName name="SEM">#REF!</definedName>
@@ -699,8 +702,8 @@
     <definedName name="tooling">#REF!</definedName>
     <definedName name="Trend_No">#REF!</definedName>
     <definedName name="Trial">#REF!</definedName>
-    <definedName name="tttt" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="tttt" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="tttt" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="tttt" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="tttt" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="TW">#REF!</definedName>
     <definedName name="TWA">#REF!</definedName>
@@ -725,69 +728,69 @@
     <definedName name="VSDL">#REF!</definedName>
     <definedName name="VSMTL">#REF!</definedName>
     <definedName name="VSOH">#REF!</definedName>
-    <definedName name="VV" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="VV" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="VV" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="VV" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="VV" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="vvv">#REF!</definedName>
     <definedName name="vvvvv">#REF!</definedName>
     <definedName name="Weight">#REF!</definedName>
     <definedName name="WGP">#REF!</definedName>
     <definedName name="WJ">#REF!</definedName>
-    <definedName name="wo" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="wo" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="wo" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="wo" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="wo" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="WPV">#REF!</definedName>
-    <definedName name="wrn.niwat." localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
-    <definedName name="wrn.niwat." localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="wrn.niwat." localSheetId="5" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
+    <definedName name="wrn.niwat." localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="wrn.niwat." hidden="1">{#N/A,#N/A,FALSE,"form";#N/A,#N/A,FALSE,"form1";#N/A,#N/A,FALSE,"form2";#N/A,#N/A,FALSE,"form3";#N/A,#N/A,FALSE,"form4";#N/A,#N/A,FALSE,"form5"}</definedName>
     <definedName name="xxxx">#REF!</definedName>
-    <definedName name="yuity" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="yuity" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="yuity" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="yuity" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="yuity" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="yyyy">#REF!</definedName>
     <definedName name="YYYYYYYY">#REF!</definedName>
     <definedName name="人員">#REF!</definedName>
     <definedName name="下一站進料方式">'[6]List Of Values'!$A$10:$A$12</definedName>
-    <definedName name="工作" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="工作" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="工作" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="工作" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="工作" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="工單出站方式">'[6]List Of Values'!$A$87:$A$91</definedName>
-    <definedName name="出口銷售收入" localSheetId="3">#REF!</definedName>
-    <definedName name="出口銷售收入" localSheetId="2">#REF!</definedName>
+    <definedName name="出口銷售收入" localSheetId="5">#REF!</definedName>
+    <definedName name="出口銷售收入" localSheetId="4">#REF!</definedName>
     <definedName name="出口銷售收入">#REF!</definedName>
-    <definedName name="本次请购" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="本次请购" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="本次请购" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="本次请购" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="本次请购" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="生產情況">#REF!</definedName>
     <definedName name="年數">#REF!</definedName>
     <definedName name="作業者操作介面">'[6]List Of Values'!$A$32:$A$35</definedName>
-    <definedName name="我" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="我" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="我" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="我" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="我" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="技術專案匯總2" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="技術專案匯總2" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="技術專案匯總2" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="技術專案匯總2" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="技術專案匯總2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="投資情況">#REF!</definedName>
     <definedName name="材料成本分析">#REF!</definedName>
-    <definedName name="其他全问题" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="其他全问题" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="其他全问题" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="其他全问题" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="其他全问题" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="固定資產投資">#REF!</definedName>
-    <definedName name="治工具" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="治工具" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="治工具" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="治工具01" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="治工具01" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具01" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="治工具01" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="治工具01" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="能源">#REF!</definedName>
     <definedName name="動作">'[6]List Of Values'!$A$19:$A$22</definedName>
-    <definedName name="啊啊啊啊" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="啊啊啊啊" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="啊啊啊啊" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="啊啊啊啊" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="啊啊啊啊" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="設備型態">'[6]List Of Values'!$A$2:$A$3</definedName>
     <definedName name="設備資訊取得方式">'[6]List Of Values'!$A$49:$A$54</definedName>
-    <definedName name="陳帥虎" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="陳帥虎" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="陳帥虎" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="陳帥虎" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="陳帥虎" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="稅">#REF!</definedName>
     <definedName name="答案">'[6]List Of Values'!$A$44:$A$45</definedName>
@@ -796,28 +799,28 @@
     <definedName name="量測值取得時機">'[6]List Of Values'!$A$111:$A$112</definedName>
     <definedName name="量測值圖表">'[6]List Of Values'!$A$135:$A$138</definedName>
     <definedName name="量測值管制">'[6]List Of Values'!$A$129:$A$131</definedName>
-    <definedName name="匯率" localSheetId="3">#REF!</definedName>
-    <definedName name="匯率" localSheetId="2">#REF!</definedName>
+    <definedName name="匯率" localSheetId="5">#REF!</definedName>
+    <definedName name="匯率" localSheetId="4">#REF!</definedName>
     <definedName name="匯率">#REF!</definedName>
-    <definedName name="暗示" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="暗示" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="暗示" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="暗示" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="暗示" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="資料格式">'[6]List Of Values'!$A$68:$A$72</definedName>
-    <definedName name="實際出口情況" localSheetId="3">#REF!</definedName>
-    <definedName name="實際出口情況" localSheetId="2">#REF!</definedName>
+    <definedName name="實際出口情況" localSheetId="5">#REF!</definedName>
+    <definedName name="實際出口情況" localSheetId="4">#REF!</definedName>
     <definedName name="實際出口情況">#REF!</definedName>
-    <definedName name="實際進口情況" localSheetId="3">#REF!</definedName>
-    <definedName name="實際進口情況" localSheetId="2">#REF!</definedName>
+    <definedName name="實際進口情況" localSheetId="5">#REF!</definedName>
+    <definedName name="實際進口情況" localSheetId="4">#REF!</definedName>
     <definedName name="實際進口情況">#REF!</definedName>
     <definedName name="廠商支援整合方式">'[6]List Of Values'!$A$59:$A$64</definedName>
-    <definedName name="請購" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="請購" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="請購" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="請購" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="請購" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="機械手">#REF!</definedName>
     <definedName name="點檢頻率">'[6]List Of Values'!$A$123:$A$125</definedName>
     <definedName name="簡化">OFFSET('[3]Password Table UAT(F)'!#REF!,,,COUNTA('[3]Password Table UAT(F)'!$B:$B)-1,1)</definedName>
-    <definedName name="舊我" localSheetId="3" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
-    <definedName name="舊我" localSheetId="2" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="舊我" localSheetId="5" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
+    <definedName name="舊我" localSheetId="4" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
     <definedName name="舊我" hidden="1">{"'A'!$A$1:$AM$51","'A'!$U$3"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1261,7 +1264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3960" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4314" uniqueCount="658">
   <si>
     <t>片材長邊尺寸 (mm) mm</t>
   </si>
@@ -5250,104 +5253,20 @@
     <xf numFmtId="0" fontId="17" fillId="22" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5357,63 +5276,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5425,6 +5287,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5454,20 +5319,158 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6149,24 +6152,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="revised 2代-03SEC CT (2+2)"/>
-      <sheetName val="revised 2代-01SG CT (1+1)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
@@ -6582,21 +6567,21 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="G8" s="200" t="s">
+      <c r="G8" s="263" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="201"/>
-      <c r="I8" s="202"/>
-      <c r="J8" s="203" t="s">
+      <c r="H8" s="264"/>
+      <c r="I8" s="265"/>
+      <c r="J8" s="266" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="204" t="s">
+      <c r="K8" s="266"/>
+      <c r="L8" s="266"/>
+      <c r="M8" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="204"/>
-      <c r="O8" s="204"/>
+      <c r="N8" s="267"/>
+      <c r="O8" s="267"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6650,7 +6635,7 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="106.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="211" t="s">
+      <c r="B10" s="250" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="85" t="s">
@@ -6703,14 +6688,14 @@
       <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="2:17" ht="84.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="212"/>
-      <c r="C11" s="214" t="s">
+      <c r="B11" s="251"/>
+      <c r="C11" s="253" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="216">
+      <c r="E11" s="255">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -6756,12 +6741,12 @@
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="2:17" ht="86.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="212"/>
-      <c r="C12" s="215"/>
+      <c r="B12" s="251"/>
+      <c r="C12" s="254"/>
       <c r="D12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="217"/>
+      <c r="E12" s="256"/>
       <c r="F12" s="14" t="s">
         <v>14</v>
       </c>
@@ -6805,14 +6790,14 @@
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="212"/>
-      <c r="C13" s="218" t="s">
+      <c r="B13" s="251"/>
+      <c r="C13" s="257" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="220">
+      <c r="E13" s="260">
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -6843,16 +6828,16 @@
         <f t="shared" ref="O13:O25" si="1">M13*N13/60</f>
         <v>12</v>
       </c>
-      <c r="P13" s="223"/>
-      <c r="Q13" s="224"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="242"/>
     </row>
     <row r="14" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="212"/>
-      <c r="C14" s="219"/>
+      <c r="B14" s="251"/>
+      <c r="C14" s="258"/>
       <c r="D14" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="E14" s="221"/>
+      <c r="E14" s="261"/>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -6872,16 +6857,16 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="223"/>
-      <c r="Q14" s="224"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="242"/>
     </row>
     <row r="15" spans="2:17" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="212"/>
-      <c r="C15" s="208"/>
+      <c r="B15" s="251"/>
+      <c r="C15" s="259"/>
       <c r="D15" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="222"/>
+      <c r="E15" s="262"/>
       <c r="F15" s="20" t="s">
         <v>18</v>
       </c>
@@ -6919,11 +6904,11 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P15" s="223"/>
-      <c r="Q15" s="224"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="242"/>
     </row>
     <row r="16" spans="2:17" ht="100.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="212"/>
+      <c r="B16" s="251"/>
       <c r="C16" s="21" t="s">
         <v>79</v>
       </c>
@@ -6973,7 +6958,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="98.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="213"/>
+      <c r="B17" s="252"/>
       <c r="C17" s="105" t="s">
         <v>80</v>
       </c>
@@ -7028,7 +7013,7 @@
       <c r="Q17" s="31"/>
     </row>
     <row r="18" spans="2:18" ht="122.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="205" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -7083,7 +7068,7 @@
       <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="234"/>
+      <c r="B19" s="206"/>
       <c r="C19" s="35" t="s">
         <v>83</v>
       </c>
@@ -7137,14 +7122,14 @@
       <c r="R19" s="37"/>
     </row>
     <row r="20" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="234"/>
+      <c r="B20" s="206"/>
       <c r="C20" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="225">
+      <c r="E20" s="243">
         <v>1</v>
       </c>
       <c r="F20" s="38" t="s">
@@ -7186,19 +7171,19 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P20" s="228"/>
-      <c r="Q20" s="230"/>
+      <c r="P20" s="245"/>
+      <c r="Q20" s="247"/>
       <c r="R20" s="41"/>
     </row>
     <row r="21" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="234"/>
+      <c r="B21" s="206"/>
       <c r="C21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="226"/>
+      <c r="E21" s="244"/>
       <c r="F21" s="20" t="s">
         <v>25</v>
       </c>
@@ -7229,19 +7214,19 @@
         <f>M21*N21/60</f>
         <v>1.25</v>
       </c>
-      <c r="P21" s="223"/>
-      <c r="Q21" s="231"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="248"/>
       <c r="R21" s="41"/>
     </row>
     <row r="22" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="234"/>
+      <c r="B22" s="206"/>
       <c r="C22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="236" t="s">
+      <c r="D22" s="222" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="226"/>
+      <c r="E22" s="244"/>
       <c r="F22" s="43" t="s">
         <v>26</v>
       </c>
@@ -7281,17 +7266,17 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P22" s="223"/>
-      <c r="Q22" s="231"/>
+      <c r="P22" s="236"/>
+      <c r="Q22" s="248"/>
       <c r="R22" s="41"/>
     </row>
     <row r="23" spans="2:18" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="234"/>
+      <c r="B23" s="206"/>
       <c r="C23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="237"/>
-      <c r="E23" s="227"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="229"/>
       <c r="F23" s="47" t="s">
         <v>24</v>
       </c>
@@ -7331,12 +7316,12 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="P23" s="229"/>
-      <c r="Q23" s="232"/>
+      <c r="P23" s="246"/>
+      <c r="Q23" s="249"/>
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="2:18" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="235"/>
+      <c r="B24" s="207"/>
       <c r="C24" s="91" t="s">
         <v>84</v>
       </c>
@@ -7390,29 +7375,29 @@
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="2:18" ht="129" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="247" t="s">
+      <c r="C25" s="212" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="247" t="s">
+      <c r="D25" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="248">
+      <c r="E25" s="234">
         <v>1</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="209">
+      <c r="G25" s="271">
         <f>90/4</f>
         <v>22.5</v>
       </c>
-      <c r="H25" s="207">
+      <c r="H25" s="270">
         <v>8</v>
       </c>
-      <c r="I25" s="205">
+      <c r="I25" s="268">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -7428,14 +7413,14 @@
         <f t="shared" si="4"/>
         <v>3.75</v>
       </c>
-      <c r="M25" s="205">
+      <c r="M25" s="268">
         <f>90/5</f>
         <v>18</v>
       </c>
-      <c r="N25" s="207">
+      <c r="N25" s="270">
         <v>10</v>
       </c>
-      <c r="O25" s="205">
+      <c r="O25" s="268">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7443,16 +7428,16 @@
       <c r="Q25" s="51"/>
     </row>
     <row r="26" spans="2:18" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="240"/>
-      <c r="C26" s="247"/>
-      <c r="D26" s="247"/>
-      <c r="E26" s="249"/>
+      <c r="B26" s="226"/>
+      <c r="C26" s="212"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="235"/>
       <c r="F26" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="210"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="206"/>
+      <c r="G26" s="272"/>
+      <c r="H26" s="259"/>
+      <c r="I26" s="269"/>
       <c r="J26" s="15">
         <f>110/4</f>
         <v>27.5</v>
@@ -7465,21 +7450,21 @@
         <f t="shared" ref="L26" si="7">J26*K26/60</f>
         <v>4.583333333333333</v>
       </c>
-      <c r="M26" s="206"/>
-      <c r="N26" s="208"/>
-      <c r="O26" s="206"/>
+      <c r="M26" s="269"/>
+      <c r="N26" s="259"/>
+      <c r="O26" s="269"/>
       <c r="P26" s="141"/>
       <c r="Q26" s="23"/>
     </row>
     <row r="27" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="240"/>
+      <c r="B27" s="226"/>
       <c r="C27" s="142" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="241" t="s">
+      <c r="D27" s="227" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="242">
+      <c r="E27" s="228">
         <v>1</v>
       </c>
       <c r="F27" s="47" t="s">
@@ -7521,16 +7506,16 @@
         <f>M27*N27/60</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="P27" s="243"/>
-      <c r="Q27" s="238"/>
+      <c r="P27" s="230"/>
+      <c r="Q27" s="224"/>
     </row>
     <row r="28" spans="2:18" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="240"/>
+      <c r="B28" s="226"/>
       <c r="C28" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="237"/>
-      <c r="E28" s="227"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="229"/>
       <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
@@ -7567,11 +7552,11 @@
         <f>M28*N28/60</f>
         <v>13</v>
       </c>
-      <c r="P28" s="244"/>
-      <c r="Q28" s="239"/>
+      <c r="P28" s="231"/>
+      <c r="Q28" s="225"/>
     </row>
     <row r="29" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="240"/>
+      <c r="B29" s="226"/>
       <c r="C29" s="35" t="s">
         <v>91</v>
       </c>
@@ -7624,7 +7609,7 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="240"/>
+      <c r="B30" s="226"/>
       <c r="C30" s="55" t="s">
         <v>92</v>
       </c>
@@ -7677,14 +7662,14 @@
       <c r="Q30" s="58"/>
     </row>
     <row r="31" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="240"/>
-      <c r="C31" s="258" t="s">
+      <c r="B31" s="226"/>
+      <c r="C31" s="211" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="247" t="s">
+      <c r="D31" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="255">
+      <c r="E31" s="208">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -7724,10 +7709,10 @@
       <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="2:18" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="240"/>
-      <c r="C32" s="258"/>
-      <c r="D32" s="247"/>
-      <c r="E32" s="256"/>
+      <c r="B32" s="226"/>
+      <c r="C32" s="211"/>
+      <c r="D32" s="212"/>
+      <c r="E32" s="209"/>
       <c r="F32" s="14" t="s">
         <v>34</v>
       </c>
@@ -7765,10 +7750,10 @@
       <c r="Q32" s="60"/>
     </row>
     <row r="33" spans="2:17" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="240"/>
-      <c r="C33" s="258"/>
-      <c r="D33" s="247"/>
-      <c r="E33" s="257"/>
+      <c r="B33" s="226"/>
+      <c r="C33" s="211"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="210"/>
       <c r="F33" s="14" t="s">
         <v>35</v>
       </c>
@@ -7806,14 +7791,14 @@
       <c r="Q33" s="60"/>
     </row>
     <row r="34" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="240"/>
-      <c r="C34" s="258" t="s">
+      <c r="B34" s="226"/>
+      <c r="C34" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="247" t="s">
+      <c r="D34" s="212" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="259">
+      <c r="E34" s="213">
         <v>1</v>
       </c>
       <c r="F34" s="61" t="s">
@@ -7852,10 +7837,10 @@
       <c r="Q34" s="31"/>
     </row>
     <row r="35" spans="2:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="240"/>
-      <c r="C35" s="258"/>
-      <c r="D35" s="247"/>
-      <c r="E35" s="259"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="211"/>
+      <c r="D35" s="212"/>
+      <c r="E35" s="213"/>
       <c r="F35" s="61" t="s">
         <v>135</v>
       </c>
@@ -7896,7 +7881,7 @@
       <c r="Q35" s="31"/>
     </row>
     <row r="36" spans="2:17" s="113" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="240"/>
+      <c r="B36" s="226"/>
       <c r="C36" s="139" t="s">
         <v>97</v>
       </c>
@@ -7946,14 +7931,14 @@
       <c r="Q36" s="126"/>
     </row>
     <row r="37" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="240"/>
-      <c r="C37" s="266" t="s">
+      <c r="B37" s="226"/>
+      <c r="C37" s="220" t="s">
         <v>109</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="245">
+      <c r="E37" s="232">
         <v>3</v>
       </c>
       <c r="F37" s="56" t="s">
@@ -7995,18 +7980,18 @@
         <f>M37*N37/60</f>
         <v>12.5</v>
       </c>
-      <c r="P37" s="223"/>
-      <c r="Q37" s="251" t="s">
+      <c r="P37" s="236"/>
+      <c r="Q37" s="238" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="81" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="240"/>
-      <c r="C38" s="267"/>
+      <c r="B38" s="226"/>
+      <c r="C38" s="221"/>
       <c r="D38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="246"/>
+      <c r="E38" s="233"/>
       <c r="F38" s="56" t="s">
         <v>43</v>
       </c>
@@ -8046,18 +8031,18 @@
         <f>M38*N38/60</f>
         <v>5</v>
       </c>
-      <c r="P38" s="223"/>
-      <c r="Q38" s="252"/>
+      <c r="P38" s="236"/>
+      <c r="Q38" s="239"/>
     </row>
     <row r="39" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="240"/>
+      <c r="B39" s="226"/>
       <c r="C39" s="62" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="246"/>
+      <c r="E39" s="233"/>
       <c r="F39" s="56" t="s">
         <v>45</v>
       </c>
@@ -8097,20 +8082,20 @@
         <f>M39*N39/60</f>
         <v>1.25</v>
       </c>
-      <c r="P39" s="223"/>
-      <c r="Q39" s="253" t="s">
+      <c r="P39" s="236"/>
+      <c r="Q39" s="240" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="240"/>
+      <c r="B40" s="226"/>
       <c r="C40" s="55" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="246"/>
+      <c r="E40" s="233"/>
       <c r="F40" s="56" t="s">
         <v>48</v>
       </c>
@@ -8150,11 +8135,11 @@
         <f>M40*N40/60</f>
         <v>0.625</v>
       </c>
-      <c r="P40" s="250"/>
-      <c r="Q40" s="254"/>
+      <c r="P40" s="237"/>
+      <c r="Q40" s="241"/>
     </row>
     <row r="41" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="233" t="s">
+      <c r="B41" s="205" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -8163,7 +8148,7 @@
       <c r="D41" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="259">
+      <c r="E41" s="213">
         <v>2</v>
       </c>
       <c r="F41" s="63" t="s">
@@ -8211,14 +8196,14 @@
       <c r="Q41" s="59"/>
     </row>
     <row r="42" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="234"/>
+      <c r="B42" s="206"/>
       <c r="C42" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="259"/>
+      <c r="E42" s="213"/>
       <c r="F42" s="63" t="s">
         <v>54</v>
       </c>
@@ -8264,7 +8249,7 @@
       <c r="Q42" s="66"/>
     </row>
     <row r="43" spans="2:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="234"/>
+      <c r="B43" s="206"/>
       <c r="C43" s="120" t="s">
         <v>112</v>
       </c>
@@ -8316,7 +8301,7 @@
       <c r="Q43" s="121"/>
     </row>
     <row r="44" spans="2:17" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="234"/>
+      <c r="B44" s="206"/>
       <c r="C44" s="9" t="s">
         <v>98</v>
       </c>
@@ -8369,7 +8354,7 @@
       <c r="Q44" s="68"/>
     </row>
     <row r="45" spans="2:17" ht="97.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="234"/>
+      <c r="B45" s="206"/>
       <c r="C45" s="35" t="s">
         <v>99</v>
       </c>
@@ -8422,14 +8407,14 @@
       <c r="Q45" s="51"/>
     </row>
     <row r="46" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="234"/>
-      <c r="C46" s="260" t="s">
+      <c r="B46" s="206"/>
+      <c r="C46" s="214" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="263" t="s">
+      <c r="D46" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="255">
+      <c r="E46" s="208">
         <v>1</v>
       </c>
       <c r="F46" s="14" t="s">
@@ -8475,10 +8460,10 @@
       <c r="Q46" s="69"/>
     </row>
     <row r="47" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="234"/>
-      <c r="C47" s="261"/>
-      <c r="D47" s="264"/>
-      <c r="E47" s="256"/>
+      <c r="B47" s="206"/>
+      <c r="C47" s="215"/>
+      <c r="D47" s="218"/>
+      <c r="E47" s="209"/>
       <c r="F47" s="14" t="s">
         <v>64</v>
       </c>
@@ -8522,10 +8507,10 @@
       <c r="Q47" s="69"/>
     </row>
     <row r="48" spans="2:17" ht="63.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="234"/>
-      <c r="C48" s="262"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="257"/>
+      <c r="B48" s="206"/>
+      <c r="C48" s="216"/>
+      <c r="D48" s="219"/>
+      <c r="E48" s="210"/>
       <c r="F48" s="14" t="s">
         <v>65</v>
       </c>
@@ -8566,7 +8551,7 @@
       <c r="Q48" s="69"/>
     </row>
     <row r="49" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="234"/>
+      <c r="B49" s="206"/>
       <c r="C49" s="35" t="s">
         <v>101</v>
       </c>
@@ -8619,7 +8604,7 @@
       <c r="Q49" s="71"/>
     </row>
     <row r="50" spans="2:17" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="235"/>
+      <c r="B50" s="207"/>
       <c r="C50" s="9" t="s">
         <v>102</v>
       </c>
@@ -8669,7 +8654,7 @@
       <c r="Q50" s="72"/>
     </row>
     <row r="51" spans="2:17" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="205" t="s">
         <v>69</v>
       </c>
       <c r="C51" s="78" t="s">
@@ -8724,7 +8709,7 @@
       </c>
     </row>
     <row r="52" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="234"/>
+      <c r="B52" s="206"/>
       <c r="C52" s="21" t="s">
         <v>123</v>
       </c>
@@ -8774,7 +8759,7 @@
       <c r="Q52" s="30"/>
     </row>
     <row r="53" spans="2:17" ht="93.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="234"/>
+      <c r="B53" s="206"/>
       <c r="C53" s="21" t="s">
         <v>123</v>
       </c>
@@ -8824,7 +8809,7 @@
       </c>
     </row>
     <row r="54" spans="2:17" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="234"/>
+      <c r="B54" s="206"/>
       <c r="C54" s="21" t="s">
         <v>113</v>
       </c>
@@ -8872,7 +8857,7 @@
       <c r="Q54" s="76"/>
     </row>
     <row r="55" spans="2:17" s="113" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="235"/>
+      <c r="B55" s="207"/>
       <c r="C55" s="114" t="s">
         <v>114</v>
       </c>
@@ -8925,18 +8910,25 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="P20:P23"/>
+    <mergeCell ref="Q20:Q23"/>
     <mergeCell ref="B18:B24"/>
     <mergeCell ref="B41:B50"/>
     <mergeCell ref="D22:D23"/>
@@ -8952,25 +8944,18 @@
     <mergeCell ref="P37:P40"/>
     <mergeCell ref="Q37:Q38"/>
     <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="P20:P23"/>
-    <mergeCell ref="Q20:Q23"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C37:C38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10055,6 +10040,1808 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679A0FB3-6FE3-4EE9-A236-996A1B4977F6}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="147" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="147" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" style="147" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="147" customWidth="1"/>
+    <col min="6" max="7" width="13.88671875" style="150" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="147"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="143" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="181" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="184" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="185" t="s">
+        <v>626</v>
+      </c>
+      <c r="F1" s="182" t="s">
+        <v>647</v>
+      </c>
+      <c r="G1" s="197" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="177" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="180" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="186" t="s">
+        <v>627</v>
+      </c>
+      <c r="F2" s="200">
+        <v>14.426399999999997</v>
+      </c>
+      <c r="G2" s="186">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="177" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="180" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F3" s="200">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G3" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="177" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="180" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="F4" s="201">
+        <v>3.8</v>
+      </c>
+      <c r="G4" s="189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="180" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="186" t="s">
+        <v>652</v>
+      </c>
+      <c r="F5" s="202">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G5" s="198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="177" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="180" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F6" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G6" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="177" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="180" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F7" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G7" s="189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="177" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="180" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F8" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G8" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="180" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F9" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G9" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="177" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="180" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="186" t="s">
+        <v>653</v>
+      </c>
+      <c r="F10" s="200">
+        <v>10</v>
+      </c>
+      <c r="G10" s="186">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="199" t="s">
+        <v>650</v>
+      </c>
+      <c r="D11" s="180" t="s">
+        <v>649</v>
+      </c>
+      <c r="E11" s="186" t="s">
+        <v>654</v>
+      </c>
+      <c r="F11" s="200">
+        <v>4.8</v>
+      </c>
+      <c r="G11" s="186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="177" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="180" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F12" s="200">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G12" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="177" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="180" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F13" s="200">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G13" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="177" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="180" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F14" s="200">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G14" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="177" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F15" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G15" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="177" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" s="180" t="s">
+        <v>252</v>
+      </c>
+      <c r="E16" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F16" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G16" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="177" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="180" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F17" s="200">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G17" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="177" t="s">
+        <v>257</v>
+      </c>
+      <c r="D18" s="180" t="s">
+        <v>258</v>
+      </c>
+      <c r="E18" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="F18" s="201">
+        <v>3.8</v>
+      </c>
+      <c r="G18" s="189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="177" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" s="180" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="186" t="s">
+        <v>652</v>
+      </c>
+      <c r="F19" s="202">
+        <v>12.0723780439164</v>
+      </c>
+      <c r="G19" s="198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="177" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="180" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F20" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G20" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="177" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" s="180" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F21" s="200">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G21" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="177" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22" s="180" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F22" s="200">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G22" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="177" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="180" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F23" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G23" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="177" t="s">
+        <v>298</v>
+      </c>
+      <c r="D24" s="180" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F24" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G24" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="199" t="s">
+        <v>650</v>
+      </c>
+      <c r="D25" s="180" t="s">
+        <v>648</v>
+      </c>
+      <c r="E25" s="186" t="s">
+        <v>654</v>
+      </c>
+      <c r="F25" s="200">
+        <v>4.8</v>
+      </c>
+      <c r="G25" s="186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="177" t="s">
+        <v>308</v>
+      </c>
+      <c r="D26" s="180" t="s">
+        <v>309</v>
+      </c>
+      <c r="E26" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F26" s="200">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G26" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="177" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="180" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F27" s="200">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G27" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="177" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" s="180" t="s">
+        <v>321</v>
+      </c>
+      <c r="E28" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F28" s="200">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G28" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="177" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" s="180" t="s">
+        <v>325</v>
+      </c>
+      <c r="E29" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F29" s="202">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G29" s="189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" s="180" t="s">
+        <v>339</v>
+      </c>
+      <c r="E30" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F30" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G30" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" s="177" t="s">
+        <v>340</v>
+      </c>
+      <c r="D31" s="180" t="s">
+        <v>341</v>
+      </c>
+      <c r="E31" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F31" s="200">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G31" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="177" t="s">
+        <v>348</v>
+      </c>
+      <c r="D32" s="180" t="s">
+        <v>349</v>
+      </c>
+      <c r="E32" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F32" s="200">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G32" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" s="177" t="s">
+        <v>360</v>
+      </c>
+      <c r="D33" s="180" t="s">
+        <v>361</v>
+      </c>
+      <c r="E33" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F33" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G33" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="177" t="s">
+        <v>362</v>
+      </c>
+      <c r="D34" s="180" t="s">
+        <v>363</v>
+      </c>
+      <c r="E34" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F34" s="200">
+        <v>2.5777777777777775</v>
+      </c>
+      <c r="G34" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="177" t="s">
+        <v>371</v>
+      </c>
+      <c r="D35" s="180" t="s">
+        <v>372</v>
+      </c>
+      <c r="E35" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F35" s="200">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G35" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="177" t="s">
+        <v>385</v>
+      </c>
+      <c r="D36" s="180" t="s">
+        <v>386</v>
+      </c>
+      <c r="E36" s="186" t="s">
+        <v>655</v>
+      </c>
+      <c r="F36" s="200">
+        <v>1.0311111111111111</v>
+      </c>
+      <c r="G36" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>387</v>
+      </c>
+      <c r="D37" s="180" t="s">
+        <v>388</v>
+      </c>
+      <c r="E37" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F37" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G37" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="177" t="s">
+        <v>391</v>
+      </c>
+      <c r="D38" s="180" t="s">
+        <v>392</v>
+      </c>
+      <c r="E38" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F38" s="200">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G38" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="177" t="s">
+        <v>397</v>
+      </c>
+      <c r="D39" s="180" t="s">
+        <v>398</v>
+      </c>
+      <c r="E39" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F39" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G39" s="186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="177" t="s">
+        <v>401</v>
+      </c>
+      <c r="D40" s="180" t="s">
+        <v>402</v>
+      </c>
+      <c r="E40" s="186" t="s">
+        <v>635</v>
+      </c>
+      <c r="F40" s="200">
+        <v>3</v>
+      </c>
+      <c r="G40" s="186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" s="177" t="s">
+        <v>415</v>
+      </c>
+      <c r="D41" s="180" t="s">
+        <v>416</v>
+      </c>
+      <c r="E41" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F41" s="200">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G41" s="186">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G41" xr:uid="{6728E53C-434A-495F-8AAB-EEEFA7B7F41D}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB220F36-3558-4225-ABA6-476253378E69}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" style="147" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5546875" style="147" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" style="147" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" style="150" customWidth="1"/>
+    <col min="6" max="7" width="13.88671875" style="150" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="147"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="144" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="143" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="181" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="184" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="185" t="s">
+        <v>626</v>
+      </c>
+      <c r="F1" s="182" t="s">
+        <v>473</v>
+      </c>
+      <c r="G1" s="197" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="177" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="180" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="186" t="s">
+        <v>627</v>
+      </c>
+      <c r="F2" s="203">
+        <v>14.426399999999997</v>
+      </c>
+      <c r="G2" s="149">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C3" s="177" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="E3" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F3" s="203">
+        <v>2.5777777777777802</v>
+      </c>
+      <c r="G3" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="177" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="180" t="s">
+        <v>428</v>
+      </c>
+      <c r="E4" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="F4" s="203">
+        <v>3.8</v>
+      </c>
+      <c r="G4" s="149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="180" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F5" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G5" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" s="177" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" s="180" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F6" s="203">
+        <v>2.5777777777777802</v>
+      </c>
+      <c r="G6" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="177" t="s">
+        <v>437</v>
+      </c>
+      <c r="D7" s="180" t="s">
+        <v>438</v>
+      </c>
+      <c r="E7" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="F7" s="203">
+        <v>3.8</v>
+      </c>
+      <c r="G7" s="149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C8" s="177" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="180" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" s="186" t="s">
+        <v>652</v>
+      </c>
+      <c r="F8" s="203">
+        <v>12.072378043916389</v>
+      </c>
+      <c r="G8" s="149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C9" s="177" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="180" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="186" t="s">
+        <v>652</v>
+      </c>
+      <c r="F9" s="203">
+        <v>12.072378043916389</v>
+      </c>
+      <c r="G9" s="149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C10" s="177" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="180" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F10" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G10" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="177" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="180" t="s">
+        <v>196</v>
+      </c>
+      <c r="E11" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F11" s="203">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G11" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C12" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="D12" s="180" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F12" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G12" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="177" t="s">
+        <v>650</v>
+      </c>
+      <c r="D13" s="180" t="s">
+        <v>651</v>
+      </c>
+      <c r="E13" s="186" t="s">
+        <v>654</v>
+      </c>
+      <c r="F13" s="204">
+        <v>4.8</v>
+      </c>
+      <c r="G13" s="176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="177" t="s">
+        <v>447</v>
+      </c>
+      <c r="D14" s="180" t="s">
+        <v>448</v>
+      </c>
+      <c r="E14" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F14" s="203">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G14" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C15" s="177" t="s">
+        <v>449</v>
+      </c>
+      <c r="D15" s="180" t="s">
+        <v>450</v>
+      </c>
+      <c r="E15" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="F15" s="203">
+        <v>3.0222222222222199</v>
+      </c>
+      <c r="G15" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C16" s="177" t="s">
+        <v>457</v>
+      </c>
+      <c r="D16" s="180" t="s">
+        <v>458</v>
+      </c>
+      <c r="E16" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F16" s="203">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G16" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C17" s="177" t="s">
+        <v>324</v>
+      </c>
+      <c r="D17" s="180" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="F17" s="203">
+        <v>3.3142857142857101</v>
+      </c>
+      <c r="G17" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C18" s="177" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" s="180" t="s">
+        <v>339</v>
+      </c>
+      <c r="E18" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F18" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G18" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C19" s="177" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="180" t="s">
+        <v>341</v>
+      </c>
+      <c r="E19" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F19" s="203">
+        <v>2.5777777777777802</v>
+      </c>
+      <c r="G19" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C20" s="177" t="s">
+        <v>461</v>
+      </c>
+      <c r="D20" s="180" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F20" s="203">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G20" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="177" t="s">
+        <v>360</v>
+      </c>
+      <c r="D21" s="180" t="s">
+        <v>361</v>
+      </c>
+      <c r="E21" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F21" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G21" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C22" s="177" t="s">
+        <v>362</v>
+      </c>
+      <c r="D22" s="180" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="F22" s="203">
+        <v>2.5777777777777802</v>
+      </c>
+      <c r="G22" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C23" s="177" t="s">
+        <v>465</v>
+      </c>
+      <c r="D23" s="180" t="s">
+        <v>466</v>
+      </c>
+      <c r="E23" s="186" t="s">
+        <v>628</v>
+      </c>
+      <c r="F23" s="203">
+        <v>3.31111111111111</v>
+      </c>
+      <c r="G23" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C24" s="177" t="s">
+        <v>385</v>
+      </c>
+      <c r="D24" s="180" t="s">
+        <v>386</v>
+      </c>
+      <c r="E24" s="186" t="s">
+        <v>655</v>
+      </c>
+      <c r="F24" s="203">
+        <v>1.0311111111111111</v>
+      </c>
+      <c r="G24" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C25" s="177" t="s">
+        <v>387</v>
+      </c>
+      <c r="D25" s="180" t="s">
+        <v>388</v>
+      </c>
+      <c r="E25" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F25" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G25" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C26" s="177" t="s">
+        <v>469</v>
+      </c>
+      <c r="D26" s="180" t="s">
+        <v>470</v>
+      </c>
+      <c r="E26" s="186" t="s">
+        <v>630</v>
+      </c>
+      <c r="F26" s="203">
+        <v>4.63657407407407</v>
+      </c>
+      <c r="G26" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C27" s="177" t="s">
+        <v>397</v>
+      </c>
+      <c r="D27" s="180" t="s">
+        <v>398</v>
+      </c>
+      <c r="E27" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F27" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G27" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C28" s="177" t="s">
+        <v>471</v>
+      </c>
+      <c r="D28" s="180" t="s">
+        <v>472</v>
+      </c>
+      <c r="E28" s="186" t="s">
+        <v>635</v>
+      </c>
+      <c r="F28" s="203">
+        <v>3</v>
+      </c>
+      <c r="G28" s="149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="144" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="145" t="s">
+        <v>419</v>
+      </c>
+      <c r="C29" s="177" t="s">
+        <v>415</v>
+      </c>
+      <c r="D29" s="180" t="s">
+        <v>416</v>
+      </c>
+      <c r="E29" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="F29" s="203">
+        <v>1.1047619047618999</v>
+      </c>
+      <c r="G29" s="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F30" s="151"/>
+      <c r="G30" s="152"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F31" s="151"/>
+      <c r="G31" s="152"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F32" s="151"/>
+      <c r="G32" s="152"/>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F33" s="151"/>
+      <c r="G33" s="152"/>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="151"/>
+      <c r="G34" s="152"/>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F35" s="151"/>
+      <c r="G35" s="152"/>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F36" s="151"/>
+      <c r="G36" s="152"/>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="151"/>
+      <c r="G37" s="152"/>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F38" s="151"/>
+      <c r="G38" s="152"/>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F39" s="151"/>
+      <c r="G39" s="152"/>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F40" s="151"/>
+      <c r="G40" s="152"/>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F41" s="151"/>
+      <c r="G41" s="152"/>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F42" s="151"/>
+      <c r="G42" s="152"/>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="151"/>
+      <c r="G43" s="152"/>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="151"/>
+      <c r="G44" s="152"/>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F45" s="151"/>
+      <c r="G45" s="152"/>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F46" s="151"/>
+      <c r="G46" s="152"/>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="151"/>
+      <c r="G47" s="152"/>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F48" s="151"/>
+      <c r="G48" s="152"/>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F49" s="151"/>
+      <c r="G49" s="152"/>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F50" s="151"/>
+      <c r="G50" s="152"/>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F51" s="151"/>
+      <c r="G51" s="152"/>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F52" s="151"/>
+      <c r="G52" s="152"/>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F53" s="151"/>
+      <c r="G53" s="152"/>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F54" s="151"/>
+      <c r="G54" s="152"/>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F55" s="151"/>
+      <c r="G55" s="152"/>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F56" s="151"/>
+      <c r="G56" s="152"/>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F57" s="151"/>
+      <c r="G57" s="152"/>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F58" s="151"/>
+      <c r="G58" s="152"/>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F59" s="151"/>
+      <c r="G59" s="152"/>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F60" s="151"/>
+      <c r="G60" s="152"/>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F61" s="151"/>
+      <c r="G61" s="152"/>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F62" s="151"/>
+      <c r="G62" s="152"/>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F63" s="151"/>
+      <c r="G63" s="152"/>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F64" s="151"/>
+      <c r="G64" s="152"/>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F65" s="151"/>
+      <c r="G65" s="152"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G65" xr:uid="{E3665249-3B56-4736-82A3-8BF617843F28}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D81907-B370-479F-A63F-759394FFDDBB}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -10110,7 +11897,7 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="268">
+      <c r="F2" s="200">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="186">
@@ -10133,7 +11920,7 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="268">
+      <c r="F3" s="200">
         <v>2.5777777777777775</v>
       </c>
       <c r="G3" s="186">
@@ -10156,7 +11943,7 @@
       <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="269">
+      <c r="F4" s="201">
         <v>3.8</v>
       </c>
       <c r="G4" s="189">
@@ -10179,7 +11966,7 @@
       <c r="E5" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="F5" s="270">
+      <c r="F5" s="202">
         <v>12.0723780439164</v>
       </c>
       <c r="G5" s="198">
@@ -10202,7 +11989,7 @@
       <c r="E6" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F6" s="268">
+      <c r="F6" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G6" s="186">
@@ -10225,7 +12012,7 @@
       <c r="E7" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F7" s="270">
+      <c r="F7" s="202">
         <v>3.3142857142857101</v>
       </c>
       <c r="G7" s="189">
@@ -10294,7 +12081,7 @@
       <c r="E10" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F10" s="268">
+      <c r="F10" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G10" s="186">
@@ -10317,7 +12104,7 @@
       <c r="E11" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F11" s="268">
+      <c r="F11" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G11" s="186">
@@ -10340,7 +12127,7 @@
       <c r="E12" s="186" t="s">
         <v>653</v>
       </c>
-      <c r="F12" s="268">
+      <c r="F12" s="200">
         <v>10</v>
       </c>
       <c r="G12" s="186">
@@ -10363,7 +12150,7 @@
       <c r="E13" s="186" t="s">
         <v>654</v>
       </c>
-      <c r="F13" s="268">
+      <c r="F13" s="200">
         <v>4.8</v>
       </c>
       <c r="G13" s="186">
@@ -10386,7 +12173,7 @@
       <c r="E14" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F14" s="268">
+      <c r="F14" s="200">
         <v>3.0222222222222199</v>
       </c>
       <c r="G14" s="186">
@@ -10409,7 +12196,7 @@
       <c r="E15" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F15" s="268">
+      <c r="F15" s="200">
         <v>3.0222222222222199</v>
       </c>
       <c r="G15" s="186">
@@ -10432,7 +12219,7 @@
       <c r="E16" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F16" s="268">
+      <c r="F16" s="200">
         <v>4.63657407407407</v>
       </c>
       <c r="G16" s="186">
@@ -10455,7 +12242,7 @@
       <c r="E17" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F17" s="270">
+      <c r="F17" s="202">
         <v>3.3142857142857101</v>
       </c>
       <c r="G17" s="186">
@@ -10547,7 +12334,7 @@
       <c r="E21" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F21" s="268">
+      <c r="F21" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G21" s="186">
@@ -10570,7 +12357,7 @@
       <c r="E22" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F22" s="268">
+      <c r="F22" s="200">
         <v>2.5777777777777775</v>
       </c>
       <c r="G22" s="186">
@@ -10593,7 +12380,7 @@
       <c r="E23" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F23" s="269">
+      <c r="F23" s="201">
         <v>3.8</v>
       </c>
       <c r="G23" s="189">
@@ -10616,7 +12403,7 @@
       <c r="E24" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="F24" s="270">
+      <c r="F24" s="202">
         <v>12.0723780439164</v>
       </c>
       <c r="G24" s="198">
@@ -10639,7 +12426,7 @@
       <c r="E25" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F25" s="268">
+      <c r="F25" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G25" s="186">
@@ -10662,7 +12449,7 @@
       <c r="E26" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F26" s="268">
+      <c r="F26" s="200">
         <v>2.5777777777777775</v>
       </c>
       <c r="G26" s="186">
@@ -10685,7 +12472,7 @@
       <c r="E27" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F27" s="268">
+      <c r="F27" s="200">
         <v>3.31111111111111</v>
       </c>
       <c r="G27" s="186">
@@ -10729,7 +12516,7 @@
       <c r="E29" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F29" s="270">
+      <c r="F29" s="202">
         <v>3.3142857142857101</v>
       </c>
       <c r="G29" s="186">
@@ -10821,7 +12608,7 @@
       <c r="E33" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F33" s="268">
+      <c r="F33" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G33" s="186">
@@ -10844,7 +12631,7 @@
       <c r="E34" s="186" t="s">
         <v>654</v>
       </c>
-      <c r="F34" s="268">
+      <c r="F34" s="200">
         <v>4.8</v>
       </c>
       <c r="G34" s="186">
@@ -10867,7 +12654,7 @@
       <c r="E35" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F35" s="268">
+      <c r="F35" s="200">
         <v>3.0222222222222199</v>
       </c>
       <c r="G35" s="186">
@@ -10890,7 +12677,7 @@
       <c r="E36" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F36" s="268">
+      <c r="F36" s="200">
         <v>3.0222222222222199</v>
       </c>
       <c r="G36" s="186">
@@ -10913,7 +12700,7 @@
       <c r="E37" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F37" s="268">
+      <c r="F37" s="200">
         <v>4.63657407407407</v>
       </c>
       <c r="G37" s="186">
@@ -10936,7 +12723,7 @@
       <c r="E38" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F38" s="270">
+      <c r="F38" s="202">
         <v>3.3142857142857101</v>
       </c>
       <c r="G38" s="189">
@@ -11028,7 +12815,7 @@
       <c r="E42" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F42" s="268">
+      <c r="F42" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G42" s="186">
@@ -11051,7 +12838,7 @@
       <c r="E43" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F43" s="268">
+      <c r="F43" s="200">
         <v>2.5777777777777775</v>
       </c>
       <c r="G43" s="186">
@@ -11074,7 +12861,7 @@
       <c r="E44" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F44" s="268">
+      <c r="F44" s="200">
         <v>3.31111111111111</v>
       </c>
       <c r="G44" s="186">
@@ -11120,7 +12907,7 @@
       <c r="E46" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F46" s="268">
+      <c r="F46" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G46" s="186">
@@ -11143,7 +12930,7 @@
       <c r="E47" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F47" s="268">
+      <c r="F47" s="200">
         <v>2.5777777777777775</v>
       </c>
       <c r="G47" s="186">
@@ -11166,7 +12953,7 @@
       <c r="E48" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F48" s="268">
+      <c r="F48" s="200">
         <v>3.31111111111111</v>
       </c>
       <c r="G48" s="186">
@@ -11212,7 +12999,7 @@
       <c r="E50" s="186" t="s">
         <v>655</v>
       </c>
-      <c r="F50" s="268">
+      <c r="F50" s="200">
         <v>1.0311111111111111</v>
       </c>
       <c r="G50" s="186">
@@ -11235,7 +13022,7 @@
       <c r="E51" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F51" s="268">
+      <c r="F51" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G51" s="186">
@@ -11258,7 +13045,7 @@
       <c r="E52" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F52" s="268">
+      <c r="F52" s="200">
         <v>4.63657407407407</v>
       </c>
       <c r="G52" s="186">
@@ -11327,7 +13114,7 @@
       <c r="E55" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F55" s="268">
+      <c r="F55" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G55" s="186">
@@ -11350,7 +13137,7 @@
       <c r="E56" s="186" t="s">
         <v>635</v>
       </c>
-      <c r="F56" s="268">
+      <c r="F56" s="200">
         <v>3</v>
       </c>
       <c r="G56" s="186">
@@ -11419,7 +13206,7 @@
       <c r="E59" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F59" s="268">
+      <c r="F59" s="200">
         <v>1.1047619047618999</v>
       </c>
       <c r="G59" s="186">
@@ -11433,7 +13220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6E6311-E6B9-426D-B9CD-C1804811A06D}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -11488,7 +13275,7 @@
       <c r="E2" s="186" t="s">
         <v>627</v>
       </c>
-      <c r="F2" s="271">
+      <c r="F2" s="203">
         <v>14.426399999999997</v>
       </c>
       <c r="G2" s="149">
@@ -11511,7 +13298,7 @@
       <c r="E3" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F3" s="271">
+      <c r="F3" s="203">
         <v>2.5777777777777802</v>
       </c>
       <c r="G3" s="149">
@@ -11534,7 +13321,7 @@
       <c r="E4" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F4" s="271">
+      <c r="F4" s="203">
         <v>3.8</v>
       </c>
       <c r="G4" s="149">
@@ -11557,7 +13344,7 @@
       <c r="E5" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F5" s="271">
+      <c r="F5" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G5" s="149">
@@ -11580,7 +13367,7 @@
       <c r="E6" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F6" s="271">
+      <c r="F6" s="203">
         <v>2.5777777777777802</v>
       </c>
       <c r="G6" s="149">
@@ -11603,7 +13390,7 @@
       <c r="E7" s="186" t="s">
         <v>632</v>
       </c>
-      <c r="F7" s="271">
+      <c r="F7" s="203">
         <v>3.8</v>
       </c>
       <c r="G7" s="149">
@@ -11626,7 +13413,7 @@
       <c r="E8" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="F8" s="271">
+      <c r="F8" s="203">
         <v>12.072378043916389</v>
       </c>
       <c r="G8" s="149">
@@ -11649,7 +13436,7 @@
       <c r="E9" s="186" t="s">
         <v>652</v>
       </c>
-      <c r="F9" s="271">
+      <c r="F9" s="203">
         <v>12.072378043916389</v>
       </c>
       <c r="G9" s="149">
@@ -11672,7 +13459,7 @@
       <c r="E10" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F10" s="271">
+      <c r="F10" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G10" s="149">
@@ -11695,7 +13482,7 @@
       <c r="E11" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F11" s="271">
+      <c r="F11" s="203">
         <v>3.3142857142857101</v>
       </c>
       <c r="G11" s="149">
@@ -11764,7 +13551,7 @@
       <c r="E14" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F14" s="271">
+      <c r="F14" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G14" s="149">
@@ -11787,7 +13574,7 @@
       <c r="E15" s="186" t="s">
         <v>654</v>
       </c>
-      <c r="F15" s="272">
+      <c r="F15" s="204">
         <v>4.8</v>
       </c>
       <c r="G15" s="176">
@@ -11810,7 +13597,7 @@
       <c r="E16" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F16" s="271">
+      <c r="F16" s="203">
         <v>3.0222222222222199</v>
       </c>
       <c r="G16" s="149">
@@ -11833,7 +13620,7 @@
       <c r="E17" s="186" t="s">
         <v>629</v>
       </c>
-      <c r="F17" s="271">
+      <c r="F17" s="203">
         <v>3.0222222222222199</v>
       </c>
       <c r="G17" s="149">
@@ -11856,7 +13643,7 @@
       <c r="E18" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F18" s="271">
+      <c r="F18" s="203">
         <v>4.63657407407407</v>
       </c>
       <c r="G18" s="149">
@@ -11879,7 +13666,7 @@
       <c r="E19" s="186" t="s">
         <v>631</v>
       </c>
-      <c r="F19" s="271">
+      <c r="F19" s="203">
         <v>3.3142857142857101</v>
       </c>
       <c r="G19" s="149">
@@ -11994,7 +13781,7 @@
       <c r="E24" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F24" s="271">
+      <c r="F24" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G24" s="149">
@@ -12017,7 +13804,7 @@
       <c r="E25" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F25" s="271">
+      <c r="F25" s="203">
         <v>2.5777777777777802</v>
       </c>
       <c r="G25" s="149">
@@ -12040,7 +13827,7 @@
       <c r="E26" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F26" s="271">
+      <c r="F26" s="203">
         <v>3.31111111111111</v>
       </c>
       <c r="G26" s="149">
@@ -12086,7 +13873,7 @@
       <c r="E28" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F28" s="271">
+      <c r="F28" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G28" s="149">
@@ -12109,7 +13896,7 @@
       <c r="E29" s="186" t="s">
         <v>634</v>
       </c>
-      <c r="F29" s="271">
+      <c r="F29" s="203">
         <v>2.5777777777777802</v>
       </c>
       <c r="G29" s="149">
@@ -12132,7 +13919,7 @@
       <c r="E30" s="186" t="s">
         <v>628</v>
       </c>
-      <c r="F30" s="271">
+      <c r="F30" s="203">
         <v>3.31111111111111</v>
       </c>
       <c r="G30" s="149">
@@ -12178,7 +13965,7 @@
       <c r="E32" s="186" t="s">
         <v>655</v>
       </c>
-      <c r="F32" s="271">
+      <c r="F32" s="203">
         <v>1.0311111111111111</v>
       </c>
       <c r="G32" s="149">
@@ -12201,7 +13988,7 @@
       <c r="E33" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F33" s="271">
+      <c r="F33" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G33" s="149">
@@ -12224,7 +14011,7 @@
       <c r="E34" s="186" t="s">
         <v>630</v>
       </c>
-      <c r="F34" s="271">
+      <c r="F34" s="203">
         <v>4.63657407407407</v>
       </c>
       <c r="G34" s="149">
@@ -12293,7 +14080,7 @@
       <c r="E37" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F37" s="271">
+      <c r="F37" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G37" s="149">
@@ -12316,7 +14103,7 @@
       <c r="E38" s="186" t="s">
         <v>635</v>
       </c>
-      <c r="F38" s="271">
+      <c r="F38" s="203">
         <v>3</v>
       </c>
       <c r="G38" s="149">
@@ -12385,7 +14172,7 @@
       <c r="E41" s="186" t="s">
         <v>637</v>
       </c>
-      <c r="F41" s="271">
+      <c r="F41" s="203">
         <v>1.1047619047618999</v>
       </c>
       <c r="G41" s="149">
@@ -12544,7 +14331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6728E53C-434A-495F-8AAB-EEEFA7B7F41D}">
   <sheetPr filterMode="1">
     <tabColor rgb="FF002060"/>
@@ -22315,7 +24102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3665249-3B56-4736-82A3-8BF617843F28}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
